--- a/2026-2027-guz-vize.xlsx
+++ b/2026-2027-guz-vize.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{8CC7AB39-C5FF-4323-85A2-4F1EF4D4C0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{270FDAC7-E2E1-4319-91A1-1E3A1CC56858}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80ADA89A-10B5-43DF-A671-19B401D1EDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4048" uniqueCount="583">
   <si>
     <t>Ders Kodu</t>
   </si>
@@ -660,7 +660,7 @@
     <t>Dr. Öğr. Üyesi Merve Hazer Yiğit Uyar</t>
   </si>
   <si>
-    <t>Araş. Gör. Rümeysa Karagöz</t>
+    <t>Arş. Gör. Rümeysa Karagöz</t>
   </si>
   <si>
     <t>SOC131</t>
@@ -672,208 +672,253 @@
     <t>DR. Öğr. Üyesi Onur Yamaner</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Melike Karatay</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Serhat Uyurkulak</t>
+  </si>
+  <si>
+    <t>F-L2-16</t>
+  </si>
+  <si>
+    <t>Arş. Gör. Berke Erdoğan</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Bilge Çağatay</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Ceren İlkay Küçüksoylu Göncü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Öğr. Üyesi Zuhal Özbay Daş </t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Dilara Karslıoğlu</t>
+  </si>
+  <si>
+    <t>IR413</t>
+  </si>
+  <si>
+    <t>B-214</t>
+  </si>
+  <si>
+    <t>POLS205</t>
+  </si>
+  <si>
+    <t>B-211</t>
+  </si>
+  <si>
+    <t>Dr. Levent Önen</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Başak Çün</t>
+  </si>
+  <si>
+    <t>POLS101</t>
+  </si>
+  <si>
+    <t>B-311</t>
+  </si>
+  <si>
+    <t>IR401</t>
+  </si>
+  <si>
+    <t>Doç. Dr. Hazal Papuççular Kutlu</t>
+  </si>
+  <si>
+    <t>IR205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doç. Dr. Nihan Akıncılar </t>
+  </si>
+  <si>
+    <t>LAW331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doç. Dr. Hazal Papuççular Kutlu </t>
+  </si>
+  <si>
+    <t>IR355</t>
+  </si>
+  <si>
+    <t>POLS463</t>
+  </si>
+  <si>
+    <t>MATH127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Öğr.Üyesi Hazar ALtınbaş </t>
+  </si>
+  <si>
+    <t>B-313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Öğr. Üyesi Tuğba Baş </t>
+  </si>
+  <si>
+    <t>B-314</t>
+  </si>
+  <si>
+    <t>Arş. Gör. Cem Bağlum</t>
+  </si>
+  <si>
+    <t>Arş. Gör. Oğuz Kaan BULUT</t>
+  </si>
+  <si>
+    <t>B-315</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Kübra Çelik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doç. Dr. Merve Mamacı </t>
+  </si>
+  <si>
+    <t>IR351</t>
+  </si>
+  <si>
+    <t>POLS201</t>
+  </si>
+  <si>
+    <t>Doç. Dr. Ercan Gündoğan</t>
+  </si>
+  <si>
+    <t>POLS103</t>
+  </si>
+  <si>
+    <t>ECON217</t>
+  </si>
+  <si>
+    <t>B-310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Öğr. Üyesi Zühal Özbay Daş </t>
+  </si>
+  <si>
+    <t>Arş. Gör. Esra Misem Sönmez</t>
+  </si>
+  <si>
+    <t>Arş. Gör. Büşra Nur Doğan</t>
+  </si>
+  <si>
+    <t>ECON201</t>
+  </si>
+  <si>
+    <t>ECON303</t>
+  </si>
+  <si>
+    <t>B-219</t>
+  </si>
+  <si>
+    <t>INTF453</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Ayben Koy</t>
+  </si>
+  <si>
+    <t>FIN411</t>
+  </si>
+  <si>
+    <t>INTF401</t>
+  </si>
+  <si>
+    <t>ECON305</t>
+  </si>
+  <si>
+    <t>ECON203</t>
+  </si>
+  <si>
+    <t>INTF3003</t>
+  </si>
+  <si>
+    <t>FIN201</t>
+  </si>
+  <si>
+    <t>BL-01</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Tuğba Baş</t>
+  </si>
+  <si>
+    <t>INTF211</t>
+  </si>
+  <si>
+    <t>INTF201</t>
+  </si>
+  <si>
+    <t>ECON355</t>
+  </si>
+  <si>
+    <t>B-217</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Ceren İlkay Küçüksoylu</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Hazar Altınbaş</t>
+  </si>
+  <si>
+    <t>ECON207</t>
+  </si>
+  <si>
+    <t>ECON413</t>
+  </si>
+  <si>
+    <t>FIN205</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Birsen ÖZALP</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Zeynep KABADAYI KUŞCU</t>
+  </si>
+  <si>
+    <t>INTF305</t>
+  </si>
+  <si>
+    <t>ECON101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Öğr. Üyesi Onur Yamaner </t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Dilara Karslıoğlu</t>
+  </si>
+  <si>
+    <t>FIN423</t>
+  </si>
+  <si>
+    <t>LAW131</t>
+  </si>
+  <si>
+    <t>Dr. Muratcan Gökdemir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Öğr. Üyesi Merve Hazer Yİğit Uyar </t>
+  </si>
+  <si>
+    <t>Arş. Gör. Oğuz Kaan Bulut</t>
+  </si>
+  <si>
+    <t>ECON381</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Zühal Özbay Daş</t>
+  </si>
+  <si>
+    <t>ECON401</t>
+  </si>
+  <si>
+    <t>FIN203</t>
+  </si>
+  <si>
+    <t>MATH125</t>
+  </si>
+  <si>
     <t>İİSBF</t>
   </si>
   <si>
-    <t xml:space="preserve">İİSBF </t>
-  </si>
-  <si>
-    <t>F-L2-16</t>
-  </si>
-  <si>
-    <t>IR413</t>
-  </si>
-  <si>
-    <t>B-214</t>
-  </si>
-  <si>
-    <t>POLS205</t>
-  </si>
-  <si>
-    <t>B-211</t>
-  </si>
-  <si>
-    <t>Dr. Levent Önen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doç. Dr. Nihan Akıncılar </t>
-  </si>
-  <si>
-    <t>POLS101</t>
-  </si>
-  <si>
-    <t>B-311</t>
-  </si>
-  <si>
-    <t>IR401</t>
-  </si>
-  <si>
-    <t>Doç. Dr. Hazal Papuççular Kutlu</t>
-  </si>
-  <si>
-    <t>IR205</t>
-  </si>
-  <si>
-    <t>LAW331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doç. Dr. Hazal Papuççular Kutlu </t>
-  </si>
-  <si>
-    <t>IR355</t>
-  </si>
-  <si>
-    <t>POLS463</t>
-  </si>
-  <si>
-    <t>MATH127</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Dilara Karslıoğlu</t>
-  </si>
-  <si>
-    <t>B-313</t>
-  </si>
-  <si>
-    <t>Arş. Gör. Büşra Nur Doğan</t>
-  </si>
-  <si>
-    <t>B-314</t>
-  </si>
-  <si>
-    <t>Arş. Gör. Cem Bağlum</t>
-  </si>
-  <si>
-    <t>B-315</t>
-  </si>
-  <si>
-    <t>IR351</t>
-  </si>
-  <si>
-    <t>POLS201</t>
-  </si>
-  <si>
-    <t>Doç. Dr. Ercan Gündoğan</t>
-  </si>
-  <si>
-    <t>POLS103</t>
-  </si>
-  <si>
-    <t>ECON217</t>
-  </si>
-  <si>
-    <t>B-310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Öğr. Üyesi Zühal Özbay Daş </t>
-  </si>
-  <si>
-    <t>Arş. Gör. Berke Erdoğan</t>
-  </si>
-  <si>
-    <t>ECON201</t>
-  </si>
-  <si>
-    <t>ECON303</t>
-  </si>
-  <si>
-    <t>B-219</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Bilge Çağatay</t>
-  </si>
-  <si>
-    <t>INTF453</t>
-  </si>
-  <si>
-    <t>Prof. Dr. Ayben Koy</t>
-  </si>
-  <si>
-    <t>FIN411</t>
-  </si>
-  <si>
-    <t>INTF401</t>
-  </si>
-  <si>
-    <t>ECON305</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Ceren İlkay Küçüksoylu</t>
-  </si>
-  <si>
-    <t>ECON203</t>
-  </si>
-  <si>
-    <t>INTF3003</t>
-  </si>
-  <si>
-    <t>FIN201</t>
-  </si>
-  <si>
-    <t>BL-01</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Tuğba Baş</t>
-  </si>
-  <si>
-    <t>INTF211</t>
-  </si>
-  <si>
-    <t>INTF201</t>
-  </si>
-  <si>
-    <t>ECON355</t>
-  </si>
-  <si>
-    <t>B-217</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Hazar Altınbaş</t>
-  </si>
-  <si>
-    <t>ECON207</t>
-  </si>
-  <si>
-    <t>ECON413</t>
-  </si>
-  <si>
-    <t>FIN205</t>
-  </si>
-  <si>
-    <t>INTF305</t>
-  </si>
-  <si>
-    <t>ECON101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Öğr. Üyesi Onur Yamaner </t>
-  </si>
-  <si>
-    <t>FIN423</t>
-  </si>
-  <si>
-    <t>LAW131</t>
-  </si>
-  <si>
-    <t>Dr. Muratcan Gökdemir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Öğr. Üyesi Merve Hazer Yİğit Uyar </t>
-  </si>
-  <si>
-    <t>ECON381</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Zühal Özbay Daş</t>
-  </si>
-  <si>
-    <t>ECON401</t>
-  </si>
-  <si>
-    <t>FIN203</t>
-  </si>
-  <si>
-    <t>MATH125</t>
+    <t>Dr. Öğr. Üyesi Özgecen Kalkan</t>
   </si>
   <si>
     <t>STAT209</t>
@@ -885,12 +930,12 @@
     <t>Dr. Öğr. Üyesi Zehra Civan</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Birsen Özalp</t>
+  </si>
+  <si>
     <t>F-317</t>
   </si>
   <si>
-    <t>Arş. Gör. Oğuz Kaan Bulut</t>
-  </si>
-  <si>
     <t>STAT2001</t>
   </si>
   <si>
@@ -906,9 +951,6 @@
     <t>ELIT115</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Başak Çün</t>
-  </si>
-  <si>
     <t>ELIT211</t>
   </si>
   <si>
@@ -966,6 +1008,9 @@
     <t>ELIT430</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Ceren İlkay Soylu Küçükgöncü</t>
+  </si>
+  <si>
     <t>ELIT303</t>
   </si>
   <si>
@@ -993,9 +1038,15 @@
     <t>Arş. Gör. Engin Yüzakı</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Dilara KARSLIOĞLU</t>
+  </si>
+  <si>
     <t>FEL101</t>
   </si>
   <si>
+    <t>Dr. Öğr. Özgecan KALKAN</t>
+  </si>
+  <si>
     <t>PSİ303</t>
   </si>
   <si>
@@ -1011,9 +1062,6 @@
     <t>Dr. Öğr. Üyesi Onur Yamaner</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Kübra Çelik</t>
-  </si>
-  <si>
     <t>PSY303</t>
   </si>
   <si>
@@ -1023,6 +1071,9 @@
     <t>B315</t>
   </si>
   <si>
+    <t>Doç. Dr. Nihan AKINCILAR</t>
+  </si>
+  <si>
     <t>PSİ209</t>
   </si>
   <si>
@@ -1035,66 +1086,90 @@
     <t>B314</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Ceren İlkay SOYLU KÜÇÜKGÖNCÜ</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Zühal ÖZBAY DAŞ</t>
+  </si>
+  <si>
+    <t>PSY353</t>
+  </si>
+  <si>
+    <t>B212</t>
+  </si>
+  <si>
+    <t>Doç. Dr. Petek Akman Özdemir</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Özlem Özden Tunca</t>
+  </si>
+  <si>
+    <t>PSİ361</t>
+  </si>
+  <si>
+    <t>B313</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Gökçe Özkılıçcı</t>
+  </si>
+  <si>
+    <t>PSY471</t>
+  </si>
+  <si>
     <t>Doç. Dr. Merve Mamacı</t>
   </si>
   <si>
-    <t>PSY353</t>
-  </si>
-  <si>
-    <t>B212</t>
-  </si>
-  <si>
-    <t>Doç. Dr. Petek Akman Özdemir</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Özlem Özden Tunca</t>
-  </si>
-  <si>
-    <t>PSİ361</t>
-  </si>
-  <si>
-    <t>B313</t>
-  </si>
-  <si>
-    <t>Dr. Öğr. Üyesi Gökçe Özkılıçcı</t>
-  </si>
-  <si>
-    <t>PSY471</t>
+    <t>Doç. Dr. Hazal Papuççular KUTLU</t>
+  </si>
+  <si>
+    <t>PSY201</t>
+  </si>
+  <si>
+    <t>PSİ451</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Hazar ALTINBAŞ</t>
+  </si>
+  <si>
+    <t>PSİ101</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Melike KARATAY</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Bilge ÇAĞATAY</t>
+  </si>
+  <si>
+    <t>PSY301</t>
+  </si>
+  <si>
+    <t>B409</t>
+  </si>
+  <si>
+    <t>PSİ301</t>
+  </si>
+  <si>
+    <t>B410</t>
+  </si>
+  <si>
+    <t>B411</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Tuğba BAŞ</t>
+  </si>
+  <si>
+    <t>B412</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Gökçe Özkılıççı</t>
+  </si>
+  <si>
+    <t>PSİ355</t>
   </si>
   <si>
     <t>Prof. Dr. Sevinç Serpil Aytaç</t>
   </si>
   <si>
-    <t>PSY201</t>
-  </si>
-  <si>
-    <t>PSİ451</t>
-  </si>
-  <si>
-    <t>PSİ101</t>
-  </si>
-  <si>
-    <t>PSY301</t>
-  </si>
-  <si>
-    <t>B409</t>
-  </si>
-  <si>
-    <t>PSİ301</t>
-  </si>
-  <si>
-    <t>B410</t>
-  </si>
-  <si>
-    <t>B411</t>
-  </si>
-  <si>
-    <t>B412</t>
-  </si>
-  <si>
-    <t>PSİ355</t>
-  </si>
-  <si>
     <t>PSY363</t>
   </si>
   <si>
@@ -1104,9 +1179,6 @@
     <t>PSİ201</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Gökçe Özkılıççı</t>
-  </si>
-  <si>
     <t>B312</t>
   </si>
   <si>
@@ -1122,9 +1194,15 @@
     <t>Dr. Merve Karaburun</t>
   </si>
   <si>
+    <t>Arş. Gör. Büşra Nur DOĞAN</t>
+  </si>
+  <si>
     <t>PSİ305</t>
   </si>
   <si>
+    <t>Arş. Gör. Esra Misem SÖNMEZ</t>
+  </si>
+  <si>
     <t>PSY467</t>
   </si>
   <si>
@@ -1167,6 +1245,9 @@
     <t>BL01</t>
   </si>
   <si>
+    <t>Mimarlıktan ar gör istenecek</t>
+  </si>
+  <si>
     <t>MATH129</t>
   </si>
   <si>
@@ -1185,6 +1266,12 @@
     <t>PSİ401</t>
   </si>
   <si>
+    <t>Arş. Gör. Cem BAĞLUM</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Merve Hazer YİĞİT UYAR</t>
+  </si>
+  <si>
     <t>PSY401</t>
   </si>
   <si>
@@ -1209,6 +1296,9 @@
     <t>Dr. Öğr. Üyesi Uğur Özbalkan</t>
   </si>
   <si>
+    <t>Arş. Esra Misem Sönmez</t>
+  </si>
+  <si>
     <t>MIS103</t>
   </si>
   <si>
@@ -1227,6 +1317,9 @@
     <t>CENG201</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Zeynep Kabadayı Kuşcu</t>
+  </si>
+  <si>
     <t>MIS403</t>
   </si>
   <si>
@@ -1257,6 +1350,9 @@
     <t>Dr. Öğr. Üyesi Cem Savaş Aydın</t>
   </si>
   <si>
+    <t>Doç Dr. Nihan Akıncılar</t>
+  </si>
+  <si>
     <t>MIS405</t>
   </si>
   <si>
@@ -1266,12 +1362,12 @@
     <t>B-413</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Zeynep Kabadayı Kuşcu</t>
-  </si>
-  <si>
     <t>B-414</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Özgecan Kalkan</t>
+  </si>
+  <si>
     <t>CENG305</t>
   </si>
   <si>
@@ -1281,18 +1377,24 @@
     <t>Dr. Öğr. Üyesi Adil Gürsel Karaçor</t>
   </si>
   <si>
+    <t>Prof. Dr. Ayben KOY</t>
+  </si>
+  <si>
+    <t>Doç. Dr. Nihan Akıncılar</t>
+  </si>
+  <si>
     <t>MIS373</t>
   </si>
   <si>
     <t>B-410</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Özgecan Kalkan</t>
-  </si>
-  <si>
     <t>B-411</t>
   </si>
   <si>
+    <t>Doç. Dr. Hazal Pabucçular Kutlu</t>
+  </si>
+  <si>
     <t>CENG463</t>
   </si>
   <si>
@@ -1302,6 +1404,12 @@
     <t>MIS208</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Alp Giray KAYA</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Şahamet Bülbül</t>
+  </si>
+  <si>
     <t>MIS211</t>
   </si>
   <si>
@@ -1311,9 +1419,6 @@
     <t>MIS109</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Birsen Özalp</t>
-  </si>
-  <si>
     <t>MIS213</t>
   </si>
   <si>
@@ -1365,9 +1470,6 @@
     <t>Arş. Gör. Mehmet Emir Erdem</t>
   </si>
   <si>
-    <t>Arş. Gör. Berkay Aktürk</t>
-  </si>
-  <si>
     <t>YBS207</t>
   </si>
   <si>
@@ -1386,9 +1488,6 @@
     <t>YBS101</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Melike Karatay</t>
-  </si>
-  <si>
     <t>BİL205</t>
   </si>
   <si>
@@ -1398,6 +1497,9 @@
     <t>MAT107</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Zuhal Özbay Daş</t>
+  </si>
+  <si>
     <t>YBS203</t>
   </si>
   <si>
@@ -1419,9 +1521,18 @@
     <t>BA301</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Gökçe ÖZKILIÇCI</t>
+  </si>
+  <si>
     <t>F-104</t>
   </si>
   <si>
+    <t>Prof. Dr. Seda BAĞDATLI KALKAN</t>
+  </si>
+  <si>
+    <t>Dr. Öğr. Üyesi Onur YAMANER</t>
+  </si>
+  <si>
     <t>BA305</t>
   </si>
   <si>
@@ -1434,9 +1545,6 @@
     <t xml:space="preserve">Vize </t>
   </si>
   <si>
-    <t>Doç. Dr. Nihan Akıncılar</t>
-  </si>
-  <si>
     <t>POLS550</t>
   </si>
   <si>
@@ -1479,6 +1587,9 @@
     <t>Doç. Dr. Elif Çaloğlu Büyükselçuk</t>
   </si>
   <si>
+    <t>Berkay</t>
+  </si>
+  <si>
     <t>İST513</t>
   </si>
   <si>
@@ -1486,6 +1597,9 @@
   </si>
   <si>
     <t>MBA562</t>
+  </si>
+  <si>
+    <t>Berrak</t>
   </si>
   <si>
     <t>MBA554</t>
@@ -1720,7 +1834,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1840,8 +1954,22 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1959,6 +2087,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2347,7 +2481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2642,12 +2776,6 @@
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2656,6 +2784,25 @@
     <xf numFmtId="0" fontId="18" fillId="19" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2982,7 +3129,7 @@
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.85546875" customWidth="1"/>
-    <col min="9" max="9" width="39.42578125" customWidth="1"/>
+    <col min="9" max="9" width="44.140625" customWidth="1"/>
     <col min="10" max="10" width="34.85546875" customWidth="1"/>
     <col min="11" max="11" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -7072,8 +7219,8 @@
       <c r="H117" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I117" s="6" t="s">
-        <v>53</v>
+      <c r="I117" s="155" t="s">
+        <v>30</v>
       </c>
       <c r="J117" s="6" t="s">
         <v>16</v>
@@ -16567,7 +16714,7 @@
         <v>206</v>
       </c>
       <c r="J390" s="133" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="391" spans="1:11">
@@ -16596,10 +16743,10 @@
         <v>209</v>
       </c>
       <c r="I391" s="136" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J391" s="133" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="392" spans="1:11">
@@ -16628,15 +16775,15 @@
         <v>209</v>
       </c>
       <c r="I392" s="136" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J392" s="133" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="393" spans="1:11">
       <c r="A393" s="133" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B393" s="133">
         <v>1</v>
@@ -16645,7 +16792,7 @@
         <v>12</v>
       </c>
       <c r="D393" s="133" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E393" s="134">
         <v>46335</v>
@@ -16666,7 +16813,7 @@
     </row>
     <row r="394" spans="1:11">
       <c r="A394" s="133" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B394" s="133">
         <v>1</v>
@@ -16675,7 +16822,7 @@
         <v>12</v>
       </c>
       <c r="D394" s="133" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E394" s="134">
         <v>46336</v>
@@ -16687,16 +16834,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H394" s="133" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I394" s="136" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J394" s="133"/>
     </row>
     <row r="395" spans="1:11">
       <c r="A395" s="133" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B395" s="133">
         <v>1</v>
@@ -16705,7 +16852,7 @@
         <v>12</v>
       </c>
       <c r="D395" s="133" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E395" s="134">
         <v>46336</v>
@@ -16717,7 +16864,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H395" s="133" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I395" s="136" t="s">
         <v>205</v>
@@ -16726,7 +16873,7 @@
     </row>
     <row r="396" spans="1:11">
       <c r="A396" s="133" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B396" s="133">
         <v>1</v>
@@ -16747,7 +16894,7 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H396" s="133" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I396" s="136" t="s">
         <v>205</v>
@@ -16756,7 +16903,7 @@
     </row>
     <row r="397" spans="1:11">
       <c r="A397" s="133" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B397" s="133">
         <v>1</v>
@@ -16777,16 +16924,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H397" s="133" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I397" s="136" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="J397" s="133"/>
     </row>
     <row r="398" spans="1:11">
       <c r="A398" s="133" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B398" s="133">
         <v>1</v>
@@ -16795,7 +16942,7 @@
         <v>12</v>
       </c>
       <c r="D398" s="133" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E398" s="134">
         <v>46337</v>
@@ -16807,16 +16954,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H398" s="136" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="I398" s="136" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J398" s="133"/>
     </row>
     <row r="399" spans="1:11">
       <c r="A399" s="133" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B399" s="133">
         <v>1</v>
@@ -16825,7 +16972,7 @@
         <v>12</v>
       </c>
       <c r="D399" s="133" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E399" s="134">
         <v>46338</v>
@@ -16837,7 +16984,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H399" s="136" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="I399" s="136" t="s">
         <v>205</v>
@@ -16846,7 +16993,7 @@
     </row>
     <row r="400" spans="1:11">
       <c r="A400" s="133" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B400" s="133">
         <v>1</v>
@@ -16867,16 +17014,16 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H400" s="136" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="I400" s="136" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J400" s="133"/>
     </row>
     <row r="401" spans="1:10">
       <c r="A401" s="133" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B401" s="133">
         <v>1</v>
@@ -16885,7 +17032,7 @@
         <v>12</v>
       </c>
       <c r="D401" s="133" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E401" s="134">
         <v>46339</v>
@@ -16897,16 +17044,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H401" s="133" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I401" s="136" t="s">
         <v>206</v>
       </c>
-      <c r="J401" s="133"/>
+      <c r="J401" s="133" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="402" spans="1:10">
       <c r="A402" s="133" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B402" s="133">
         <v>2</v>
@@ -16915,7 +17064,7 @@
         <v>12</v>
       </c>
       <c r="D402" s="133" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E402" s="134">
         <v>46339</v>
@@ -16927,16 +17076,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H402" s="133" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I402" s="136" t="s">
-        <v>231</v>
-      </c>
-      <c r="J402" s="133"/>
+        <v>237</v>
+      </c>
+      <c r="J402" s="133" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="403" spans="1:10">
       <c r="A403" s="133" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B403" s="133">
         <v>2</v>
@@ -16945,7 +17096,7 @@
         <v>12</v>
       </c>
       <c r="D403" s="133" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E403" s="134">
         <v>46339</v>
@@ -16957,16 +17108,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H403" s="133" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I403" s="136" t="s">
-        <v>233</v>
-      </c>
-      <c r="J403" s="133"/>
+        <v>239</v>
+      </c>
+      <c r="J403" s="166" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="404" spans="1:10">
       <c r="A404" s="133" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B404" s="133">
         <v>2</v>
@@ -16975,7 +17128,7 @@
         <v>12</v>
       </c>
       <c r="D404" s="133" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E404" s="134">
         <v>46339</v>
@@ -16987,16 +17140,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H404" s="133" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I404" s="136" t="s">
-        <v>210</v>
-      </c>
-      <c r="J404" s="133"/>
+        <v>242</v>
+      </c>
+      <c r="J404" s="133" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="405" spans="1:10">
       <c r="A405" s="133" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B405" s="133">
         <v>1</v>
@@ -17005,7 +17160,7 @@
         <v>12</v>
       </c>
       <c r="D405" s="133" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E405" s="134">
         <v>46339</v>
@@ -17026,7 +17181,7 @@
     </row>
     <row r="406" spans="1:10">
       <c r="A406" s="133" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B406" s="133">
         <v>1</v>
@@ -17035,7 +17190,7 @@
         <v>12</v>
       </c>
       <c r="D406" s="133" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E406" s="134">
         <v>46339</v>
@@ -17047,7 +17202,7 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H406" s="133" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="I406" s="136" t="s">
         <v>206</v>
@@ -17056,7 +17211,7 @@
     </row>
     <row r="407" spans="1:10">
       <c r="A407" s="133" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B407" s="133">
         <v>1</v>
@@ -17065,7 +17220,7 @@
         <v>12</v>
       </c>
       <c r="D407" s="133" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E407" s="134">
         <v>46339</v>
@@ -17077,7 +17232,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="H407" s="133" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="I407" s="136" t="s">
         <v>206</v>
@@ -17086,7 +17241,7 @@
     </row>
     <row r="408" spans="1:10">
       <c r="A408" s="137" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B408" s="137">
         <v>1</v>
@@ -17095,7 +17250,7 @@
         <v>12</v>
       </c>
       <c r="D408" s="137" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E408" s="138">
         <v>46335</v>
@@ -17107,16 +17262,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H408" s="137" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I408" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="J408" s="137"/>
+        <v>213</v>
+      </c>
+      <c r="J408" s="137" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="409" spans="1:10">
       <c r="A409" s="137" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B409" s="137">
         <v>1</v>
@@ -17125,7 +17282,7 @@
         <v>12</v>
       </c>
       <c r="D409" s="137" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E409" s="138">
         <v>46335</v>
@@ -17137,18 +17294,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H409" s="137" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I409" s="140" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="J409" s="140" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
     </row>
     <row r="410" spans="1:10">
       <c r="A410" s="137" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B410" s="137">
         <v>1</v>
@@ -17157,7 +17314,7 @@
         <v>12</v>
       </c>
       <c r="D410" s="137" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E410" s="138">
         <v>46335</v>
@@ -17169,16 +17326,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H410" s="137" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I410" s="137" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="J410" s="137"/>
     </row>
     <row r="411" spans="1:10">
       <c r="A411" s="137" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B411" s="137">
         <v>1</v>
@@ -17187,7 +17344,7 @@
         <v>12</v>
       </c>
       <c r="D411" s="137" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E411" s="138">
         <v>46335</v>
@@ -17199,16 +17356,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H411" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="I411" s="137" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="J411" s="140"/>
     </row>
     <row r="412" spans="1:10">
       <c r="A412" s="137" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B412" s="137">
         <v>1</v>
@@ -17217,7 +17374,7 @@
         <v>12</v>
       </c>
       <c r="D412" s="137" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E412" s="138">
         <v>46335</v>
@@ -17229,16 +17386,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H412" s="137" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="I412" s="137" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="J412" s="140"/>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" ht="15">
       <c r="A413" s="137" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B413" s="137">
         <v>1</v>
@@ -17259,18 +17416,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H413" s="137" t="s">
-        <v>248</v>
-      </c>
-      <c r="I413" s="140" t="s">
-        <v>210</v>
-      </c>
-      <c r="J413" s="140" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="414" spans="1:10">
+        <v>257</v>
+      </c>
+      <c r="I413" s="165" t="s">
+        <v>240</v>
+      </c>
+      <c r="J413" s="165"/>
+    </row>
+    <row r="414" spans="1:10" ht="15">
       <c r="A414" s="137" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B414" s="137">
         <v>1</v>
@@ -17291,18 +17446,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H414" s="137" t="s">
-        <v>248</v>
-      </c>
-      <c r="I414" s="140" t="s">
-        <v>210</v>
-      </c>
-      <c r="J414" s="140" t="s">
-        <v>210</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="I414" s="165" t="s">
+        <v>240</v>
+      </c>
+      <c r="J414" s="140"/>
     </row>
     <row r="415" spans="1:10">
       <c r="A415" s="137" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B415" s="137">
         <v>1</v>
@@ -17311,7 +17464,7 @@
         <v>12</v>
       </c>
       <c r="D415" s="137" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E415" s="138">
         <v>46336</v>
@@ -17323,18 +17476,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H415" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="I415" s="141" t="s">
-        <v>252</v>
-      </c>
-      <c r="J415" s="140" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10">
+        <v>239</v>
+      </c>
+      <c r="J415" s="140"/>
+    </row>
+    <row r="416" spans="1:10" ht="15">
       <c r="A416" s="137" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B416" s="137">
         <v>1</v>
@@ -17343,7 +17494,7 @@
         <v>12</v>
       </c>
       <c r="D416" s="137" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E416" s="138">
         <v>46336</v>
@@ -17355,18 +17506,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H416" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="I416" s="141" t="s">
-        <v>252</v>
-      </c>
-      <c r="J416" s="140" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="417" spans="1:10">
+        <v>239</v>
+      </c>
+      <c r="J416" s="140"/>
+    </row>
+    <row r="417" spans="1:10" ht="15">
       <c r="A417" s="137" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B417" s="137">
         <v>1</v>
@@ -17375,7 +17524,7 @@
         <v>12</v>
       </c>
       <c r="D417" s="137" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E417" s="138">
         <v>46336</v>
@@ -17387,18 +17536,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H417" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="I417" s="141" t="s">
-        <v>252</v>
-      </c>
-      <c r="J417" s="140" t="s">
-        <v>210</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="J417" s="140"/>
     </row>
     <row r="418" spans="1:10">
       <c r="A418" s="137" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B418" s="137">
         <v>1</v>
@@ -17407,7 +17554,7 @@
         <v>12</v>
       </c>
       <c r="D418" s="137" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E418" s="138">
         <v>46336</v>
@@ -17419,18 +17566,18 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H418" s="137" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I418" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="J418" s="137" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
     </row>
     <row r="419" spans="1:10">
       <c r="A419" s="137" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B419" s="137">
         <v>1</v>
@@ -17439,7 +17586,7 @@
         <v>12</v>
       </c>
       <c r="D419" s="137" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E419" s="138">
         <v>46336</v>
@@ -17451,18 +17598,18 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H419" s="137" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I419" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="J419" s="137" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
     </row>
     <row r="420" spans="1:10">
       <c r="A420" s="137" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B420" s="137">
         <v>1</v>
@@ -17471,7 +17618,7 @@
         <v>12</v>
       </c>
       <c r="D420" s="137" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E420" s="138">
         <v>46336</v>
@@ -17483,18 +17630,18 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H420" s="137" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I420" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="J420" s="137" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
     </row>
     <row r="421" spans="1:10">
       <c r="A421" s="137" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B421" s="137">
         <v>1</v>
@@ -17503,7 +17650,7 @@
         <v>12</v>
       </c>
       <c r="D421" s="137" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E421" s="138">
         <v>46337</v>
@@ -17515,16 +17662,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H421" s="141" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="I421" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="J421" s="140"/>
     </row>
     <row r="422" spans="1:10">
       <c r="A422" s="137" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B422" s="137">
         <v>1</v>
@@ -17533,7 +17680,7 @@
         <v>12</v>
       </c>
       <c r="D422" s="137" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E422" s="138">
         <v>46337</v>
@@ -17545,16 +17692,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H422" s="141" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="I422" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="J422" s="140"/>
     </row>
     <row r="423" spans="1:10">
       <c r="A423" s="137" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B423" s="137">
         <v>1</v>
@@ -17563,7 +17710,7 @@
         <v>12</v>
       </c>
       <c r="D423" s="137" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E423" s="138">
         <v>46337</v>
@@ -17575,16 +17722,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H423" s="141" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="I423" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="J423" s="140"/>
     </row>
     <row r="424" spans="1:10">
       <c r="A424" s="137" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B424" s="137">
         <v>1</v>
@@ -17605,18 +17752,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H424" s="137" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I424" s="140" t="s">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="J424" s="140" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
     </row>
     <row r="425" spans="1:10">
       <c r="A425" s="137" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B425" s="137">
         <v>1</v>
@@ -17637,18 +17784,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H425" s="137" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I425" s="140" t="s">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="J425" s="140" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
     </row>
     <row r="426" spans="1:10">
       <c r="A426" s="137" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B426" s="137">
         <v>1</v>
@@ -17657,7 +17804,7 @@
         <v>12</v>
       </c>
       <c r="D426" s="137" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E426" s="138">
         <v>46337</v>
@@ -17669,18 +17816,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H426" s="137" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="I426" s="140" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="J426" s="140" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" ht="15">
       <c r="A427" s="137" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B427" s="137">
         <v>1</v>
@@ -17689,7 +17836,7 @@
         <v>12</v>
       </c>
       <c r="D427" s="137" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E427" s="138">
         <v>46337</v>
@@ -17701,18 +17848,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H427" s="137" t="s">
-        <v>252</v>
-      </c>
-      <c r="I427" s="140" t="s">
-        <v>210</v>
+        <v>270</v>
+      </c>
+      <c r="I427" s="141" t="s">
+        <v>265</v>
       </c>
       <c r="J427" s="140" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
     </row>
     <row r="428" spans="1:10">
       <c r="A428" s="137" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B428" s="137">
         <v>1</v>
@@ -17721,7 +17868,7 @@
         <v>12</v>
       </c>
       <c r="D428" s="137" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E428" s="138">
         <v>46337</v>
@@ -17733,16 +17880,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H428" s="137" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="I428" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="J428" s="140"/>
+        <v>213</v>
+      </c>
+      <c r="J428" s="140" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="429" spans="1:10">
       <c r="A429" s="137" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B429" s="137">
         <v>1</v>
@@ -17751,7 +17900,7 @@
         <v>12</v>
       </c>
       <c r="D429" s="137" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E429" s="138">
         <v>46337</v>
@@ -17763,16 +17912,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H429" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I429" s="137" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="J429" s="140"/>
     </row>
     <row r="430" spans="1:10">
       <c r="A430" s="137" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B430" s="137">
         <v>1</v>
@@ -17781,7 +17930,7 @@
         <v>12</v>
       </c>
       <c r="D430" s="137" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E430" s="138">
         <v>46338</v>
@@ -17793,18 +17942,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H430" s="137" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I430" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="J430" s="137" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="431" spans="1:10">
       <c r="A431" s="137" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B431" s="137">
         <v>1</v>
@@ -17813,7 +17962,7 @@
         <v>12</v>
       </c>
       <c r="D431" s="137" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E431" s="138">
         <v>46338</v>
@@ -17825,18 +17974,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H431" s="137" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I431" s="137" t="s">
         <v>206</v>
       </c>
       <c r="J431" s="137" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
     </row>
     <row r="432" spans="1:10">
       <c r="A432" s="137" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B432" s="137">
         <v>1</v>
@@ -17845,7 +17994,7 @@
         <v>12</v>
       </c>
       <c r="D432" s="137" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E432" s="138">
         <v>46338</v>
@@ -17857,18 +18006,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H432" s="137" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I432" s="137" t="s">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="J432" s="137" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
     </row>
     <row r="433" spans="1:10">
       <c r="A433" s="137" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B433" s="137">
         <v>1</v>
@@ -17889,16 +18038,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H433" s="137" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="I433" s="137" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="J433" s="140"/>
     </row>
     <row r="434" spans="1:10">
       <c r="A434" s="137" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B434" s="137">
         <v>1</v>
@@ -17907,7 +18056,7 @@
         <v>12</v>
       </c>
       <c r="D434" s="137" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E434" s="138">
         <v>46338</v>
@@ -17919,16 +18068,16 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H434" s="137" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="I434" s="137" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="J434" s="137"/>
     </row>
     <row r="435" spans="1:10">
       <c r="A435" s="137" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B435" s="137">
         <v>1</v>
@@ -17949,16 +18098,16 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H435" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I435" s="137" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="J435" s="140"/>
     </row>
-    <row r="436" spans="1:10">
+    <row r="436" spans="1:10" ht="15">
       <c r="A436" s="137" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B436" s="137">
         <v>1</v>
@@ -17979,18 +18128,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H436" s="137" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I436" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="J436" s="140" t="s">
-        <v>210</v>
+        <v>213</v>
+      </c>
+      <c r="J436" s="154" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="437" spans="1:10">
       <c r="A437" s="137" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B437" s="137">
         <v>1</v>
@@ -17999,7 +18148,7 @@
         <v>12</v>
       </c>
       <c r="D437" s="137" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E437" s="138">
         <v>46339</v>
@@ -18011,18 +18160,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H437" s="137" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I437" s="140" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="J437" s="140" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="438" spans="1:10">
+    <row r="438" spans="1:10" ht="15">
       <c r="A438" s="137" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B438" s="137">
         <v>1</v>
@@ -18031,7 +18180,7 @@
         <v>12</v>
       </c>
       <c r="D438" s="137" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="E438" s="138">
         <v>46339</v>
@@ -18043,18 +18192,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H438" s="137" t="s">
-        <v>280</v>
-      </c>
-      <c r="I438" s="140" t="s">
-        <v>210</v>
+        <v>295</v>
+      </c>
+      <c r="I438" s="137" t="s">
+        <v>213</v>
       </c>
       <c r="J438" s="140" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="439" spans="1:10">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" ht="15">
       <c r="A439" s="137" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B439" s="137">
         <v>1</v>
@@ -18063,7 +18212,7 @@
         <v>12</v>
       </c>
       <c r="D439" s="137" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E439" s="138">
         <v>46339</v>
@@ -18075,18 +18224,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H439" s="137" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="I439" s="137" t="s">
-        <v>282</v>
-      </c>
-      <c r="J439" s="137" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10">
+        <v>285</v>
+      </c>
+      <c r="J439" s="140" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" ht="15">
       <c r="A440" s="137" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="B440" s="137">
         <v>1</v>
@@ -18095,7 +18244,7 @@
         <v>12</v>
       </c>
       <c r="D440" s="137" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E440" s="138">
         <v>46339</v>
@@ -18107,18 +18256,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H440" s="137" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="I440" s="137" t="s">
-        <v>282</v>
-      </c>
-      <c r="J440" s="137" t="s">
-        <v>242</v>
+        <v>285</v>
+      </c>
+      <c r="J440" s="140" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="441" spans="1:10">
       <c r="A441" s="137" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B441" s="137">
         <v>1</v>
@@ -18127,7 +18276,7 @@
         <v>12</v>
       </c>
       <c r="D441" s="137" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E441" s="138">
         <v>46339</v>
@@ -18139,16 +18288,16 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H441" s="137" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I441" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="J441" s="137"/>
     </row>
     <row r="442" spans="1:10">
       <c r="A442" s="137" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B442" s="137">
         <v>1</v>
@@ -18157,7 +18306,7 @@
         <v>12</v>
       </c>
       <c r="D442" s="137" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E442" s="138">
         <v>46339</v>
@@ -18169,16 +18318,16 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H442" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I442" s="137" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="J442" s="137"/>
     </row>
     <row r="443" spans="1:10">
       <c r="A443" s="137" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B443" s="137">
         <v>1</v>
@@ -18187,7 +18336,7 @@
         <v>12</v>
       </c>
       <c r="D443" s="137" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E443" s="138">
         <v>46339</v>
@@ -18199,16 +18348,16 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H443" s="137" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I443" s="137" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="J443" s="137"/>
     </row>
     <row r="444" spans="1:10">
       <c r="A444" s="115" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B444" s="115">
         <v>1</v>
@@ -18229,14 +18378,15 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H444" s="115" t="s">
-        <v>288</v>
-      </c>
-      <c r="I444" s="115"/>
-      <c r="J444" s="115"/>
+        <v>223</v>
+      </c>
+      <c r="I444" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="445" spans="1:10">
       <c r="A445" s="115" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B445" s="115">
         <v>1</v>
@@ -18257,14 +18407,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H445" s="115" t="s">
-        <v>290</v>
-      </c>
-      <c r="I445" s="115"/>
-      <c r="J445" s="115"/>
+        <v>304</v>
+      </c>
+      <c r="I445" s="115" t="s">
+        <v>223</v>
+      </c>
+      <c r="J445" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="446" spans="1:10">
       <c r="A446" s="115" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B446" s="115">
         <v>1</v>
@@ -18273,7 +18427,7 @@
         <v>12</v>
       </c>
       <c r="D446" s="115" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E446" s="116">
         <v>46336</v>
@@ -18285,14 +18439,15 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H446" s="115" t="s">
-        <v>290</v>
-      </c>
-      <c r="I446" s="115"/>
-      <c r="J446" s="115"/>
+        <v>304</v>
+      </c>
+      <c r="I446" s="115" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="447" spans="1:10">
       <c r="A447" s="115" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B447" s="115">
         <v>1</v>
@@ -18313,14 +18468,15 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H447" s="115" t="s">
-        <v>288</v>
-      </c>
-      <c r="I447" s="115"/>
-      <c r="J447" s="115"/>
+        <v>223</v>
+      </c>
+      <c r="I447" s="115" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="448" spans="1:10">
       <c r="A448" s="115" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B448" s="115">
         <v>1</v>
@@ -18329,7 +18485,7 @@
         <v>12</v>
       </c>
       <c r="D448" s="115" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E448" s="116">
         <v>46336</v>
@@ -18341,14 +18497,15 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H448" s="115" t="s">
-        <v>295</v>
-      </c>
-      <c r="I448" s="115"/>
-      <c r="J448" s="115"/>
+        <v>309</v>
+      </c>
+      <c r="I448" s="115" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="449" spans="1:10">
       <c r="A449" s="115" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B449" s="115">
         <v>1</v>
@@ -18357,7 +18514,7 @@
         <v>12</v>
       </c>
       <c r="D449" s="115" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E449" s="116">
         <v>46336</v>
@@ -18369,14 +18526,15 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H449" s="115" t="s">
-        <v>298</v>
-      </c>
-      <c r="I449" s="115"/>
-      <c r="J449" s="115"/>
+        <v>312</v>
+      </c>
+      <c r="I449" s="115" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="450" spans="1:10">
       <c r="A450" s="115" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B450" s="115">
         <v>1</v>
@@ -18385,7 +18543,7 @@
         <v>12</v>
       </c>
       <c r="D450" s="115" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="E450" s="116">
         <v>46337</v>
@@ -18397,14 +18555,15 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H450" s="115" t="s">
-        <v>301</v>
-      </c>
-      <c r="I450" s="115"/>
-      <c r="J450" s="115"/>
+        <v>315</v>
+      </c>
+      <c r="I450" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="451" spans="1:10">
       <c r="A451" s="115" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B451" s="115">
         <v>1</v>
@@ -18413,7 +18572,7 @@
         <v>12</v>
       </c>
       <c r="D451" s="115" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="E451" s="116">
         <v>46337</v>
@@ -18425,14 +18584,15 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H451" s="115" t="s">
-        <v>301</v>
-      </c>
-      <c r="I451" s="115"/>
-      <c r="J451" s="115"/>
+        <v>315</v>
+      </c>
+      <c r="I451" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="452" spans="1:10">
       <c r="A452" s="115" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B452" s="115">
         <v>1</v>
@@ -18441,7 +18601,7 @@
         <v>12</v>
       </c>
       <c r="D452" s="115" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E452" s="116">
         <v>46337</v>
@@ -18453,14 +18613,15 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H452" s="115" t="s">
-        <v>298</v>
-      </c>
-      <c r="I452" s="115"/>
-      <c r="J452" s="115"/>
+        <v>312</v>
+      </c>
+      <c r="I452" s="115" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="453" spans="1:10">
       <c r="A453" s="115" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B453" s="115">
         <v>1</v>
@@ -18469,7 +18630,7 @@
         <v>12</v>
       </c>
       <c r="D453" s="115" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="E453" s="116">
         <v>46338</v>
@@ -18481,23 +18642,27 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H453" s="115" t="s">
-        <v>295</v>
-      </c>
-      <c r="I453" s="115"/>
-      <c r="J453" s="115"/>
+        <v>309</v>
+      </c>
+      <c r="I453" s="115" t="s">
+        <v>223</v>
+      </c>
+      <c r="J453" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="454" spans="1:10">
       <c r="A454" s="115" t="s">
+        <v>320</v>
+      </c>
+      <c r="B454" s="115">
+        <v>1</v>
+      </c>
+      <c r="C454" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="D454" s="115" t="s">
         <v>306</v>
-      </c>
-      <c r="B454" s="115">
-        <v>1</v>
-      </c>
-      <c r="C454" s="115" t="s">
-        <v>12</v>
-      </c>
-      <c r="D454" s="115" t="s">
-        <v>292</v>
       </c>
       <c r="E454" s="116">
         <v>46338</v>
@@ -18509,14 +18674,15 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H454" s="115" t="s">
-        <v>288</v>
-      </c>
-      <c r="I454" s="115"/>
-      <c r="J454" s="115"/>
+        <v>223</v>
+      </c>
+      <c r="I454" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="455" spans="1:10">
       <c r="A455" s="115" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B455" s="115">
         <v>1</v>
@@ -18525,7 +18691,7 @@
         <v>12</v>
       </c>
       <c r="D455" s="115" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E455" s="116">
         <v>46338</v>
@@ -18537,14 +18703,15 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H455" s="115" t="s">
-        <v>288</v>
-      </c>
-      <c r="I455" s="115"/>
-      <c r="J455" s="115"/>
+        <v>223</v>
+      </c>
+      <c r="I455" s="115" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="456" spans="1:10">
       <c r="A456" s="115" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B456" s="115">
         <v>1</v>
@@ -18553,7 +18720,7 @@
         <v>12</v>
       </c>
       <c r="D456" s="115" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E456" s="116">
         <v>46338</v>
@@ -18565,14 +18732,15 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H456" s="115" t="s">
-        <v>295</v>
-      </c>
-      <c r="I456" s="115"/>
-      <c r="J456" s="115"/>
+        <v>309</v>
+      </c>
+      <c r="I456" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="457" spans="1:10">
       <c r="A457" s="115" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B457" s="115">
         <v>1</v>
@@ -18593,14 +18761,15 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H457" s="115" t="s">
-        <v>290</v>
-      </c>
-      <c r="I457" s="115"/>
-      <c r="J457" s="115"/>
+        <v>304</v>
+      </c>
+      <c r="I457" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="458" spans="1:10">
       <c r="A458" s="115" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B458" s="115">
         <v>1</v>
@@ -18621,14 +18790,15 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H458" s="115" t="s">
-        <v>288</v>
-      </c>
-      <c r="I458" s="115"/>
-      <c r="J458" s="115"/>
+        <v>223</v>
+      </c>
+      <c r="I458" s="115" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="459" spans="1:10">
       <c r="A459" s="115" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B459" s="115">
         <v>1</v>
@@ -18649,14 +18819,18 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H459" s="115" t="s">
-        <v>290</v>
-      </c>
-      <c r="I459" s="115"/>
-      <c r="J459" s="115"/>
+        <v>304</v>
+      </c>
+      <c r="I459" s="115" t="s">
+        <v>251</v>
+      </c>
+      <c r="J459" s="115" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="460" spans="1:10">
       <c r="A460" s="115" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B460" s="115">
         <v>1</v>
@@ -18677,14 +18851,18 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="H460" s="115" t="s">
-        <v>295</v>
-      </c>
-      <c r="I460" s="115"/>
-      <c r="J460" s="115"/>
-    </row>
-    <row r="461" spans="1:10">
+        <v>309</v>
+      </c>
+      <c r="I460" s="115" t="s">
+        <v>223</v>
+      </c>
+      <c r="J460" s="115" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="461" spans="1:10" ht="15">
       <c r="A461" s="142" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B461" s="142">
         <v>1</v>
@@ -18693,7 +18871,7 @@
         <v>12</v>
       </c>
       <c r="D461" s="142" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="E461" s="143">
         <v>46335</v>
@@ -18705,18 +18883,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H461" s="145" t="s">
-        <v>315</v>
-      </c>
-      <c r="I461" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J461" s="153" t="s">
-        <v>210</v>
+        <v>330</v>
+      </c>
+      <c r="I461" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J461" s="150" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="462" spans="1:10">
       <c r="A462" s="142" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="B462" s="142">
         <v>1</v>
@@ -18737,18 +18915,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H462" s="145" t="s">
-        <v>315</v>
-      </c>
-      <c r="I462" s="153" t="s">
-        <v>210</v>
-      </c>
-      <c r="J462" s="153" t="s">
-        <v>210</v>
+        <v>330</v>
+      </c>
+      <c r="I462" s="151" t="s">
+        <v>334</v>
+      </c>
+      <c r="J462" s="151" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="463" spans="1:10">
       <c r="A463" s="142" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B463" s="142">
         <v>1</v>
@@ -18769,16 +18947,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H463" s="145" t="s">
-        <v>319</v>
-      </c>
-      <c r="I463" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J463" s="152"/>
+        <v>336</v>
+      </c>
+      <c r="I463" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J463" s="150"/>
     </row>
     <row r="464" spans="1:10">
       <c r="A464" s="142" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B464" s="142">
         <v>1</v>
@@ -18799,16 +18977,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H464" s="145" t="s">
-        <v>319</v>
-      </c>
-      <c r="I464" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J464" s="152"/>
+        <v>336</v>
+      </c>
+      <c r="I464" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J464" s="150"/>
     </row>
     <row r="465" spans="1:10">
       <c r="A465" s="142" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="B465" s="142">
         <v>1</v>
@@ -18829,18 +19007,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H465" s="145" t="s">
-        <v>322</v>
-      </c>
-      <c r="I465" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J465" s="153" t="s">
-        <v>323</v>
+        <v>339</v>
+      </c>
+      <c r="I465" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J465" s="151" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="466" spans="1:10">
       <c r="A466" s="142" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B466" s="142">
         <v>1</v>
@@ -18861,16 +19039,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H466" s="145" t="s">
-        <v>319</v>
-      </c>
-      <c r="I466" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J466" s="152"/>
+        <v>336</v>
+      </c>
+      <c r="I466" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J466" s="150"/>
     </row>
     <row r="467" spans="1:10">
       <c r="A467" s="142" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B467" s="142">
         <v>1</v>
@@ -18879,7 +19057,7 @@
         <v>12</v>
       </c>
       <c r="D467" s="142" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="E467" s="143">
         <v>46335</v>
@@ -18891,18 +19069,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H467" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="I467" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J467" s="152" t="s">
-        <v>211</v>
+        <v>242</v>
+      </c>
+      <c r="I467" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J467" s="150" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="468" spans="1:10" ht="15">
       <c r="A468" s="142" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="B468" s="142">
         <v>1</v>
@@ -18911,7 +19089,7 @@
         <v>12</v>
       </c>
       <c r="D468" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E468" s="143">
         <v>46335</v>
@@ -18923,18 +19101,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H468" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="I468" s="155" t="s">
-        <v>329</v>
-      </c>
-      <c r="J468" s="152" t="s">
-        <v>211</v>
+        <v>242</v>
+      </c>
+      <c r="I468" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="J468" s="150" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="469" spans="1:10" ht="15">
       <c r="A469" s="142" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="B469" s="142">
         <v>1</v>
@@ -18943,7 +19121,7 @@
         <v>12</v>
       </c>
       <c r="D469" s="142" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E469" s="143">
         <v>46335</v>
@@ -18955,18 +19133,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H469" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="I469" s="155" t="s">
-        <v>331</v>
-      </c>
-      <c r="J469" s="152" t="s">
-        <v>211</v>
+        <v>242</v>
+      </c>
+      <c r="I469" s="150" t="s">
+        <v>348</v>
+      </c>
+      <c r="J469" s="150" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="470" spans="1:10">
       <c r="A470" s="142" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B470" s="142">
         <v>1</v>
@@ -18975,7 +19153,7 @@
         <v>12</v>
       </c>
       <c r="D470" s="142" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="E470" s="143">
         <v>46336</v>
@@ -18987,16 +19165,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H470" s="145" t="s">
-        <v>334</v>
-      </c>
-      <c r="I470" s="152" t="s">
-        <v>335</v>
-      </c>
-      <c r="J470" s="152"/>
+        <v>352</v>
+      </c>
+      <c r="I470" s="150" t="s">
+        <v>353</v>
+      </c>
+      <c r="J470" s="150"/>
     </row>
     <row r="471" spans="1:10" ht="15">
       <c r="A471" s="142" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B471" s="142">
         <v>1</v>
@@ -19005,7 +19183,7 @@
         <v>12</v>
       </c>
       <c r="D471" s="142" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E471" s="143">
         <v>46336</v>
@@ -19017,18 +19195,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H471" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I471" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J471" s="155" t="s">
-        <v>334</v>
+        <v>353</v>
+      </c>
+      <c r="I471" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J471" s="153" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="472" spans="1:10" ht="15">
       <c r="A472" s="142" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B472" s="142">
         <v>1</v>
@@ -19037,7 +19215,7 @@
         <v>12</v>
       </c>
       <c r="D472" s="142" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E472" s="143">
         <v>46336</v>
@@ -19049,18 +19227,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H472" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I472" s="155" t="s">
-        <v>338</v>
-      </c>
-      <c r="J472" s="152" t="s">
-        <v>320</v>
+        <v>353</v>
+      </c>
+      <c r="I472" s="153" t="s">
+        <v>356</v>
+      </c>
+      <c r="J472" s="150" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="473" spans="1:10" ht="15">
       <c r="A473" s="142" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B473" s="142">
         <v>1</v>
@@ -19069,7 +19247,7 @@
         <v>12</v>
       </c>
       <c r="D473" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E473" s="143">
         <v>46336</v>
@@ -19081,16 +19259,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H473" s="145" t="s">
-        <v>331</v>
-      </c>
-      <c r="I473" s="155" t="s">
-        <v>340</v>
-      </c>
-      <c r="J473" s="152"/>
+        <v>358</v>
+      </c>
+      <c r="I473" s="153" t="s">
+        <v>359</v>
+      </c>
+      <c r="J473" s="150"/>
     </row>
     <row r="474" spans="1:10">
       <c r="A474" s="142" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="B474" s="142">
         <v>1</v>
@@ -19099,7 +19277,7 @@
         <v>12</v>
       </c>
       <c r="D474" s="142" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E474" s="143">
         <v>46336</v>
@@ -19111,16 +19289,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H474" s="145" t="s">
-        <v>331</v>
-      </c>
-      <c r="I474" s="152" t="s">
-        <v>335</v>
-      </c>
-      <c r="J474" s="152"/>
+        <v>358</v>
+      </c>
+      <c r="I474" s="150" t="s">
+        <v>353</v>
+      </c>
+      <c r="J474" s="150"/>
     </row>
     <row r="475" spans="1:10" ht="15">
       <c r="A475" s="142" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="B475" s="142">
         <v>1</v>
@@ -19141,18 +19319,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H475" s="145" t="s">
-        <v>338</v>
-      </c>
-      <c r="I475" s="155" t="s">
-        <v>334</v>
-      </c>
-      <c r="J475" s="152" t="s">
-        <v>210</v>
+        <v>356</v>
+      </c>
+      <c r="I475" s="153" t="s">
+        <v>352</v>
+      </c>
+      <c r="J475" s="150" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="476" spans="1:10">
       <c r="A476" s="142" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="B476" s="142">
         <v>1</v>
@@ -19173,18 +19351,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H476" s="145" t="s">
-        <v>338</v>
-      </c>
-      <c r="I476" s="152" t="s">
-        <v>210</v>
-      </c>
-      <c r="J476" s="152" t="s">
-        <v>210</v>
+        <v>356</v>
+      </c>
+      <c r="I476" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="J476" s="150" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="477" spans="1:10" ht="15">
       <c r="A477" s="142" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="B477" s="142">
         <v>1</v>
@@ -19193,7 +19371,7 @@
         <v>12</v>
       </c>
       <c r="D477" s="142" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E477" s="143">
         <v>46336</v>
@@ -19205,18 +19383,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H477" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I477" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J477" s="155" t="s">
-        <v>319</v>
+        <v>353</v>
+      </c>
+      <c r="I477" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J477" s="153" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="15">
       <c r="A478" s="142" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="B478" s="142">
         <v>1</v>
@@ -19225,7 +19403,7 @@
         <v>12</v>
       </c>
       <c r="D478" s="142" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E478" s="143">
         <v>46336</v>
@@ -19237,18 +19415,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H478" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I478" s="155" t="s">
-        <v>331</v>
-      </c>
-      <c r="J478" s="152" t="s">
-        <v>211</v>
+        <v>353</v>
+      </c>
+      <c r="I478" s="153" t="s">
+        <v>364</v>
+      </c>
+      <c r="J478" s="150" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="479" spans="1:10">
       <c r="A479" s="142" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B479" s="142">
         <v>1</v>
@@ -19257,7 +19435,7 @@
         <v>12</v>
       </c>
       <c r="D479" s="142" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="E479" s="143">
         <v>46337</v>
@@ -19269,16 +19447,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H479" s="145" t="s">
-        <v>331</v>
-      </c>
-      <c r="I479" s="152" t="s">
-        <v>210</v>
-      </c>
-      <c r="J479" s="152"/>
+        <v>358</v>
+      </c>
+      <c r="I479" s="150" t="s">
+        <v>364</v>
+      </c>
+      <c r="J479" s="150"/>
     </row>
     <row r="480" spans="1:10">
       <c r="A480" s="142" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B480" s="142">
         <v>1</v>
@@ -19287,7 +19465,7 @@
         <v>12</v>
       </c>
       <c r="D480" s="142" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="E480" s="143">
         <v>46337</v>
@@ -19299,18 +19477,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H480" s="145" t="s">
-        <v>329</v>
-      </c>
-      <c r="I480" s="152" t="s">
-        <v>210</v>
-      </c>
-      <c r="J480" s="152" t="s">
-        <v>210</v>
+        <v>346</v>
+      </c>
+      <c r="I480" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="J480" s="150" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="481" spans="1:10">
       <c r="A481" s="142" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B481" s="142">
         <v>1</v>
@@ -19319,7 +19497,7 @@
         <v>12</v>
       </c>
       <c r="D481" s="142" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="E481" s="143">
         <v>46337</v>
@@ -19331,18 +19509,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H481" s="145" t="s">
-        <v>329</v>
-      </c>
-      <c r="I481" s="152" t="s">
-        <v>210</v>
-      </c>
-      <c r="J481" s="152" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="482" spans="1:10">
+        <v>346</v>
+      </c>
+      <c r="I481" s="150" t="s">
+        <v>349</v>
+      </c>
+      <c r="J481" s="150" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" ht="15">
       <c r="A482" s="142" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B482" s="142">
         <v>1</v>
@@ -19351,7 +19529,7 @@
         <v>12</v>
       </c>
       <c r="D482" s="142" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="E482" s="143">
         <v>46337</v>
@@ -19363,18 +19541,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H482" s="145" t="s">
-        <v>329</v>
-      </c>
-      <c r="I482" s="152" t="s">
-        <v>210</v>
-      </c>
-      <c r="J482" s="152" t="s">
-        <v>210</v>
+        <v>346</v>
+      </c>
+      <c r="I482" s="156" t="s">
+        <v>242</v>
+      </c>
+      <c r="J482" s="156" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="483" spans="1:10">
       <c r="A483" s="142" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="B483" s="142">
         <v>1</v>
@@ -19383,7 +19561,7 @@
         <v>12</v>
       </c>
       <c r="D483" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E483" s="143">
         <v>46337</v>
@@ -19395,16 +19573,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H483" s="145" t="s">
-        <v>340</v>
-      </c>
-      <c r="I483" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J483" s="152"/>
+        <v>375</v>
+      </c>
+      <c r="I483" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J483" s="150"/>
     </row>
     <row r="484" spans="1:10" ht="15">
       <c r="A484" s="142" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="B484" s="142">
         <v>1</v>
@@ -19413,7 +19591,7 @@
         <v>12</v>
       </c>
       <c r="D484" s="142" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="E484" s="143">
         <v>46337</v>
@@ -19425,16 +19603,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H484" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="I484" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J484" s="152"/>
+        <v>242</v>
+      </c>
+      <c r="I484" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J484" s="150"/>
     </row>
     <row r="485" spans="1:10" ht="15">
       <c r="A485" s="142" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="B485" s="142">
         <v>1</v>
@@ -19443,7 +19621,7 @@
         <v>12</v>
       </c>
       <c r="D485" s="142" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="E485" s="143">
         <v>46337</v>
@@ -19455,18 +19633,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H485" s="145" t="s">
-        <v>354</v>
-      </c>
-      <c r="I485" s="155" t="s">
-        <v>331</v>
-      </c>
-      <c r="J485" s="155" t="s">
-        <v>323</v>
+        <v>373</v>
+      </c>
+      <c r="I485" s="153" t="s">
+        <v>358</v>
+      </c>
+      <c r="J485" s="153" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="486" spans="1:10" ht="15">
       <c r="A486" s="142" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="B486" s="142">
         <v>1</v>
@@ -19475,7 +19653,7 @@
         <v>12</v>
       </c>
       <c r="D486" s="142" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="E486" s="143">
         <v>46337</v>
@@ -19487,18 +19665,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H486" s="145" t="s">
-        <v>354</v>
-      </c>
-      <c r="I486" s="155" t="s">
-        <v>329</v>
-      </c>
-      <c r="J486" s="152" t="s">
-        <v>316</v>
+        <v>373</v>
+      </c>
+      <c r="I486" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="J486" s="150" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="487" spans="1:10">
       <c r="A487" s="142" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="B487" s="142">
         <v>1</v>
@@ -19507,7 +19685,7 @@
         <v>12</v>
       </c>
       <c r="D487" s="142" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="E487" s="143">
         <v>46337</v>
@@ -19519,16 +19697,16 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H487" s="145" t="s">
-        <v>331</v>
-      </c>
-      <c r="I487" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J487" s="152"/>
+        <v>358</v>
+      </c>
+      <c r="I487" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J487" s="150"/>
     </row>
     <row r="488" spans="1:10" ht="15">
       <c r="A488" s="142" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="B488" s="142">
         <v>1</v>
@@ -19537,7 +19715,7 @@
         <v>12</v>
       </c>
       <c r="D488" s="142" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="E488" s="143">
         <v>46337</v>
@@ -19549,18 +19727,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H488" s="145" t="s">
-        <v>359</v>
-      </c>
-      <c r="I488" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J488" s="155" t="s">
-        <v>329</v>
+        <v>383</v>
+      </c>
+      <c r="I488" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J488" s="153" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="489" spans="1:10" ht="15">
       <c r="A489" s="142" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="B489" s="142">
         <v>1</v>
@@ -19569,7 +19747,7 @@
         <v>12</v>
       </c>
       <c r="D489" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E489" s="143">
         <v>46337</v>
@@ -19581,18 +19759,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H489" s="145" t="s">
-        <v>359</v>
-      </c>
-      <c r="I489" s="155" t="s">
-        <v>323</v>
-      </c>
-      <c r="J489" s="155" t="s">
-        <v>319</v>
+        <v>383</v>
+      </c>
+      <c r="I489" s="153" t="s">
+        <v>384</v>
+      </c>
+      <c r="J489" s="153" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="490" spans="1:10" ht="15">
       <c r="A490" s="142" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="B490" s="142">
         <v>1</v>
@@ -19601,7 +19779,7 @@
         <v>12</v>
       </c>
       <c r="D490" s="142" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="E490" s="143">
         <v>46338</v>
@@ -19613,18 +19791,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H490" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I490" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J490" s="155" t="s">
-        <v>323</v>
+        <v>353</v>
+      </c>
+      <c r="I490" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J490" s="153" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="491" spans="1:10" ht="15">
       <c r="A491" s="142" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="B491" s="142">
         <v>1</v>
@@ -19633,7 +19811,7 @@
         <v>12</v>
       </c>
       <c r="D491" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E491" s="143">
         <v>46338</v>
@@ -19645,18 +19823,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H491" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I491" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J491" s="155" t="s">
-        <v>319</v>
+        <v>353</v>
+      </c>
+      <c r="I491" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J491" s="153" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="492" spans="1:10">
       <c r="A492" s="142" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="B492" s="142">
         <v>1</v>
@@ -19665,7 +19843,7 @@
         <v>12</v>
       </c>
       <c r="D492" s="142" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="E492" s="143">
         <v>46338</v>
@@ -19677,16 +19855,16 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H492" s="145" t="s">
-        <v>362</v>
-      </c>
-      <c r="I492" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J492" s="152"/>
+        <v>388</v>
+      </c>
+      <c r="I492" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J492" s="150"/>
     </row>
     <row r="493" spans="1:10" ht="15">
       <c r="A493" s="142" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B493" s="142">
         <v>1</v>
@@ -19695,7 +19873,7 @@
         <v>12</v>
       </c>
       <c r="D493" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E493" s="143">
         <v>46338</v>
@@ -19707,18 +19885,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H493" s="145" t="s">
-        <v>334</v>
-      </c>
-      <c r="I493" s="154" t="s">
-        <v>335</v>
-      </c>
-      <c r="J493" s="155" t="s">
-        <v>319</v>
+        <v>352</v>
+      </c>
+      <c r="I493" s="152" t="s">
+        <v>353</v>
+      </c>
+      <c r="J493" s="153" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="494" spans="1:10" ht="15">
       <c r="A494" s="142" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B494" s="142">
         <v>1</v>
@@ -19727,7 +19905,7 @@
         <v>12</v>
       </c>
       <c r="D494" s="142" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="E494" s="143">
         <v>46338</v>
@@ -19739,18 +19917,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H494" s="145" t="s">
-        <v>334</v>
-      </c>
-      <c r="I494" s="155" t="s">
-        <v>331</v>
-      </c>
-      <c r="J494" s="152" t="s">
-        <v>210</v>
+        <v>352</v>
+      </c>
+      <c r="I494" s="156" t="s">
+        <v>242</v>
+      </c>
+      <c r="J494" s="150" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="495" spans="1:10" ht="15">
       <c r="A495" s="142" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="B495" s="142">
         <v>1</v>
@@ -19759,7 +19937,7 @@
         <v>12</v>
       </c>
       <c r="D495" s="142" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E495" s="143">
         <v>46338</v>
@@ -19771,18 +19949,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H495" s="145" t="s">
+        <v>352</v>
+      </c>
+      <c r="I495" s="163" t="s">
+        <v>365</v>
+      </c>
+      <c r="J495" s="150" t="s">
         <v>334</v>
-      </c>
-      <c r="I495" s="155" t="s">
-        <v>323</v>
-      </c>
-      <c r="J495" s="152" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="496" spans="1:10" ht="15">
       <c r="A496" s="142" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="B496" s="142">
         <v>1</v>
@@ -19791,7 +19969,7 @@
         <v>12</v>
       </c>
       <c r="D496" s="142" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E496" s="143">
         <v>46338</v>
@@ -19803,18 +19981,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H496" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I496" s="155" t="s">
-        <v>334</v>
-      </c>
-      <c r="J496" s="152" t="s">
-        <v>210</v>
+        <v>353</v>
+      </c>
+      <c r="I496" s="153" t="s">
+        <v>352</v>
+      </c>
+      <c r="J496" s="150" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="497" spans="1:10" ht="15">
       <c r="A497" s="142" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="B497" s="142">
         <v>1</v>
@@ -19823,7 +20001,7 @@
         <v>12</v>
       </c>
       <c r="D497" s="142" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E497" s="143">
         <v>46338</v>
@@ -19835,18 +20013,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H497" s="145" t="s">
-        <v>335</v>
-      </c>
-      <c r="I497" s="155" t="s">
-        <v>319</v>
-      </c>
-      <c r="J497" s="152" t="s">
-        <v>210</v>
+        <v>353</v>
+      </c>
+      <c r="I497" s="153" t="s">
+        <v>336</v>
+      </c>
+      <c r="J497" s="150" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="498" spans="1:10" ht="15">
       <c r="A498" s="142" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="B498" s="142">
         <v>1</v>
@@ -19855,7 +20033,7 @@
         <v>12</v>
       </c>
       <c r="D498" s="142" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="E498" s="143">
         <v>46338</v>
@@ -19867,18 +20045,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H498" s="145" t="s">
-        <v>368</v>
-      </c>
-      <c r="I498" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J498" s="154" t="s">
-        <v>335</v>
+        <v>394</v>
+      </c>
+      <c r="I498" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J498" s="152" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="499" spans="1:10" ht="15">
       <c r="A499" s="142" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="B499" s="142">
         <v>1</v>
@@ -19887,7 +20065,7 @@
         <v>12</v>
       </c>
       <c r="D499" s="142" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="E499" s="143">
         <v>46338</v>
@@ -19899,18 +20077,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H499" s="145" t="s">
-        <v>368</v>
-      </c>
-      <c r="I499" s="155" t="s">
-        <v>329</v>
-      </c>
-      <c r="J499" s="152" t="s">
-        <v>210</v>
+        <v>394</v>
+      </c>
+      <c r="I499" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="J499" s="150" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="500" spans="1:10" ht="15">
       <c r="A500" s="142" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="B500" s="142">
         <v>1</v>
@@ -19919,7 +20097,7 @@
         <v>12</v>
       </c>
       <c r="D500" s="142" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E500" s="143">
         <v>46338</v>
@@ -19931,16 +20109,16 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H500" s="145" t="s">
-        <v>362</v>
-      </c>
-      <c r="I500" s="155" t="s">
-        <v>323</v>
-      </c>
-      <c r="J500" s="152"/>
+        <v>388</v>
+      </c>
+      <c r="I500" s="153" t="s">
+        <v>242</v>
+      </c>
+      <c r="J500" s="150"/>
     </row>
     <row r="501" spans="1:10" ht="15">
       <c r="A501" s="142" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="B501" s="142">
         <v>1</v>
@@ -19949,7 +20127,7 @@
         <v>12</v>
       </c>
       <c r="D501" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E501" s="143">
         <v>46338</v>
@@ -19961,18 +20139,18 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H501" s="145" t="s">
-        <v>372</v>
-      </c>
-      <c r="I501" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J501" s="155" t="s">
-        <v>335</v>
+        <v>398</v>
+      </c>
+      <c r="I501" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J501" s="153" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="502" spans="1:10">
       <c r="A502" s="142" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="B502" s="142">
         <v>1</v>
@@ -19981,7 +20159,7 @@
         <v>12</v>
       </c>
       <c r="D502" s="142" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="E502" s="143">
         <v>46338</v>
@@ -19993,16 +20171,18 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H502" s="145" t="s">
-        <v>372</v>
-      </c>
-      <c r="I502" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J502" s="152"/>
-    </row>
-    <row r="503" spans="1:10">
+        <v>398</v>
+      </c>
+      <c r="I502" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J502" s="150" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" ht="30.75">
       <c r="A503" s="142" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="B503" s="142">
         <v>1</v>
@@ -20011,7 +20191,7 @@
         <v>12</v>
       </c>
       <c r="D503" s="142" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="E503" s="143">
         <v>46339</v>
@@ -20023,16 +20203,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H503" s="145" t="s">
-        <v>229</v>
-      </c>
-      <c r="I503" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J503" s="152"/>
+        <v>217</v>
+      </c>
+      <c r="I503" s="159" t="s">
+        <v>401</v>
+      </c>
+      <c r="J503" s="156" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="504" spans="1:10" ht="15">
       <c r="A504" s="142" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="B504" s="142">
         <v>1</v>
@@ -20041,7 +20223,7 @@
         <v>12</v>
       </c>
       <c r="D504" s="142" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="E504" s="143">
         <v>46339</v>
@@ -20053,18 +20235,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H504" s="145" t="s">
-        <v>229</v>
-      </c>
-      <c r="I504" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J504" s="155" t="s">
-        <v>319</v>
+        <v>217</v>
+      </c>
+      <c r="I504" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J504" s="153" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="505" spans="1:10" ht="15">
       <c r="A505" s="142" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="B505" s="142">
         <v>1</v>
@@ -20073,7 +20255,7 @@
         <v>12</v>
       </c>
       <c r="D505" s="142" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="E505" s="143">
         <v>46339</v>
@@ -20085,16 +20267,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H505" s="145" t="s">
-        <v>329</v>
-      </c>
-      <c r="I505" s="155" t="s">
-        <v>334</v>
-      </c>
-      <c r="J505" s="152"/>
+        <v>346</v>
+      </c>
+      <c r="I505" s="153" t="s">
+        <v>352</v>
+      </c>
+      <c r="J505" s="150"/>
     </row>
     <row r="506" spans="1:10">
       <c r="A506" s="142" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="B506" s="142">
         <v>1</v>
@@ -20103,7 +20285,7 @@
         <v>12</v>
       </c>
       <c r="D506" s="142" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="E506" s="143">
         <v>46339</v>
@@ -20115,18 +20297,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H506" s="145" t="s">
-        <v>334</v>
-      </c>
-      <c r="I506" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J506" s="152" t="s">
-        <v>210</v>
+        <v>352</v>
+      </c>
+      <c r="I506" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J506" s="150" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="507" spans="1:10" ht="15">
       <c r="A507" s="142" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="B507" s="142">
         <v>1</v>
@@ -20135,7 +20317,7 @@
         <v>12</v>
       </c>
       <c r="D507" s="142" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E507" s="143">
         <v>46339</v>
@@ -20147,18 +20329,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H507" s="145" t="s">
-        <v>334</v>
-      </c>
-      <c r="I507" s="155" t="s">
-        <v>329</v>
-      </c>
-      <c r="J507" s="152" t="s">
-        <v>210</v>
+        <v>352</v>
+      </c>
+      <c r="I507" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="J507" s="150" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="508" spans="1:10">
       <c r="A508" s="142" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="B508" s="142">
         <v>1</v>
@@ -20167,7 +20349,7 @@
         <v>12</v>
       </c>
       <c r="D508" s="142" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="E508" s="143">
         <v>46339</v>
@@ -20179,18 +20361,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H508" s="145" t="s">
-        <v>319</v>
-      </c>
-      <c r="I508" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J508" s="152" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="509" spans="1:10">
+        <v>336</v>
+      </c>
+      <c r="I508" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J508" s="150" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" ht="15">
       <c r="A509" s="142" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="B509" s="142">
         <v>1</v>
@@ -20199,7 +20381,7 @@
         <v>12</v>
       </c>
       <c r="D509" s="142" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E509" s="143">
         <v>46339</v>
@@ -20211,18 +20393,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H509" s="145" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="I509" s="152" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="J509" s="152" t="s">
-        <v>210</v>
+        <v>358</v>
       </c>
     </row>
     <row r="510" spans="1:10">
       <c r="A510" s="142" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="B510" s="142">
         <v>1</v>
@@ -20231,7 +20413,7 @@
         <v>12</v>
       </c>
       <c r="D510" s="142" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="E510" s="143">
         <v>46339</v>
@@ -20243,18 +20425,18 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H510" s="145" t="s">
-        <v>329</v>
-      </c>
-      <c r="I510" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J510" s="152" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="511" spans="1:10">
+        <v>346</v>
+      </c>
+      <c r="I510" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J510" s="150" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" ht="15">
       <c r="A511" s="142" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="B511" s="142">
         <v>1</v>
@@ -20263,7 +20445,7 @@
         <v>12</v>
       </c>
       <c r="D511" s="142" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="E511" s="143">
         <v>46339</v>
@@ -20275,18 +20457,18 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H511" s="145" t="s">
-        <v>329</v>
-      </c>
-      <c r="I511" s="152" t="s">
-        <v>210</v>
-      </c>
-      <c r="J511" s="152" t="s">
-        <v>210</v>
+        <v>346</v>
+      </c>
+      <c r="I511" s="163" t="s">
+        <v>409</v>
+      </c>
+      <c r="J511" s="150" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="512" spans="1:10">
       <c r="A512" s="142" t="s">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="B512" s="142">
         <v>1</v>
@@ -20295,7 +20477,7 @@
         <v>12</v>
       </c>
       <c r="D512" s="142" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="E512" s="143">
         <v>46339</v>
@@ -20307,18 +20489,18 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H512" s="145" t="s">
-        <v>329</v>
-      </c>
-      <c r="I512" s="152" t="s">
-        <v>320</v>
-      </c>
-      <c r="J512" s="152" t="s">
-        <v>210</v>
+        <v>346</v>
+      </c>
+      <c r="I512" s="150" t="s">
+        <v>337</v>
+      </c>
+      <c r="J512" s="150" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="513" spans="1:10">
       <c r="A513" s="142" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="B513" s="142">
         <v>1</v>
@@ -20327,7 +20509,7 @@
         <v>12</v>
       </c>
       <c r="D513" s="142" t="s">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="E513" s="143">
         <v>46339</v>
@@ -20339,18 +20521,18 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="H513" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="I513" s="152" t="s">
-        <v>316</v>
-      </c>
-      <c r="J513" s="152" t="s">
-        <v>210</v>
+        <v>242</v>
+      </c>
+      <c r="I513" s="150" t="s">
+        <v>331</v>
+      </c>
+      <c r="J513" s="150" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="514" spans="1:10" ht="15">
       <c r="A514" s="142" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="B514" s="142">
         <v>1</v>
@@ -20359,7 +20541,7 @@
         <v>12</v>
       </c>
       <c r="D514" s="142" t="s">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="E514" s="143">
         <v>46339</v>
@@ -20371,18 +20553,18 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="H514" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="I514" s="155" t="s">
-        <v>329</v>
-      </c>
-      <c r="J514" s="152" t="s">
-        <v>210</v>
+        <v>242</v>
+      </c>
+      <c r="I514" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="J514" s="150" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="515" spans="1:10">
       <c r="A515" s="142" t="s">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="B515" s="142">
         <v>1</v>
@@ -20391,7 +20573,7 @@
         <v>12</v>
       </c>
       <c r="D515" s="142" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="E515" s="143">
         <v>46339</v>
@@ -20403,18 +20585,18 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="H515" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="I515" s="152" t="s">
-        <v>210</v>
-      </c>
-      <c r="J515" s="152" t="s">
-        <v>210</v>
+        <v>242</v>
+      </c>
+      <c r="I515" s="150" t="s">
+        <v>364</v>
+      </c>
+      <c r="J515" s="150" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="516" spans="1:10">
       <c r="A516" s="115" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="B516" s="115">
         <v>1</v>
@@ -20423,7 +20605,7 @@
         <v>12</v>
       </c>
       <c r="D516" s="115" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E516" s="116">
         <v>46335</v>
@@ -20435,16 +20617,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H516" s="115" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="I516" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J516" s="115"/>
+        <v>252</v>
+      </c>
+      <c r="J516" s="115" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="517" spans="1:10">
       <c r="A517" s="115" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="B517" s="115">
         <v>1</v>
@@ -20453,7 +20637,7 @@
         <v>12</v>
       </c>
       <c r="D517" s="115" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E517" s="116">
         <v>46335</v>
@@ -20465,18 +20649,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H517" s="115" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="I517" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J517" s="115" t="s">
-        <v>210</v>
+        <v>418</v>
       </c>
     </row>
     <row r="518" spans="1:10">
       <c r="A518" s="115" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="B518" s="115">
         <v>2</v>
@@ -20485,7 +20669,7 @@
         <v>12</v>
       </c>
       <c r="D518" s="115" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E518" s="116">
         <v>46335</v>
@@ -20497,18 +20681,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H518" s="115" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="I518" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J518" s="115" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="519" spans="1:10">
       <c r="A519" s="115" t="s">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="B519" s="115">
         <v>2</v>
@@ -20517,7 +20701,7 @@
         <v>12</v>
       </c>
       <c r="D519" s="115" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E519" s="116">
         <v>46335</v>
@@ -20529,16 +20713,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H519" s="115" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="I519" s="115" t="s">
-        <v>233</v>
-      </c>
-      <c r="J519" s="115"/>
+        <v>239</v>
+      </c>
+      <c r="J519" s="115" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="520" spans="1:10">
       <c r="A520" s="115" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="B520" s="115">
         <v>1</v>
@@ -20547,7 +20733,7 @@
         <v>12</v>
       </c>
       <c r="D520" s="115" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E520" s="116">
         <v>46335</v>
@@ -20559,16 +20745,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H520" s="115" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="I520" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J520" s="115"/>
+        <v>252</v>
+      </c>
+      <c r="J520" s="115" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="521" spans="1:10">
       <c r="A521" s="115" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="B521" s="115">
         <v>1</v>
@@ -20577,7 +20765,7 @@
         <v>12</v>
       </c>
       <c r="D521" s="115" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E521" s="116">
         <v>46335</v>
@@ -20589,16 +20777,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H521" s="115" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="I521" s="115" t="s">
-        <v>233</v>
-      </c>
-      <c r="J521" s="115"/>
+        <v>239</v>
+      </c>
+      <c r="J521" s="115" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="522" spans="1:10">
       <c r="A522" s="115" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="B522" s="115">
         <v>1</v>
@@ -20607,7 +20797,7 @@
         <v>12</v>
       </c>
       <c r="D522" s="115" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E522" s="116">
         <v>46335</v>
@@ -20619,16 +20809,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H522" s="115" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="I522" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J522" s="115"/>
+        <v>252</v>
+      </c>
+      <c r="J522" s="115" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="523" spans="1:10">
       <c r="A523" s="115" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="B523" s="115">
         <v>1</v>
@@ -20637,7 +20829,7 @@
         <v>12</v>
       </c>
       <c r="D523" s="115" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="E523" s="116">
         <v>46335</v>
@@ -20649,18 +20841,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H523" s="115" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="I523" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J523" s="115" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="524" spans="1:10">
       <c r="A524" s="115" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="B524" s="115">
         <v>1</v>
@@ -20669,7 +20861,7 @@
         <v>12</v>
       </c>
       <c r="D524" s="115" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="E524" s="116">
         <v>46335</v>
@@ -20681,18 +20873,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H524" s="115" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="I524" s="115" t="s">
-        <v>210</v>
+        <v>352</v>
       </c>
       <c r="J524" s="115" t="s">
-        <v>210</v>
+        <v>358</v>
       </c>
     </row>
     <row r="525" spans="1:10">
       <c r="A525" s="115" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="B525" s="115">
         <v>3</v>
@@ -20701,7 +20893,7 @@
         <v>12</v>
       </c>
       <c r="D525" s="115" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="E525" s="116">
         <v>46335</v>
@@ -20713,10 +20905,10 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H525" s="115" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="I525" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J525" s="115" t="s">
         <v>210</v>
@@ -20724,7 +20916,7 @@
     </row>
     <row r="526" spans="1:10">
       <c r="A526" s="115" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="B526" s="115">
         <v>3</v>
@@ -20733,7 +20925,7 @@
         <v>12</v>
       </c>
       <c r="D526" s="115" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="E526" s="116">
         <v>46335</v>
@@ -20745,16 +20937,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H526" s="115" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="I526" s="115" t="s">
-        <v>233</v>
-      </c>
-      <c r="J526" s="115"/>
+        <v>239</v>
+      </c>
+      <c r="J526" s="115" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="527" spans="1:10">
       <c r="A527" s="115" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
       <c r="B527" s="115">
         <v>1</v>
@@ -20763,7 +20957,7 @@
         <v>12</v>
       </c>
       <c r="D527" s="115" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
       <c r="E527" s="116">
         <v>46335</v>
@@ -20775,18 +20969,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H527" s="115" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
       <c r="I527" s="115" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="J527" s="115" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="528" spans="1:10">
       <c r="A528" s="115" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
       <c r="B528" s="115">
         <v>1</v>
@@ -20795,7 +20989,7 @@
         <v>12</v>
       </c>
       <c r="D528" s="115" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="E528" s="116">
         <v>46335</v>
@@ -20807,16 +21001,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H528" s="115" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
       <c r="I528" s="115" t="s">
-        <v>233</v>
-      </c>
-      <c r="J528" s="115"/>
+        <v>239</v>
+      </c>
+      <c r="J528" s="115" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="529" spans="1:10">
       <c r="A529" s="115" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="B529" s="115">
         <v>1</v>
@@ -20825,7 +21021,7 @@
         <v>12</v>
       </c>
       <c r="D529" s="115" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E529" s="116">
         <v>46336</v>
@@ -20837,18 +21033,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H529" s="115" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="I529" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J529" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="530" spans="1:10">
       <c r="A530" s="115" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="B530" s="115">
         <v>2</v>
@@ -20857,7 +21053,7 @@
         <v>12</v>
       </c>
       <c r="D530" s="115" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E530" s="116">
         <v>46336</v>
@@ -20869,18 +21065,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H530" s="115" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="I530" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J530" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="531" spans="1:10">
       <c r="A531" s="115" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="B531" s="115">
         <v>1</v>
@@ -20889,7 +21085,7 @@
         <v>12</v>
       </c>
       <c r="D531" s="115" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="E531" s="116">
         <v>46336</v>
@@ -20901,16 +21097,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H531" s="115" t="s">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="I531" s="115" t="s">
-        <v>210</v>
-      </c>
-      <c r="J531" s="115"/>
+        <v>436</v>
+      </c>
+      <c r="J531" s="115" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="532" spans="1:10">
       <c r="A532" s="115" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="B532" s="115">
         <v>1</v>
@@ -20919,7 +21117,7 @@
         <v>12</v>
       </c>
       <c r="D532" s="115" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="E532" s="116">
         <v>46336</v>
@@ -20931,16 +21129,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H532" s="115" t="s">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="I532" s="115" t="s">
-        <v>210</v>
-      </c>
-      <c r="J532" s="115"/>
+        <v>436</v>
+      </c>
+      <c r="J532" s="115" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="533" spans="1:10">
       <c r="A533" s="115" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="B533" s="115">
         <v>1</v>
@@ -20949,7 +21149,7 @@
         <v>12</v>
       </c>
       <c r="D533" s="115" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="E533" s="116">
         <v>46336</v>
@@ -20961,16 +21161,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H533" s="115" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I533" s="115" t="s">
-        <v>210</v>
-      </c>
-      <c r="J533" s="115"/>
+        <v>375</v>
+      </c>
+      <c r="J533" s="115" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="534" spans="1:10">
       <c r="A534" s="115" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="B534" s="115">
         <v>1</v>
@@ -20979,7 +21181,7 @@
         <v>12</v>
       </c>
       <c r="D534" s="115" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="E534" s="116">
         <v>46336</v>
@@ -20991,18 +21193,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H534" s="115" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I534" s="115" t="s">
-        <v>210</v>
+        <v>441</v>
       </c>
       <c r="J534" s="115" t="s">
-        <v>210</v>
+        <v>371</v>
       </c>
     </row>
     <row r="535" spans="1:10">
       <c r="A535" s="115" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="B535" s="115">
         <v>1</v>
@@ -21011,7 +21213,7 @@
         <v>12</v>
       </c>
       <c r="D535" s="115" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="E535" s="116">
         <v>46336</v>
@@ -21023,16 +21225,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H535" s="115" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="I535" s="115" t="s">
         <v>210</v>
       </c>
-      <c r="J535" s="115"/>
+      <c r="J535" s="115" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="536" spans="1:10">
       <c r="A536" s="115" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="B536" s="115">
         <v>1</v>
@@ -21041,7 +21245,7 @@
         <v>12</v>
       </c>
       <c r="D536" s="115" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="E536" s="116">
         <v>46336</v>
@@ -21053,18 +21257,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H536" s="115" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="I536" s="115" t="s">
-        <v>210</v>
+        <v>441</v>
       </c>
       <c r="J536" s="115" t="s">
-        <v>210</v>
+        <v>446</v>
       </c>
     </row>
     <row r="537" spans="1:10">
       <c r="A537" s="115" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="B537" s="115">
         <v>1</v>
@@ -21073,7 +21277,7 @@
         <v>12</v>
       </c>
       <c r="D537" s="115" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="E537" s="116">
         <v>46336</v>
@@ -21085,16 +21289,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H537" s="115" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I537" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J537" s="115"/>
+        <v>252</v>
+      </c>
+      <c r="J537" s="115" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="538" spans="1:10">
       <c r="A538" s="115" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="B538" s="115">
         <v>1</v>
@@ -21103,7 +21309,7 @@
         <v>12</v>
       </c>
       <c r="D538" s="115" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="E538" s="116">
         <v>46336</v>
@@ -21115,18 +21321,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H538" s="115" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I538" s="115" t="s">
-        <v>210</v>
+        <v>450</v>
       </c>
       <c r="J538" s="115" t="s">
-        <v>210</v>
+        <v>425</v>
       </c>
     </row>
     <row r="539" spans="1:10">
       <c r="A539" s="115" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="B539" s="115">
         <v>1</v>
@@ -21135,7 +21341,7 @@
         <v>12</v>
       </c>
       <c r="D539" s="115" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="E539" s="116">
         <v>46337</v>
@@ -21147,16 +21353,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H539" s="115" t="s">
-        <v>401</v>
-      </c>
-      <c r="I539" s="115" t="s">
-        <v>210</v>
+        <v>432</v>
+      </c>
+      <c r="I539" s="154" t="s">
+        <v>291</v>
       </c>
       <c r="J539" s="115"/>
     </row>
     <row r="540" spans="1:10">
       <c r="A540" s="115" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="B540" s="115">
         <v>1</v>
@@ -21165,7 +21371,7 @@
         <v>12</v>
       </c>
       <c r="D540" s="115" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E540" s="116">
         <v>46337</v>
@@ -21177,18 +21383,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H540" s="115" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I540" s="115" t="s">
-        <v>210</v>
+        <v>454</v>
       </c>
       <c r="J540" s="115" t="s">
-        <v>210</v>
+        <v>455</v>
       </c>
     </row>
     <row r="541" spans="1:10">
       <c r="A541" s="115" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="B541" s="115">
         <v>1</v>
@@ -21197,7 +21403,7 @@
         <v>12</v>
       </c>
       <c r="D541" s="115" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E541" s="116">
         <v>46337</v>
@@ -21209,14 +21415,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H541" s="115" t="s">
-        <v>408</v>
-      </c>
-      <c r="I541" s="115"/>
-      <c r="J541" s="115"/>
+        <v>425</v>
+      </c>
+      <c r="I541" s="115" t="s">
+        <v>454</v>
+      </c>
+      <c r="J541" s="115" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="542" spans="1:10">
       <c r="A542" s="115" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="B542" s="115">
         <v>1</v>
@@ -21225,7 +21435,7 @@
         <v>12</v>
       </c>
       <c r="D542" s="115" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="E542" s="116">
         <v>46337</v>
@@ -21237,16 +21447,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H542" s="115" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="I542" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J542" s="115"/>
+        <v>252</v>
+      </c>
+      <c r="J542" s="115" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="543" spans="1:10">
       <c r="A543" s="115" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="B543" s="115">
         <v>1</v>
@@ -21255,7 +21467,7 @@
         <v>12</v>
       </c>
       <c r="D543" s="115" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="E543" s="116">
         <v>46337</v>
@@ -21267,18 +21479,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H543" s="115" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="I543" s="115" t="s">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="J543" s="115" t="s">
-        <v>210</v>
+        <v>455</v>
       </c>
     </row>
     <row r="544" spans="1:10">
       <c r="A544" s="115" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="B544" s="115">
         <v>1</v>
@@ -21287,7 +21499,7 @@
         <v>12</v>
       </c>
       <c r="D544" s="115" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E544" s="116">
         <v>46337</v>
@@ -21299,18 +21511,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H544" s="115" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="I544" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J544" s="115" t="s">
-        <v>210</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:10">
       <c r="A545" s="115" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="B545" s="115">
         <v>1</v>
@@ -21319,7 +21531,7 @@
         <v>12</v>
       </c>
       <c r="D545" s="115" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="E545" s="116">
         <v>46337</v>
@@ -21331,18 +21543,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H545" s="115" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="I545" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J545" s="115" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="546" spans="1:10">
       <c r="A546" s="115" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="B546" s="115">
         <v>1</v>
@@ -21351,7 +21563,7 @@
         <v>12</v>
       </c>
       <c r="D546" s="115" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="E546" s="116">
         <v>46337</v>
@@ -21363,18 +21575,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H546" s="115" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="I546" s="115" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J546" s="115" t="s">
-        <v>210</v>
+        <v>454</v>
       </c>
     </row>
     <row r="547" spans="1:10">
       <c r="A547" s="115" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="B547" s="115">
         <v>1</v>
@@ -21383,7 +21595,7 @@
         <v>12</v>
       </c>
       <c r="D547" s="115" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="E547" s="116">
         <v>46338</v>
@@ -21395,16 +21607,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H547" s="115" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="I547" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J547" s="115"/>
     </row>
     <row r="548" spans="1:10">
       <c r="A548" s="115" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="B548" s="115">
         <v>1</v>
@@ -21413,7 +21625,7 @@
         <v>12</v>
       </c>
       <c r="D548" s="115" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E548" s="116">
         <v>46338</v>
@@ -21425,18 +21637,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H548" s="115" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="I548" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J548" s="115" t="s">
-        <v>210</v>
+        <v>362</v>
       </c>
     </row>
     <row r="549" spans="1:10">
       <c r="A549" s="115" t="s">
-        <v>426</v>
+        <v>461</v>
       </c>
       <c r="B549" s="115">
         <v>1</v>
@@ -21445,7 +21657,7 @@
         <v>12</v>
       </c>
       <c r="D549" s="115" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E549" s="116">
         <v>46338</v>
@@ -21457,16 +21669,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H549" s="115" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I549" s="115" t="s">
-        <v>210</v>
-      </c>
-      <c r="J549" s="115"/>
+        <v>346</v>
+      </c>
+      <c r="J549" s="115" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="550" spans="1:10">
       <c r="A550" s="115" t="s">
-        <v>426</v>
+        <v>461</v>
       </c>
       <c r="B550" s="115">
         <v>1</v>
@@ -21475,7 +21689,7 @@
         <v>12</v>
       </c>
       <c r="D550" s="115" t="s">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="E550" s="116">
         <v>46338</v>
@@ -21487,18 +21701,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H550" s="115" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I550" s="115" t="s">
-        <v>210</v>
+        <v>296</v>
       </c>
       <c r="J550" s="115" t="s">
-        <v>210</v>
+        <v>371</v>
       </c>
     </row>
     <row r="551" spans="1:10">
       <c r="A551" s="115" t="s">
-        <v>428</v>
+        <v>463</v>
       </c>
       <c r="B551" s="115">
         <v>1</v>
@@ -21507,7 +21721,7 @@
         <v>12</v>
       </c>
       <c r="D551" s="115" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E551" s="116">
         <v>46338</v>
@@ -21519,18 +21733,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H551" s="115" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="I551" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J551" s="115" t="s">
-        <v>210</v>
+        <v>287</v>
       </c>
     </row>
     <row r="552" spans="1:10">
       <c r="A552" s="115" t="s">
-        <v>428</v>
+        <v>463</v>
       </c>
       <c r="B552" s="115">
         <v>2</v>
@@ -21539,7 +21753,7 @@
         <v>12</v>
       </c>
       <c r="D552" s="115" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E552" s="116">
         <v>46338</v>
@@ -21551,18 +21765,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H552" s="115" t="s">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="I552" s="115" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="J552" s="115" t="s">
-        <v>210</v>
+        <v>296</v>
       </c>
     </row>
     <row r="553" spans="1:10">
       <c r="A553" s="115" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="B553" s="115">
         <v>1</v>
@@ -21571,7 +21785,7 @@
         <v>12</v>
       </c>
       <c r="D553" s="115" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="E553" s="116">
         <v>46338</v>
@@ -21583,16 +21797,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H553" s="115" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I553" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J553" s="115"/>
+        <v>252</v>
+      </c>
+      <c r="J553" s="115" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="554" spans="1:10">
       <c r="A554" s="115" t="s">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="B554" s="115">
         <v>1</v>
@@ -21601,7 +21817,7 @@
         <v>12</v>
       </c>
       <c r="D554" s="115" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="E554" s="116">
         <v>46338</v>
@@ -21613,18 +21829,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H554" s="115" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I554" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J554" s="115" t="s">
-        <v>210</v>
+        <v>425</v>
       </c>
     </row>
     <row r="555" spans="1:10">
       <c r="A555" s="115" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="B555" s="115">
         <v>1</v>
@@ -21633,7 +21849,7 @@
         <v>12</v>
       </c>
       <c r="D555" s="115" t="s">
-        <v>435</v>
+        <v>470</v>
       </c>
       <c r="E555" s="116">
         <v>46339</v>
@@ -21645,16 +21861,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H555" s="115" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="I555" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J555" s="115"/>
+        <v>291</v>
+      </c>
+      <c r="J555" s="115" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="556" spans="1:10">
       <c r="A556" s="115" t="s">
-        <v>434</v>
+        <v>469</v>
       </c>
       <c r="B556" s="115">
         <v>1</v>
@@ -21663,7 +21881,7 @@
         <v>12</v>
       </c>
       <c r="D556" s="115" t="s">
-        <v>437</v>
+        <v>472</v>
       </c>
       <c r="E556" s="116">
         <v>46339</v>
@@ -21675,18 +21893,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H556" s="115" t="s">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="I556" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J556" s="115" t="s">
-        <v>210</v>
+        <v>291</v>
       </c>
     </row>
     <row r="557" spans="1:10">
       <c r="A557" s="115" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="B557" s="115">
         <v>1</v>
@@ -21695,7 +21913,7 @@
         <v>12</v>
       </c>
       <c r="D557" s="115" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E557" s="116">
         <v>46336</v>
@@ -21707,16 +21925,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H557" s="131" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I557" s="115" t="s">
-        <v>210</v>
-      </c>
-      <c r="J557" s="115"/>
+        <v>409</v>
+      </c>
+      <c r="J557" s="115" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="558" spans="1:10">
       <c r="A558" s="115" t="s">
-        <v>438</v>
+        <v>473</v>
       </c>
       <c r="B558" s="115">
         <v>1</v>
@@ -21725,7 +21945,7 @@
         <v>12</v>
       </c>
       <c r="D558" s="115" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="E558" s="116">
         <v>46336</v>
@@ -21737,10 +21957,10 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H558" s="131" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I558" s="115" t="s">
-        <v>210</v>
+        <v>425</v>
       </c>
       <c r="J558" s="115" t="s">
         <v>210</v>
@@ -21748,7 +21968,7 @@
     </row>
     <row r="559" spans="1:10">
       <c r="A559" s="115" t="s">
-        <v>439</v>
+        <v>474</v>
       </c>
       <c r="B559" s="115">
         <v>1</v>
@@ -21757,7 +21977,7 @@
         <v>12</v>
       </c>
       <c r="D559" s="115" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E559" s="116">
         <v>46335</v>
@@ -21769,18 +21989,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H559" s="115" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="I559" s="115" t="s">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="J559" s="115" t="s">
-        <v>441</v>
+        <v>223</v>
       </c>
     </row>
     <row r="560" spans="1:10">
       <c r="A560" s="115" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="B560" s="115">
         <v>1</v>
@@ -21801,16 +22021,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H560" s="115" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I560" s="115" t="s">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="J560" s="115"/>
     </row>
-    <row r="561" spans="1:10">
+    <row r="561" spans="1:10" ht="15">
       <c r="A561" s="115" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="B561" s="115">
         <v>1</v>
@@ -21819,7 +22039,7 @@
         <v>12</v>
       </c>
       <c r="D561" s="115" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E561" s="116">
         <v>46336</v>
@@ -21831,16 +22051,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H561" s="115" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="I561" s="115" t="s">
-        <v>231</v>
-      </c>
-      <c r="J561" s="115"/>
+        <v>252</v>
+      </c>
+      <c r="J561" s="130" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="562" spans="1:10">
       <c r="A562" s="115" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="B562" s="115">
         <v>1</v>
@@ -21849,7 +22071,7 @@
         <v>12</v>
       </c>
       <c r="D562" s="115" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E562" s="116">
         <v>46336</v>
@@ -21861,18 +22083,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H562" s="115" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="I562" s="115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J562" s="115" t="s">
-        <v>210</v>
+        <v>291</v>
       </c>
     </row>
     <row r="563" spans="1:10">
       <c r="A563" s="115" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="B563" s="115">
         <v>1</v>
@@ -21881,7 +22103,7 @@
         <v>12</v>
       </c>
       <c r="D563" s="115" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E563" s="116">
         <v>46336</v>
@@ -21893,16 +22115,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H563" s="115" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="I563" s="115" t="s">
-        <v>210</v>
+        <v>291</v>
       </c>
       <c r="J563" s="115"/>
     </row>
     <row r="564" spans="1:10">
       <c r="A564" s="115" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="B564" s="115">
         <v>1</v>
@@ -21911,7 +22133,7 @@
         <v>12</v>
       </c>
       <c r="D564" s="115" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E564" s="116">
         <v>46337</v>
@@ -21923,16 +22145,16 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H564" s="115" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="I564" s="115" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="J564" s="115"/>
     </row>
     <row r="565" spans="1:10">
       <c r="A565" s="115" t="s">
-        <v>447</v>
+        <v>481</v>
       </c>
       <c r="B565" s="115">
         <v>1</v>
@@ -21941,7 +22163,7 @@
         <v>12</v>
       </c>
       <c r="D565" s="115" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E565" s="116">
         <v>46337</v>
@@ -21953,16 +22175,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H565" s="115" t="s">
-        <v>448</v>
+        <v>210</v>
       </c>
       <c r="I565" s="115" t="s">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="J565" s="115"/>
     </row>
     <row r="566" spans="1:10">
       <c r="A566" s="115" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="B566" s="115">
         <v>1</v>
@@ -21971,7 +22193,7 @@
         <v>12</v>
       </c>
       <c r="D566" s="115" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E566" s="116">
         <v>46338</v>
@@ -21983,16 +22205,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H566" s="115" t="s">
-        <v>448</v>
+        <v>210</v>
       </c>
       <c r="I566" s="115" t="s">
-        <v>450</v>
-      </c>
-      <c r="J566" s="115"/>
+        <v>483</v>
+      </c>
+      <c r="J566" s="115" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="567" spans="1:10">
       <c r="A567" s="115" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="B567" s="115">
         <v>1</v>
@@ -22001,7 +22225,7 @@
         <v>12</v>
       </c>
       <c r="D567" s="115" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="E567" s="116">
         <v>46338</v>
@@ -22013,16 +22237,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H567" s="115" t="s">
-        <v>448</v>
+        <v>210</v>
       </c>
       <c r="I567" s="115" t="s">
-        <v>210</v>
-      </c>
-      <c r="J567" s="115"/>
+        <v>483</v>
+      </c>
+      <c r="J567" s="115" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="568" spans="1:10">
       <c r="A568" s="115" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="B568" s="115">
         <v>1</v>
@@ -22043,18 +22269,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H568" s="132" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I568" s="115" t="s">
-        <v>210</v>
-      </c>
-      <c r="J568" s="115" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="569" spans="1:10">
+        <v>331</v>
+      </c>
+      <c r="J568" s="154" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="569" spans="1:10" ht="15">
       <c r="A569" s="115" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="B569" s="115">
         <v>1</v>
@@ -22063,7 +22289,7 @@
         <v>12</v>
       </c>
       <c r="D569" s="115" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E569" s="116">
         <v>46339</v>
@@ -22075,18 +22301,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H569" s="132" t="s">
-        <v>229</v>
-      </c>
-      <c r="I569" s="115" t="s">
-        <v>210</v>
+        <v>217</v>
+      </c>
+      <c r="I569" s="130" t="s">
+        <v>485</v>
       </c>
       <c r="J569" s="115" t="s">
-        <v>210</v>
+        <v>296</v>
       </c>
     </row>
     <row r="570" spans="1:10">
       <c r="A570" s="115" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="B570" s="115">
         <v>1</v>
@@ -22095,7 +22321,7 @@
         <v>12</v>
       </c>
       <c r="D570" s="115" t="s">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="E570" s="116">
         <v>46339</v>
@@ -22107,16 +22333,16 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H570" s="115" t="s">
-        <v>423</v>
+        <v>296</v>
       </c>
       <c r="I570" s="115" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="J570" s="115"/>
     </row>
     <row r="571" spans="1:10">
       <c r="A571" s="146" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="B571" s="146">
         <v>1</v>
@@ -22125,7 +22351,7 @@
         <v>12</v>
       </c>
       <c r="D571" s="146" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E571" s="148">
         <v>46337</v>
@@ -22137,18 +22363,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H571" s="146" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I571" s="146" t="s">
-        <v>210</v>
+        <v>454</v>
       </c>
       <c r="J571" s="146" t="s">
-        <v>210</v>
+        <v>455</v>
       </c>
     </row>
     <row r="572" spans="1:10">
       <c r="A572" s="146" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="B572" s="146">
         <v>1</v>
@@ -22157,7 +22383,7 @@
         <v>12</v>
       </c>
       <c r="D572" s="146" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="E572" s="148">
         <v>46335</v>
@@ -22169,18 +22395,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H572" s="146" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="I572" s="146" t="s">
         <v>54</v>
       </c>
       <c r="J572" s="146" t="s">
-        <v>210</v>
+        <v>445</v>
       </c>
     </row>
     <row r="573" spans="1:10">
       <c r="A573" s="146" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="B573" s="146">
         <v>1</v>
@@ -22189,7 +22415,7 @@
         <v>12</v>
       </c>
       <c r="D573" s="146" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="E573" s="148">
         <v>46335</v>
@@ -22201,7 +22427,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H573" s="146" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="I573" s="146" t="s">
         <v>30</v>
@@ -22210,7 +22436,7 @@
     </row>
     <row r="574" spans="1:10">
       <c r="A574" s="146" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="B574" s="146">
         <v>1</v>
@@ -22231,16 +22457,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H574" s="146" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I574" s="146" t="s">
-        <v>210</v>
-      </c>
-      <c r="J574" s="146"/>
-    </row>
-    <row r="575" spans="1:10">
+        <v>348</v>
+      </c>
+      <c r="J574" s="146" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="575" spans="1:10" ht="15">
       <c r="A575" s="146" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="B575" s="146">
         <v>1</v>
@@ -22249,7 +22477,7 @@
         <v>12</v>
       </c>
       <c r="D575" s="146" t="s">
-        <v>459</v>
+        <v>494</v>
       </c>
       <c r="E575" s="148">
         <v>46339</v>
@@ -22261,18 +22489,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H575" s="146" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I575" s="146" t="s">
-        <v>210</v>
-      </c>
-      <c r="J575" s="146" t="s">
-        <v>210</v>
+        <v>495</v>
+      </c>
+      <c r="J575" s="164" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="576" spans="1:10">
       <c r="A576" s="146" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="B576" s="146">
         <v>1</v>
@@ -22293,10 +22521,10 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H576" s="146" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I576" s="146" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="J576" s="147"/>
     </row>
@@ -22308,7 +22536,7 @@
     </row>
     <row r="578" spans="1:10">
       <c r="A578" s="119" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="B578" s="119"/>
       <c r="C578" s="119"/>
@@ -22321,16 +22549,16 @@
     </row>
     <row r="579" spans="1:10">
       <c r="A579" s="119" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="B579" s="119">
         <v>1</v>
       </c>
       <c r="C579" s="119" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D579" s="119" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="E579" s="120">
         <v>46335</v>
@@ -22342,7 +22570,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H579" s="119" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="I579" s="119" t="s">
         <v>206</v>
@@ -22350,16 +22578,16 @@
     </row>
     <row r="580" spans="1:10">
       <c r="A580" s="119" t="s">
-        <v>465</v>
+        <v>501</v>
       </c>
       <c r="B580" s="119">
         <v>1</v>
       </c>
       <c r="C580" s="119" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D580" s="119" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="E580" s="120">
         <v>46336</v>
@@ -22379,16 +22607,16 @@
     </row>
     <row r="581" spans="1:10">
       <c r="A581" s="119" t="s">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="B581" s="119">
         <v>1</v>
       </c>
       <c r="C581" s="119" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D581" s="119" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="E581" s="120">
         <v>46337</v>
@@ -22400,7 +22628,7 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="H581" s="119" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I581" s="119" t="s">
         <v>206</v>
@@ -22408,16 +22636,16 @@
     </row>
     <row r="582" spans="1:10">
       <c r="A582" s="119" t="s">
-        <v>467</v>
+        <v>503</v>
       </c>
       <c r="B582" s="119">
         <v>1</v>
       </c>
       <c r="C582" s="119" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D582" s="119" t="s">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="E582" s="120">
         <v>46338</v>
@@ -22429,24 +22657,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H582" s="119" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="I582" s="119" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="583" spans="1:10">
+    <row r="583" spans="1:10" ht="15">
       <c r="A583" s="122" t="s">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="B583" s="122">
         <v>1</v>
       </c>
       <c r="C583" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D583" s="122" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="E583" s="123">
         <v>46335</v>
@@ -22458,22 +22686,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H583" s="122" t="s">
-        <v>457</v>
-      </c>
-      <c r="I583" s="122"/>
-    </row>
-    <row r="584" spans="1:10">
+        <v>491</v>
+      </c>
+      <c r="I583" s="160" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="584" spans="1:10" ht="15">
       <c r="A584" s="122" t="s">
-        <v>469</v>
+        <v>505</v>
       </c>
       <c r="B584" s="122">
         <v>1</v>
       </c>
       <c r="C584" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D584" s="122" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E584" s="123">
         <v>46335</v>
@@ -22485,22 +22715,22 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H584" s="122" t="s">
-        <v>470</v>
-      </c>
-      <c r="I584" s="122"/>
-    </row>
-    <row r="585" spans="1:10">
+        <v>506</v>
+      </c>
+      <c r="I584" s="161"/>
+    </row>
+    <row r="585" spans="1:10" ht="15">
       <c r="A585" s="122" t="s">
-        <v>471</v>
+        <v>507</v>
       </c>
       <c r="B585" s="122">
         <v>1</v>
       </c>
       <c r="C585" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D585" s="122" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="E585" s="123">
         <v>46336</v>
@@ -22512,19 +22742,19 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H585" s="122" t="s">
-        <v>472</v>
-      </c>
-      <c r="I585" s="122"/>
-    </row>
-    <row r="586" spans="1:10">
+        <v>508</v>
+      </c>
+      <c r="I585" s="161"/>
+    </row>
+    <row r="586" spans="1:10" ht="15">
       <c r="A586" s="122" t="s">
-        <v>473</v>
+        <v>509</v>
       </c>
       <c r="B586" s="122">
         <v>1</v>
       </c>
       <c r="C586" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D586" s="122" t="s">
         <v>13</v>
@@ -22539,22 +22769,22 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H586" s="122" t="s">
-        <v>474</v>
-      </c>
-      <c r="I586" s="122"/>
-    </row>
-    <row r="587" spans="1:10">
+        <v>510</v>
+      </c>
+      <c r="I586" s="161"/>
+    </row>
+    <row r="587" spans="1:10" ht="15">
       <c r="A587" s="125" t="s">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="B587" s="125">
         <v>1</v>
       </c>
       <c r="C587" s="125" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D587" s="125" t="s">
-        <v>476</v>
+        <v>512</v>
       </c>
       <c r="E587" s="126">
         <v>46338</v>
@@ -22566,22 +22796,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H587" s="125" t="s">
-        <v>423</v>
-      </c>
-      <c r="I587" s="125"/>
-    </row>
-    <row r="588" spans="1:10">
+        <v>296</v>
+      </c>
+      <c r="I587" s="160" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="588" spans="1:10" ht="15">
       <c r="A588" s="122" t="s">
-        <v>477</v>
+        <v>513</v>
       </c>
       <c r="B588" s="122">
         <v>1</v>
       </c>
       <c r="C588" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D588" s="122" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E588" s="123">
         <v>46339</v>
@@ -22593,22 +22825,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H588" s="122" t="s">
-        <v>478</v>
-      </c>
-      <c r="I588" s="122"/>
-    </row>
-    <row r="589" spans="1:10">
+        <v>514</v>
+      </c>
+      <c r="I588" s="161" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="589" spans="1:10" ht="15">
       <c r="A589" s="122" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="B589" s="122">
         <v>1</v>
       </c>
       <c r="C589" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D589" s="122" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E589" s="123">
         <v>46339</v>
@@ -22620,22 +22854,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H589" s="122" t="s">
-        <v>478</v>
-      </c>
-      <c r="I589" s="122"/>
-    </row>
-    <row r="590" spans="1:10">
+        <v>514</v>
+      </c>
+      <c r="I589" s="161" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="590" spans="1:10" ht="15">
       <c r="A590" s="122" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="B590" s="122">
         <v>1</v>
       </c>
       <c r="C590" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D590" s="122" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E590" s="123">
         <v>46339</v>
@@ -22647,22 +22883,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H590" s="122" t="s">
-        <v>478</v>
-      </c>
-      <c r="I590" s="122"/>
-    </row>
-    <row r="591" spans="1:10">
+        <v>514</v>
+      </c>
+      <c r="I590" s="161" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="591" spans="1:10" ht="15">
       <c r="A591" s="122" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="B591" s="122">
         <v>1</v>
       </c>
       <c r="C591" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D591" s="122" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E591" s="123">
         <v>46335</v>
@@ -22674,22 +22912,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H591" s="122" t="s">
-        <v>397</v>
-      </c>
-      <c r="I591" s="122"/>
-    </row>
-    <row r="592" spans="1:10">
+        <v>428</v>
+      </c>
+      <c r="I591" s="161" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="592" spans="1:10" ht="15">
       <c r="A592" s="122" t="s">
-        <v>482</v>
+        <v>520</v>
       </c>
       <c r="B592" s="122">
         <v>1</v>
       </c>
       <c r="C592" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D592" s="122" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="E592" s="123">
         <v>46336</v>
@@ -22701,22 +22941,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H592" s="122" t="s">
-        <v>457</v>
-      </c>
-      <c r="I592" s="122"/>
-    </row>
-    <row r="593" spans="1:9">
+        <v>491</v>
+      </c>
+      <c r="I592" s="160" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="593" spans="1:9" ht="15">
       <c r="A593" s="122" t="s">
-        <v>483</v>
+        <v>521</v>
       </c>
       <c r="B593" s="122">
         <v>1</v>
       </c>
       <c r="C593" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D593" s="122" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E593" s="123">
         <v>46337</v>
@@ -22728,22 +22970,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H593" s="122" t="s">
-        <v>484</v>
-      </c>
-      <c r="I593" s="122"/>
-    </row>
-    <row r="594" spans="1:9">
+        <v>522</v>
+      </c>
+      <c r="I593" s="160" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="594" spans="1:9" ht="15">
       <c r="A594" s="122" t="s">
-        <v>485</v>
+        <v>523</v>
       </c>
       <c r="B594" s="122">
         <v>1</v>
       </c>
       <c r="C594" s="122" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D594" s="122" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="E594" s="123">
         <v>46338</v>
@@ -22755,22 +22999,24 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H594" s="122" t="s">
+        <v>508</v>
+      </c>
+      <c r="I594" s="161" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="595" spans="1:9" ht="15">
+      <c r="A595" s="122" t="s">
+        <v>524</v>
+      </c>
+      <c r="B595" s="122">
+        <v>1</v>
+      </c>
+      <c r="C595" s="122" t="s">
+        <v>12</v>
+      </c>
+      <c r="D595" s="122" t="s">
         <v>472</v>
-      </c>
-      <c r="I594" s="122"/>
-    </row>
-    <row r="595" spans="1:9">
-      <c r="A595" s="122" t="s">
-        <v>486</v>
-      </c>
-      <c r="B595" s="122">
-        <v>1</v>
-      </c>
-      <c r="C595" s="122" t="s">
-        <v>12</v>
-      </c>
-      <c r="D595" s="122" t="s">
-        <v>437</v>
       </c>
       <c r="E595" s="123">
         <v>46339</v>
@@ -22782,13 +23028,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H595" s="122" t="s">
-        <v>404</v>
-      </c>
-      <c r="I595" s="122"/>
-    </row>
-    <row r="596" spans="1:9">
+        <v>435</v>
+      </c>
+      <c r="I595" s="160" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" ht="15">
       <c r="A596" s="122" t="s">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="B596" s="122">
         <v>1</v>
@@ -22797,7 +23045,7 @@
         <v>12</v>
       </c>
       <c r="D596" s="122" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="E596" s="123">
         <v>46339</v>
@@ -22809,13 +23057,13 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H596" s="122" t="s">
-        <v>404</v>
-      </c>
-      <c r="I596" s="122"/>
-    </row>
-    <row r="597" spans="1:9">
+        <v>435</v>
+      </c>
+      <c r="I596" s="161"/>
+    </row>
+    <row r="597" spans="1:9" ht="15">
       <c r="A597" s="122" t="s">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="B597" s="122">
         <v>1</v>
@@ -22824,7 +23072,7 @@
         <v>12</v>
       </c>
       <c r="D597" s="122" t="s">
-        <v>437</v>
+        <v>472</v>
       </c>
       <c r="E597" s="123">
         <v>46339</v>
@@ -22836,13 +23084,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H597" s="122" t="s">
-        <v>404</v>
-      </c>
-      <c r="I597" s="122"/>
-    </row>
-    <row r="598" spans="1:9">
+        <v>435</v>
+      </c>
+      <c r="I597" s="160" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="598" spans="1:9" ht="15">
       <c r="A598" s="125" t="s">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="B598" s="125">
         <v>1</v>
@@ -22851,7 +23101,7 @@
         <v>12</v>
       </c>
       <c r="D598" s="125" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="E598" s="126">
         <v>46339</v>
@@ -22863,13 +23113,13 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H598" s="125" t="s">
-        <v>404</v>
-      </c>
-      <c r="I598" s="125"/>
-    </row>
-    <row r="599" spans="1:9">
+        <v>435</v>
+      </c>
+      <c r="I598" s="162"/>
+    </row>
+    <row r="599" spans="1:9" ht="15">
       <c r="A599" s="122" t="s">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="B599" s="125">
         <v>1</v>
@@ -22878,7 +23128,7 @@
         <v>12</v>
       </c>
       <c r="D599" s="122" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="E599" s="123">
         <v>46336</v>
@@ -22890,13 +23140,13 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="H599" s="122" t="s">
-        <v>340</v>
-      </c>
-      <c r="I599" s="122"/>
-    </row>
-    <row r="600" spans="1:9">
+        <v>375</v>
+      </c>
+      <c r="I599" s="161"/>
+    </row>
+    <row r="600" spans="1:9" ht="15">
       <c r="A600" s="122" t="s">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="B600" s="125">
         <v>1</v>
@@ -22905,7 +23155,7 @@
         <v>12</v>
       </c>
       <c r="D600" s="122" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E600" s="123">
         <v>46336</v>
@@ -22917,13 +23167,13 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H600" s="122" t="s">
-        <v>338</v>
-      </c>
-      <c r="I600" s="122"/>
-    </row>
-    <row r="601" spans="1:9">
+        <v>356</v>
+      </c>
+      <c r="I600" s="161"/>
+    </row>
+    <row r="601" spans="1:9" ht="15">
       <c r="A601" s="122" t="s">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="B601" s="125">
         <v>1</v>
@@ -22932,7 +23182,7 @@
         <v>12</v>
       </c>
       <c r="D601" s="122" t="s">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="E601" s="123">
         <v>46336</v>
@@ -22944,9 +23194,9 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="H601" s="122" t="s">
-        <v>492</v>
-      </c>
-      <c r="I601" s="122"/>
+        <v>530</v>
+      </c>
+      <c r="I601" s="161"/>
     </row>
     <row r="602" spans="1:9">
       <c r="A602" s="122"/>
@@ -22992,175 +23242,175 @@
     <row r="1" spans="1:38" ht="20.100000000000001">
       <c r="A1" s="28"/>
       <c r="B1" s="29"/>
-      <c r="C1" s="150" t="s">
-        <v>493</v>
-      </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="150" t="s">
-        <v>494</v>
-      </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="150" t="s">
-        <v>495</v>
-      </c>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
-      <c r="V1" s="151"/>
-      <c r="W1" s="151"/>
-      <c r="X1" s="150" t="s">
-        <v>496</v>
-      </c>
-      <c r="Y1" s="151"/>
-      <c r="Z1" s="151"/>
-      <c r="AA1" s="151"/>
-      <c r="AB1" s="151"/>
-      <c r="AC1" s="151"/>
-      <c r="AD1" s="151"/>
-      <c r="AE1" s="151"/>
-      <c r="AF1" s="150" t="s">
-        <v>497</v>
-      </c>
-      <c r="AG1" s="151"/>
-      <c r="AH1" s="151"/>
-      <c r="AI1" s="151"/>
-      <c r="AJ1" s="151"/>
+      <c r="C1" s="157" t="s">
+        <v>531</v>
+      </c>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="157" t="s">
+        <v>532</v>
+      </c>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="157" t="s">
+        <v>533</v>
+      </c>
+      <c r="R1" s="158"/>
+      <c r="S1" s="158"/>
+      <c r="T1" s="158"/>
+      <c r="U1" s="158"/>
+      <c r="V1" s="158"/>
+      <c r="W1" s="158"/>
+      <c r="X1" s="157" t="s">
+        <v>534</v>
+      </c>
+      <c r="Y1" s="158"/>
+      <c r="Z1" s="158"/>
+      <c r="AA1" s="158"/>
+      <c r="AB1" s="158"/>
+      <c r="AC1" s="158"/>
+      <c r="AD1" s="158"/>
+      <c r="AE1" s="158"/>
+      <c r="AF1" s="157" t="s">
+        <v>535</v>
+      </c>
+      <c r="AG1" s="158"/>
+      <c r="AH1" s="158"/>
+      <c r="AI1" s="158"/>
+      <c r="AJ1" s="158"/>
       <c r="AK1" s="30"/>
       <c r="AL1" s="30"/>
     </row>
     <row r="2" spans="1:38" ht="20.100000000000001">
       <c r="A2" s="31" t="s">
-        <v>498</v>
+        <v>536</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="H2" s="35" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="J2" s="33" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="N2" s="34" t="s">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="O2" s="34" t="s">
-        <v>512</v>
+        <v>550</v>
       </c>
       <c r="P2" s="34" t="s">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="Q2" s="33" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="R2" s="33" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="S2" s="33" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="T2" s="34" t="s">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="U2" s="34" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="V2" s="34" t="s">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="W2" s="34" t="s">
-        <v>512</v>
+        <v>550</v>
       </c>
       <c r="X2" s="33" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="Y2" s="33" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="Z2" s="33" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="AA2" s="34" t="s">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="AB2" s="34" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="AC2" s="34" t="s">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="AD2" s="34" t="s">
-        <v>512</v>
+        <v>550</v>
       </c>
       <c r="AE2" s="35" t="s">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="AF2" s="33" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="AG2" s="34" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="AH2" s="36" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AI2" s="34" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="AJ2" s="35" t="s">
-        <v>515</v>
+        <v>553</v>
       </c>
       <c r="AK2" s="37" t="s">
-        <v>516</v>
+        <v>554</v>
       </c>
       <c r="AL2" s="35" t="s">
-        <v>517</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:38" ht="109.5" customHeight="1">
       <c r="A3" s="38" t="s">
-        <v>518</v>
+        <v>556</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="41"/>
@@ -23170,58 +23420,58 @@
       <c r="H3" s="43"/>
       <c r="I3" s="40"/>
       <c r="J3" s="44" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="K3" s="45" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="L3" s="45" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="M3" s="45" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="N3" s="45" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="O3" s="45" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="P3" s="46" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="Q3" s="47" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="R3" s="48" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="S3" s="48" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="T3" s="48" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="U3" s="42"/>
       <c r="V3" s="42"/>
       <c r="W3" s="49"/>
       <c r="X3" s="50" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="Y3" s="51" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="Z3" s="51" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="AA3" s="51" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AB3" s="51" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="AC3" s="51" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="AD3" s="49"/>
       <c r="AE3" s="52"/>
@@ -23235,7 +23485,7 @@
     </row>
     <row r="4" spans="1:38" ht="109.5" customHeight="1">
       <c r="A4" s="38" t="s">
-        <v>537</v>
+        <v>575</v>
       </c>
       <c r="B4" s="55">
         <v>30</v>
@@ -23248,58 +23498,58 @@
       <c r="H4" s="60"/>
       <c r="I4" s="56"/>
       <c r="J4" s="61" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="K4" s="62" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="L4" s="63" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="M4" s="63" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="N4" s="63" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="O4" s="63" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="P4" s="64" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="Q4" s="65" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="R4" s="66" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="T4" s="66" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="U4" s="58"/>
       <c r="V4" s="58"/>
       <c r="W4" s="67"/>
       <c r="X4" s="68" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="Y4" s="69" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="Z4" s="69" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="AA4" s="69" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AB4" s="69" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="AC4" s="69" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="AD4" s="67"/>
       <c r="AE4" s="70"/>
@@ -23313,7 +23563,7 @@
     </row>
     <row r="5" spans="1:38" ht="109.5" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>538</v>
+        <v>576</v>
       </c>
       <c r="B5" s="55">
         <v>50</v>
@@ -23326,58 +23576,58 @@
       <c r="H5" s="60"/>
       <c r="I5" s="56"/>
       <c r="J5" s="61" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="K5" s="62" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="L5" s="63" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="M5" s="63" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="N5" s="63" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="O5" s="63" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="P5" s="64" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="Q5" s="65" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="R5" s="76" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="S5" s="76" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="T5" s="76" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="U5" s="75"/>
       <c r="V5" s="75"/>
       <c r="W5" s="67"/>
       <c r="X5" s="68" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="Y5" s="77" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="Z5" s="77" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="AA5" s="77" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AB5" s="77" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="AC5" s="77" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="AD5" s="67"/>
       <c r="AE5" s="70"/>
@@ -23391,7 +23641,7 @@
     </row>
     <row r="6" spans="1:38" ht="109.5" customHeight="1">
       <c r="A6" s="79" t="s">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="B6" s="55">
         <v>50</v>
@@ -23404,58 +23654,58 @@
       <c r="H6" s="82"/>
       <c r="I6" s="80"/>
       <c r="J6" s="61" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="K6" s="62" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="L6" s="63" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="M6" s="63" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="N6" s="63" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="O6" s="63" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="P6" s="64" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="Q6" s="83" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="R6" s="76" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="S6" s="76" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="T6" s="76" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="U6" s="75"/>
       <c r="V6" s="75"/>
       <c r="W6" s="84"/>
       <c r="X6" s="85" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="Y6" s="77" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="Z6" s="77" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="AA6" s="77" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AB6" s="77" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="AC6" s="77" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="AD6" s="84"/>
       <c r="AE6" s="70"/>
@@ -23469,7 +23719,7 @@
     </row>
     <row r="7" spans="1:38" ht="109.5" customHeight="1">
       <c r="A7" s="79" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
       <c r="B7" s="55">
         <v>50</v>
@@ -23482,58 +23732,58 @@
       <c r="H7" s="82"/>
       <c r="I7" s="80"/>
       <c r="J7" s="61" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="K7" s="62" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="L7" s="63" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="M7" s="63" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="N7" s="63" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="O7" s="63" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="P7" s="64" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="Q7" s="83" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="R7" s="76" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="S7" s="76" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="T7" s="76" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="U7" s="75"/>
       <c r="V7" s="75"/>
       <c r="W7" s="84"/>
       <c r="X7" s="85" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="Y7" s="77" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="Z7" s="77" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="AA7" s="77" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AB7" s="77" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="AC7" s="77" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="AD7" s="84"/>
       <c r="AE7" s="70"/>
@@ -23547,7 +23797,7 @@
     </row>
     <row r="8" spans="1:38" ht="109.5" customHeight="1">
       <c r="A8" s="79" t="s">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="B8" s="55">
         <v>48</v>
@@ -23560,58 +23810,58 @@
       <c r="H8" s="82"/>
       <c r="I8" s="80"/>
       <c r="J8" s="61" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="K8" s="62" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="L8" s="63" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="M8" s="63" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="N8" s="63" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="O8" s="63" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="P8" s="64" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="Q8" s="83" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="R8" s="76" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="S8" s="76" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="T8" s="76" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="U8" s="75"/>
       <c r="V8" s="75"/>
       <c r="W8" s="84"/>
       <c r="X8" s="85" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="Y8" s="77" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="Z8" s="77" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="AA8" s="77" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AB8" s="77" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="AC8" s="77" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="AD8" s="84"/>
       <c r="AE8" s="70"/>
@@ -23625,7 +23875,7 @@
     </row>
     <row r="9" spans="1:38" ht="109.5" customHeight="1">
       <c r="A9" s="90" t="s">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="B9" s="91">
         <v>40</v>
@@ -23633,65 +23883,65 @@
       <c r="C9" s="92"/>
       <c r="D9" s="93"/>
       <c r="E9" s="94" t="s">
-        <v>543</v>
+        <v>581</v>
       </c>
       <c r="F9" s="95"/>
       <c r="G9" s="95"/>
       <c r="H9" s="96"/>
       <c r="I9" s="92"/>
       <c r="J9" s="97" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="K9" s="98" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="L9" s="99" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="M9" s="99" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="N9" s="99" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="O9" s="99" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="P9" s="100" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
       <c r="Q9" s="101" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="R9" s="102" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="S9" s="102" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="T9" s="102" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="U9" s="103"/>
       <c r="V9" s="103"/>
       <c r="W9" s="104"/>
       <c r="X9" s="105" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="Y9" s="106" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="Z9" s="106" t="s">
-        <v>544</v>
+        <v>582</v>
       </c>
       <c r="AA9" s="106" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="AB9" s="106" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="AC9" s="106" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
       <c r="AD9" s="104"/>
       <c r="AE9" s="107"/>
@@ -23716,17 +23966,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="46f9de43-f693-4abd-b3da-16a9446d5b24" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="123f497b-f32e-4e02-92f3-8b4fa7417143">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Belge" ma:contentTypeID="0x010100256068D72C9EFB48AF3F54B18B894F64" ma:contentTypeVersion="11" ma:contentTypeDescription="Yeni belge oluşturun." ma:contentTypeScope="" ma:versionID="031d77c6e7ce9fd8ad3730b16c288e5d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="123f497b-f32e-4e02-92f3-8b4fa7417143" xmlns:ns3="46f9de43-f693-4abd-b3da-16a9446d5b24" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71bdbe7e907a0810769a1636b68cfc86" ns2:_="" ns3:_="">
     <xsd:import namespace="123f497b-f32e-4e02-92f3-8b4fa7417143"/>
@@ -23921,6 +24160,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="46f9de43-f693-4abd-b3da-16a9446d5b24" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="123f497b-f32e-4e02-92f3-8b4fa7417143">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -23931,11 +24181,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1710214D-5748-497F-83BE-598C45444980}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C87A36E5-3CCC-40F7-B843-81D2CDEBAE6D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C87A36E5-3CCC-40F7-B843-81D2CDEBAE6D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1710214D-5748-497F-83BE-598C45444980}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/2026-2027-guz-vize.xlsx
+++ b/2026-2027-guz-vize.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80ADA89A-10B5-43DF-A671-19B401D1EDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C493007A-BD1B-4BD6-B5C0-027BD5AFD758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4048" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="581">
   <si>
     <t>Ders Kodu</t>
   </si>
@@ -744,6 +744,9 @@
     <t>POLS463</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Onur Yamaner</t>
+  </si>
+  <si>
     <t>MATH127</t>
   </si>
   <si>
@@ -879,9 +882,6 @@
     <t>ECON101</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Öğr. Üyesi Onur Yamaner </t>
-  </si>
-  <si>
     <t>Dr. Öğr. Dilara Karslıoğlu</t>
   </si>
   <si>
@@ -1059,9 +1059,6 @@
     <t>SOS133</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Onur Yamaner</t>
-  </si>
-  <si>
     <t>PSY303</t>
   </si>
   <si>
@@ -1392,9 +1389,6 @@
     <t>B-411</t>
   </si>
   <si>
-    <t>Doç. Dr. Hazal Pabucçular Kutlu</t>
-  </si>
-  <si>
     <t>CENG463</t>
   </si>
   <si>
@@ -1467,7 +1461,7 @@
     <t>BİL109</t>
   </si>
   <si>
-    <t>Arş. Gör. Mehmet Emir Erdem</t>
+    <t>MDBF</t>
   </si>
   <si>
     <t>YBS207</t>
@@ -1491,9 +1485,6 @@
     <t>BİL205</t>
   </si>
   <si>
-    <t>MDBF</t>
-  </si>
-  <si>
     <t>MAT107</t>
   </si>
   <si>
@@ -1561,6 +1552,9 @@
   </si>
   <si>
     <t>Dr. Öğr. Üyesi Engincan Yıldız</t>
+  </si>
+  <si>
+    <t>Büşra Bur Doğan</t>
   </si>
   <si>
     <t>İŞL576</t>
@@ -2481,7 +2475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2764,8 +2758,6 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="20" fontId="18" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2798,11 +2790,18 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7219,7 +7218,7 @@
       <c r="H117" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I117" s="155" t="s">
+      <c r="I117" s="153" t="s">
         <v>30</v>
       </c>
       <c r="J117" s="6" t="s">
@@ -17013,17 +17012,17 @@
       <c r="G400" s="135">
         <v>0.67708333333333337</v>
       </c>
-      <c r="H400" s="136" t="s">
+      <c r="H400" s="162" t="s">
         <v>229</v>
       </c>
-      <c r="I400" s="136" t="s">
-        <v>231</v>
-      </c>
-      <c r="J400" s="133"/>
+      <c r="I400" s="162" t="s">
+        <v>234</v>
+      </c>
+      <c r="J400" s="163"/>
     </row>
     <row r="401" spans="1:10">
       <c r="A401" s="133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B401" s="133">
         <v>1</v>
@@ -17043,19 +17042,19 @@
       <c r="G401" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H401" s="133" t="s">
+      <c r="H401" s="163" t="s">
         <v>217</v>
       </c>
-      <c r="I401" s="136" t="s">
+      <c r="I401" s="162" t="s">
         <v>206</v>
       </c>
-      <c r="J401" s="133" t="s">
-        <v>235</v>
+      <c r="J401" s="163" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="402" spans="1:10">
       <c r="A402" s="133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B402" s="133">
         <v>2</v>
@@ -17064,7 +17063,7 @@
         <v>12</v>
       </c>
       <c r="D402" s="133" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E402" s="134">
         <v>46339</v>
@@ -17075,19 +17074,19 @@
       <c r="G402" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H402" s="133" t="s">
+      <c r="H402" s="163" t="s">
         <v>217</v>
       </c>
-      <c r="I402" s="136" t="s">
-        <v>237</v>
-      </c>
-      <c r="J402" s="133" t="s">
+      <c r="I402" s="162" t="s">
+        <v>238</v>
+      </c>
+      <c r="J402" s="163" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="403" spans="1:10">
       <c r="A403" s="133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B403" s="133">
         <v>2</v>
@@ -17096,7 +17095,7 @@
         <v>12</v>
       </c>
       <c r="D403" s="133" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E403" s="134">
         <v>46339</v>
@@ -17107,19 +17106,19 @@
       <c r="G403" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H403" s="133" t="s">
+      <c r="H403" s="163" t="s">
         <v>217</v>
       </c>
-      <c r="I403" s="136" t="s">
-        <v>239</v>
-      </c>
-      <c r="J403" s="166" t="s">
+      <c r="I403" s="162" t="s">
         <v>240</v>
+      </c>
+      <c r="J403" s="163" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="404" spans="1:10">
       <c r="A404" s="133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B404" s="133">
         <v>2</v>
@@ -17128,7 +17127,7 @@
         <v>12</v>
       </c>
       <c r="D404" s="133" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E404" s="134">
         <v>46339</v>
@@ -17139,19 +17138,19 @@
       <c r="G404" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H404" s="133" t="s">
+      <c r="H404" s="163" t="s">
         <v>217</v>
       </c>
-      <c r="I404" s="136" t="s">
-        <v>242</v>
-      </c>
-      <c r="J404" s="133" t="s">
+      <c r="I404" s="162" t="s">
         <v>243</v>
+      </c>
+      <c r="J404" s="163" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="405" spans="1:10">
       <c r="A405" s="133" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B405" s="133">
         <v>1</v>
@@ -17171,17 +17170,17 @@
       <c r="G405" s="135">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H405" s="133" t="s">
+      <c r="H405" s="163" t="s">
         <v>205</v>
       </c>
-      <c r="I405" s="136" t="s">
+      <c r="I405" s="162" t="s">
         <v>206</v>
       </c>
-      <c r="J405" s="133"/>
+      <c r="J405" s="163"/>
     </row>
     <row r="406" spans="1:10">
       <c r="A406" s="133" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B406" s="133">
         <v>1</v>
@@ -17201,17 +17200,17 @@
       <c r="G406" s="135">
         <v>0.63541666666666663</v>
       </c>
-      <c r="H406" s="133" t="s">
-        <v>246</v>
-      </c>
-      <c r="I406" s="136" t="s">
+      <c r="H406" s="163" t="s">
+        <v>247</v>
+      </c>
+      <c r="I406" s="162" t="s">
         <v>206</v>
       </c>
-      <c r="J406" s="133"/>
+      <c r="J406" s="163"/>
     </row>
     <row r="407" spans="1:10">
       <c r="A407" s="133" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B407" s="133">
         <v>1</v>
@@ -17231,17 +17230,17 @@
       <c r="G407" s="135">
         <v>0.69791666666666663</v>
       </c>
-      <c r="H407" s="133" t="s">
-        <v>246</v>
-      </c>
-      <c r="I407" s="136" t="s">
+      <c r="H407" s="163" t="s">
+        <v>247</v>
+      </c>
+      <c r="I407" s="162" t="s">
         <v>206</v>
       </c>
-      <c r="J407" s="133"/>
+      <c r="J407" s="163"/>
     </row>
     <row r="408" spans="1:10">
       <c r="A408" s="137" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B408" s="137">
         <v>1</v>
@@ -17250,7 +17249,7 @@
         <v>12</v>
       </c>
       <c r="D408" s="137" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E408" s="138">
         <v>46335</v>
@@ -17261,19 +17260,19 @@
       <c r="G408" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H408" s="137" t="s">
-        <v>250</v>
-      </c>
-      <c r="I408" s="137" t="s">
+      <c r="H408" s="164" t="s">
+        <v>251</v>
+      </c>
+      <c r="I408" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J408" s="137" t="s">
-        <v>251</v>
+      <c r="J408" s="164" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="409" spans="1:10">
       <c r="A409" s="137" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B409" s="137">
         <v>1</v>
@@ -17293,19 +17292,19 @@
       <c r="G409" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H409" s="137" t="s">
-        <v>250</v>
-      </c>
-      <c r="I409" s="140" t="s">
-        <v>252</v>
-      </c>
-      <c r="J409" s="140" t="s">
-        <v>239</v>
+      <c r="H409" s="164" t="s">
+        <v>251</v>
+      </c>
+      <c r="I409" s="165" t="s">
+        <v>253</v>
+      </c>
+      <c r="J409" s="165" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="410" spans="1:10">
       <c r="A410" s="137" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B410" s="137">
         <v>1</v>
@@ -17314,7 +17313,7 @@
         <v>12</v>
       </c>
       <c r="D410" s="137" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E410" s="138">
         <v>46335</v>
@@ -17325,17 +17324,17 @@
       <c r="G410" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H410" s="137" t="s">
-        <v>250</v>
-      </c>
-      <c r="I410" s="137" t="s">
+      <c r="H410" s="164" t="s">
+        <v>251</v>
+      </c>
+      <c r="I410" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J410" s="137"/>
+      <c r="J410" s="164"/>
     </row>
     <row r="411" spans="1:10">
       <c r="A411" s="137" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B411" s="137">
         <v>1</v>
@@ -17344,7 +17343,7 @@
         <v>12</v>
       </c>
       <c r="D411" s="137" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E411" s="138">
         <v>46335</v>
@@ -17355,26 +17354,26 @@
       <c r="G411" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H411" s="137" t="s">
+      <c r="H411" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="I411" s="137" t="s">
+      <c r="I411" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J411" s="140"/>
+      <c r="J411" s="165"/>
     </row>
     <row r="412" spans="1:10">
       <c r="A412" s="137" t="s">
+        <v>257</v>
+      </c>
+      <c r="B412" s="137">
+        <v>1</v>
+      </c>
+      <c r="C412" s="137" t="s">
+        <v>12</v>
+      </c>
+      <c r="D412" s="137" t="s">
         <v>256</v>
-      </c>
-      <c r="B412" s="137">
-        <v>1</v>
-      </c>
-      <c r="C412" s="137" t="s">
-        <v>12</v>
-      </c>
-      <c r="D412" s="137" t="s">
-        <v>255</v>
       </c>
       <c r="E412" s="138">
         <v>46335</v>
@@ -17385,17 +17384,17 @@
       <c r="G412" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H412" s="137" t="s">
-        <v>257</v>
-      </c>
-      <c r="I412" s="137" t="s">
+      <c r="H412" s="164" t="s">
+        <v>258</v>
+      </c>
+      <c r="I412" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J412" s="140"/>
+      <c r="J412" s="165"/>
     </row>
     <row r="413" spans="1:10" ht="15">
       <c r="A413" s="137" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B413" s="137">
         <v>1</v>
@@ -17415,17 +17414,17 @@
       <c r="G413" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H413" s="137" t="s">
-        <v>257</v>
-      </c>
-      <c r="I413" s="165" t="s">
-        <v>240</v>
-      </c>
-      <c r="J413" s="165"/>
+      <c r="H413" s="164" t="s">
+        <v>258</v>
+      </c>
+      <c r="I413" s="164" t="s">
+        <v>241</v>
+      </c>
+      <c r="J413" s="164"/>
     </row>
     <row r="414" spans="1:10" ht="15">
       <c r="A414" s="137" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B414" s="137">
         <v>1</v>
@@ -17445,17 +17444,17 @@
       <c r="G414" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H414" s="137" t="s">
-        <v>257</v>
-      </c>
-      <c r="I414" s="165" t="s">
-        <v>240</v>
-      </c>
-      <c r="J414" s="140"/>
+      <c r="H414" s="164" t="s">
+        <v>258</v>
+      </c>
+      <c r="I414" s="164" t="s">
+        <v>241</v>
+      </c>
+      <c r="J414" s="165"/>
     </row>
     <row r="415" spans="1:10">
       <c r="A415" s="137" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B415" s="137">
         <v>1</v>
@@ -17475,17 +17474,17 @@
       <c r="G415" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H415" s="137" t="s">
+      <c r="H415" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="I415" s="141" t="s">
-        <v>239</v>
-      </c>
-      <c r="J415" s="140"/>
+      <c r="I415" s="166" t="s">
+        <v>240</v>
+      </c>
+      <c r="J415" s="165"/>
     </row>
     <row r="416" spans="1:10" ht="15">
       <c r="A416" s="137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B416" s="137">
         <v>1</v>
@@ -17505,17 +17504,17 @@
       <c r="G416" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H416" s="137" t="s">
+      <c r="H416" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="I416" s="141" t="s">
-        <v>239</v>
-      </c>
-      <c r="J416" s="140"/>
+      <c r="I416" s="166" t="s">
+        <v>240</v>
+      </c>
+      <c r="J416" s="165"/>
     </row>
     <row r="417" spans="1:10" ht="15">
       <c r="A417" s="137" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B417" s="137">
         <v>1</v>
@@ -17535,17 +17534,17 @@
       <c r="G417" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H417" s="137" t="s">
+      <c r="H417" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="I417" s="141" t="s">
-        <v>239</v>
-      </c>
-      <c r="J417" s="140"/>
+      <c r="I417" s="166" t="s">
+        <v>240</v>
+      </c>
+      <c r="J417" s="165"/>
     </row>
     <row r="418" spans="1:10">
       <c r="A418" s="137" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B418" s="137">
         <v>1</v>
@@ -17554,7 +17553,7 @@
         <v>12</v>
       </c>
       <c r="D418" s="137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E418" s="138">
         <v>46336</v>
@@ -17565,19 +17564,19 @@
       <c r="G418" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H418" s="137" t="s">
-        <v>265</v>
-      </c>
-      <c r="I418" s="137" t="s">
+      <c r="H418" s="164" t="s">
+        <v>266</v>
+      </c>
+      <c r="I418" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="J418" s="137" t="s">
+      <c r="J418" s="164" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="419" spans="1:10">
       <c r="A419" s="137" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B419" s="137">
         <v>1</v>
@@ -17586,7 +17585,7 @@
         <v>12</v>
       </c>
       <c r="D419" s="137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E419" s="138">
         <v>46336</v>
@@ -17597,19 +17596,19 @@
       <c r="G419" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H419" s="137" t="s">
-        <v>265</v>
-      </c>
-      <c r="I419" s="137" t="s">
+      <c r="H419" s="164" t="s">
+        <v>266</v>
+      </c>
+      <c r="I419" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="J419" s="137" t="s">
+      <c r="J419" s="164" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="420" spans="1:10">
       <c r="A420" s="137" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B420" s="137">
         <v>1</v>
@@ -17618,7 +17617,7 @@
         <v>12</v>
       </c>
       <c r="D420" s="137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E420" s="138">
         <v>46336</v>
@@ -17629,19 +17628,19 @@
       <c r="G420" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H420" s="137" t="s">
-        <v>265</v>
-      </c>
-      <c r="I420" s="137" t="s">
+      <c r="H420" s="164" t="s">
+        <v>266</v>
+      </c>
+      <c r="I420" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="J420" s="137" t="s">
+      <c r="J420" s="164" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="421" spans="1:10">
       <c r="A421" s="137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B421" s="137">
         <v>1</v>
@@ -17650,7 +17649,7 @@
         <v>12</v>
       </c>
       <c r="D421" s="137" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E421" s="138">
         <v>46337</v>
@@ -17661,17 +17660,17 @@
       <c r="G421" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H421" s="141" t="s">
-        <v>270</v>
-      </c>
-      <c r="I421" s="137" t="s">
+      <c r="H421" s="166" t="s">
         <v>271</v>
       </c>
-      <c r="J421" s="140"/>
+      <c r="I421" s="164" t="s">
+        <v>272</v>
+      </c>
+      <c r="J421" s="165"/>
     </row>
     <row r="422" spans="1:10">
       <c r="A422" s="137" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B422" s="137">
         <v>1</v>
@@ -17680,7 +17679,7 @@
         <v>12</v>
       </c>
       <c r="D422" s="137" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E422" s="138">
         <v>46337</v>
@@ -17691,17 +17690,17 @@
       <c r="G422" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H422" s="141" t="s">
-        <v>270</v>
-      </c>
-      <c r="I422" s="137" t="s">
+      <c r="H422" s="166" t="s">
         <v>271</v>
       </c>
-      <c r="J422" s="140"/>
+      <c r="I422" s="164" t="s">
+        <v>272</v>
+      </c>
+      <c r="J422" s="165"/>
     </row>
     <row r="423" spans="1:10">
       <c r="A423" s="137" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B423" s="137">
         <v>1</v>
@@ -17710,7 +17709,7 @@
         <v>12</v>
       </c>
       <c r="D423" s="137" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E423" s="138">
         <v>46337</v>
@@ -17721,17 +17720,17 @@
       <c r="G423" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H423" s="141" t="s">
-        <v>270</v>
-      </c>
-      <c r="I423" s="137" t="s">
+      <c r="H423" s="166" t="s">
         <v>271</v>
       </c>
-      <c r="J423" s="140"/>
+      <c r="I423" s="164" t="s">
+        <v>272</v>
+      </c>
+      <c r="J423" s="165"/>
     </row>
     <row r="424" spans="1:10">
       <c r="A424" s="137" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B424" s="137">
         <v>1</v>
@@ -17751,19 +17750,19 @@
       <c r="G424" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H424" s="137" t="s">
-        <v>265</v>
-      </c>
-      <c r="I424" s="140" t="s">
-        <v>275</v>
-      </c>
-      <c r="J424" s="140" t="s">
+      <c r="H424" s="164" t="s">
+        <v>266</v>
+      </c>
+      <c r="I424" s="165" t="s">
         <v>276</v>
+      </c>
+      <c r="J424" s="165" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="425" spans="1:10">
       <c r="A425" s="137" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B425" s="137">
         <v>1</v>
@@ -17783,19 +17782,19 @@
       <c r="G425" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H425" s="137" t="s">
-        <v>265</v>
-      </c>
-      <c r="I425" s="140" t="s">
-        <v>275</v>
-      </c>
-      <c r="J425" s="140" t="s">
+      <c r="H425" s="164" t="s">
+        <v>266</v>
+      </c>
+      <c r="I425" s="165" t="s">
         <v>276</v>
+      </c>
+      <c r="J425" s="165" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="426" spans="1:10">
       <c r="A426" s="137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B426" s="137">
         <v>1</v>
@@ -17804,7 +17803,7 @@
         <v>12</v>
       </c>
       <c r="D426" s="137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E426" s="138">
         <v>46337</v>
@@ -17815,19 +17814,19 @@
       <c r="G426" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H426" s="137" t="s">
-        <v>270</v>
-      </c>
-      <c r="I426" s="140" t="s">
-        <v>279</v>
-      </c>
-      <c r="J426" s="140" t="s">
+      <c r="H426" s="164" t="s">
+        <v>271</v>
+      </c>
+      <c r="I426" s="165" t="s">
+        <v>231</v>
+      </c>
+      <c r="J426" s="165" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="427" spans="1:10" ht="15">
       <c r="A427" s="137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B427" s="137">
         <v>1</v>
@@ -17836,7 +17835,7 @@
         <v>12</v>
       </c>
       <c r="D427" s="137" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E427" s="138">
         <v>46337</v>
@@ -17847,19 +17846,19 @@
       <c r="G427" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H427" s="137" t="s">
-        <v>270</v>
-      </c>
-      <c r="I427" s="141" t="s">
-        <v>265</v>
-      </c>
-      <c r="J427" s="140" t="s">
-        <v>276</v>
+      <c r="H427" s="164" t="s">
+        <v>271</v>
+      </c>
+      <c r="I427" s="166" t="s">
+        <v>266</v>
+      </c>
+      <c r="J427" s="165" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="428" spans="1:10">
       <c r="A428" s="137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B428" s="137">
         <v>1</v>
@@ -17868,7 +17867,7 @@
         <v>12</v>
       </c>
       <c r="D428" s="137" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E428" s="138">
         <v>46337</v>
@@ -17879,14 +17878,14 @@
       <c r="G428" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H428" s="137" t="s">
-        <v>270</v>
-      </c>
-      <c r="I428" s="137" t="s">
+      <c r="H428" s="164" t="s">
+        <v>271</v>
+      </c>
+      <c r="I428" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J428" s="140" t="s">
-        <v>271</v>
+      <c r="J428" s="165" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -17900,7 +17899,7 @@
         <v>12</v>
       </c>
       <c r="D429" s="137" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E429" s="138">
         <v>46337</v>
@@ -17911,13 +17910,13 @@
       <c r="G429" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H429" s="137" t="s">
-        <v>271</v>
-      </c>
-      <c r="I429" s="137" t="s">
+      <c r="H429" s="164" t="s">
+        <v>272</v>
+      </c>
+      <c r="I429" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J429" s="140"/>
+      <c r="J429" s="165"/>
     </row>
     <row r="430" spans="1:10">
       <c r="A430" s="137" t="s">
@@ -17930,7 +17929,7 @@
         <v>12</v>
       </c>
       <c r="D430" s="137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E430" s="138">
         <v>46338</v>
@@ -17941,14 +17940,14 @@
       <c r="G430" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H430" s="137" t="s">
+      <c r="H430" s="164" t="s">
         <v>283</v>
       </c>
-      <c r="I430" s="137" t="s">
+      <c r="I430" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="J430" s="137" t="s">
-        <v>270</v>
+      <c r="J430" s="164" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -17962,7 +17961,7 @@
         <v>12</v>
       </c>
       <c r="D431" s="137" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E431" s="138">
         <v>46338</v>
@@ -17973,13 +17972,13 @@
       <c r="G431" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H431" s="137" t="s">
+      <c r="H431" s="164" t="s">
         <v>283</v>
       </c>
-      <c r="I431" s="137" t="s">
+      <c r="I431" s="164" t="s">
         <v>206</v>
       </c>
-      <c r="J431" s="137" t="s">
+      <c r="J431" s="164" t="s">
         <v>284</v>
       </c>
     </row>
@@ -17994,7 +17993,7 @@
         <v>12</v>
       </c>
       <c r="D432" s="137" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E432" s="138">
         <v>46338</v>
@@ -18005,14 +18004,14 @@
       <c r="G432" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H432" s="137" t="s">
+      <c r="H432" s="164" t="s">
         <v>283</v>
       </c>
-      <c r="I432" s="137" t="s">
+      <c r="I432" s="164" t="s">
         <v>285</v>
       </c>
-      <c r="J432" s="137" t="s">
-        <v>239</v>
+      <c r="J432" s="164" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -18037,13 +18036,13 @@
       <c r="G433" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H433" s="137" t="s">
+      <c r="H433" s="164" t="s">
         <v>287</v>
       </c>
-      <c r="I433" s="137" t="s">
+      <c r="I433" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J433" s="140"/>
+      <c r="J433" s="165"/>
     </row>
     <row r="434" spans="1:10">
       <c r="A434" s="137" t="s">
@@ -18067,13 +18066,13 @@
       <c r="G434" s="139">
         <v>0.67708333333333337</v>
       </c>
-      <c r="H434" s="137" t="s">
+      <c r="H434" s="164" t="s">
         <v>214</v>
       </c>
-      <c r="I434" s="137" t="s">
-        <v>250</v>
-      </c>
-      <c r="J434" s="137"/>
+      <c r="I434" s="164" t="s">
+        <v>251</v>
+      </c>
+      <c r="J434" s="164"/>
     </row>
     <row r="435" spans="1:10">
       <c r="A435" s="137" t="s">
@@ -18097,13 +18096,13 @@
       <c r="G435" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H435" s="137" t="s">
-        <v>271</v>
-      </c>
-      <c r="I435" s="137" t="s">
+      <c r="H435" s="164" t="s">
+        <v>272</v>
+      </c>
+      <c r="I435" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J435" s="140"/>
+      <c r="J435" s="165"/>
     </row>
     <row r="436" spans="1:10" ht="15">
       <c r="A436" s="137" t="s">
@@ -18127,13 +18126,13 @@
       <c r="G436" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H436" s="137" t="s">
+      <c r="H436" s="164" t="s">
         <v>217</v>
       </c>
-      <c r="I436" s="137" t="s">
+      <c r="I436" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J436" s="154" t="s">
+      <c r="J436" s="167" t="s">
         <v>291</v>
       </c>
     </row>
@@ -18148,7 +18147,7 @@
         <v>12</v>
       </c>
       <c r="D437" s="137" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E437" s="138">
         <v>46339</v>
@@ -18159,13 +18158,13 @@
       <c r="G437" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H437" s="137" t="s">
+      <c r="H437" s="164" t="s">
         <v>217</v>
       </c>
-      <c r="I437" s="140" t="s">
+      <c r="I437" s="165" t="s">
         <v>292</v>
       </c>
-      <c r="J437" s="140" t="s">
+      <c r="J437" s="165" t="s">
         <v>210</v>
       </c>
     </row>
@@ -18191,13 +18190,13 @@
       <c r="G438" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H438" s="137" t="s">
+      <c r="H438" s="164" t="s">
         <v>295</v>
       </c>
-      <c r="I438" s="137" t="s">
+      <c r="I438" s="164" t="s">
         <v>213</v>
       </c>
-      <c r="J438" s="140" t="s">
+      <c r="J438" s="165" t="s">
         <v>296</v>
       </c>
     </row>
@@ -18223,13 +18222,13 @@
       <c r="G439" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H439" s="137" t="s">
+      <c r="H439" s="164" t="s">
         <v>295</v>
       </c>
-      <c r="I439" s="137" t="s">
+      <c r="I439" s="164" t="s">
         <v>285</v>
       </c>
-      <c r="J439" s="140" t="s">
+      <c r="J439" s="165" t="s">
         <v>210</v>
       </c>
     </row>
@@ -18255,13 +18254,13 @@
       <c r="G440" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H440" s="137" t="s">
+      <c r="H440" s="164" t="s">
         <v>295</v>
       </c>
-      <c r="I440" s="137" t="s">
+      <c r="I440" s="164" t="s">
         <v>285</v>
       </c>
-      <c r="J440" s="140" t="s">
+      <c r="J440" s="165" t="s">
         <v>210</v>
       </c>
     </row>
@@ -18276,7 +18275,7 @@
         <v>12</v>
       </c>
       <c r="D441" s="137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E441" s="138">
         <v>46339</v>
@@ -18288,10 +18287,10 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H441" s="137" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I441" s="137" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J441" s="137"/>
     </row>
@@ -18306,7 +18305,7 @@
         <v>12</v>
       </c>
       <c r="D442" s="137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E442" s="138">
         <v>46339</v>
@@ -18318,7 +18317,7 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H442" s="137" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I442" s="137" t="s">
         <v>287</v>
@@ -18336,7 +18335,7 @@
         <v>12</v>
       </c>
       <c r="D443" s="137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E443" s="138">
         <v>46339</v>
@@ -18348,7 +18347,7 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="H443" s="137" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I443" s="137" t="s">
         <v>287</v>
@@ -18381,7 +18380,7 @@
         <v>223</v>
       </c>
       <c r="I444" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="445" spans="1:10">
@@ -18413,7 +18412,7 @@
         <v>223</v>
       </c>
       <c r="J445" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="446" spans="1:10">
@@ -18529,7 +18528,7 @@
         <v>312</v>
       </c>
       <c r="I449" s="115" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="450" spans="1:10">
@@ -18558,7 +18557,7 @@
         <v>315</v>
       </c>
       <c r="I450" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="451" spans="1:10">
@@ -18587,7 +18586,7 @@
         <v>315</v>
       </c>
       <c r="I451" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="452" spans="1:10">
@@ -18648,7 +18647,7 @@
         <v>223</v>
       </c>
       <c r="J453" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="454" spans="1:10">
@@ -18677,7 +18676,7 @@
         <v>223</v>
       </c>
       <c r="I454" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="455" spans="1:10">
@@ -18735,7 +18734,7 @@
         <v>309</v>
       </c>
       <c r="I456" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="457" spans="1:10">
@@ -18764,7 +18763,7 @@
         <v>304</v>
       </c>
       <c r="I457" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="458" spans="1:10">
@@ -18793,7 +18792,7 @@
         <v>223</v>
       </c>
       <c r="I458" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="459" spans="1:10">
@@ -18822,7 +18821,7 @@
         <v>304</v>
       </c>
       <c r="I459" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J459" s="115" t="s">
         <v>213</v>
@@ -18857,1746 +18856,1746 @@
         <v>223</v>
       </c>
       <c r="J460" s="115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="461" spans="1:10" ht="15">
-      <c r="A461" s="142" t="s">
+      <c r="A461" s="140" t="s">
         <v>328</v>
       </c>
-      <c r="B461" s="142">
-        <v>1</v>
-      </c>
-      <c r="C461" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D461" s="142" t="s">
+      <c r="B461" s="140">
+        <v>1</v>
+      </c>
+      <c r="C461" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D461" s="140" t="s">
         <v>329</v>
       </c>
-      <c r="E461" s="143">
+      <c r="E461" s="141">
         <v>46335</v>
       </c>
-      <c r="F461" s="144">
+      <c r="F461" s="142">
         <v>0.375</v>
       </c>
-      <c r="G461" s="144">
+      <c r="G461" s="142">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H461" s="145" t="s">
+      <c r="H461" s="143" t="s">
         <v>330</v>
       </c>
-      <c r="I461" s="150" t="s">
+      <c r="I461" s="148" t="s">
         <v>331</v>
       </c>
-      <c r="J461" s="150" t="s">
+      <c r="J461" s="148" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="462" spans="1:10">
-      <c r="A462" s="142" t="s">
+      <c r="A462" s="140" t="s">
         <v>333</v>
       </c>
-      <c r="B462" s="142">
-        <v>1</v>
-      </c>
-      <c r="C462" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D462" s="142" t="s">
+      <c r="B462" s="140">
+        <v>1</v>
+      </c>
+      <c r="C462" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D462" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="E462" s="143">
+      <c r="E462" s="141">
         <v>46335</v>
       </c>
-      <c r="F462" s="144">
+      <c r="F462" s="142">
         <v>0.375</v>
       </c>
-      <c r="G462" s="144">
+      <c r="G462" s="142">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H462" s="145" t="s">
+      <c r="H462" s="143" t="s">
         <v>330</v>
       </c>
-      <c r="I462" s="151" t="s">
+      <c r="I462" s="149" t="s">
         <v>334</v>
       </c>
-      <c r="J462" s="151" t="s">
+      <c r="J462" s="149" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="463" spans="1:10">
+      <c r="A463" s="140" t="s">
+        <v>335</v>
+      </c>
+      <c r="B463" s="140">
+        <v>1</v>
+      </c>
+      <c r="C463" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D463" s="140" t="s">
+        <v>115</v>
+      </c>
+      <c r="E463" s="141">
+        <v>46335</v>
+      </c>
+      <c r="F463" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G463" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H463" s="143" t="s">
+        <v>336</v>
+      </c>
+      <c r="I463" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J463" s="148"/>
+    </row>
+    <row r="464" spans="1:10">
+      <c r="A464" s="140" t="s">
+        <v>335</v>
+      </c>
+      <c r="B464" s="140">
+        <v>1</v>
+      </c>
+      <c r="C464" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D464" s="140" t="s">
+        <v>115</v>
+      </c>
+      <c r="E464" s="141">
+        <v>46335</v>
+      </c>
+      <c r="F464" s="142">
+        <v>0.4375</v>
+      </c>
+      <c r="G464" s="142">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H464" s="143" t="s">
+        <v>336</v>
+      </c>
+      <c r="I464" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J464" s="148"/>
+    </row>
+    <row r="465" spans="1:10">
+      <c r="A465" s="140" t="s">
+        <v>338</v>
+      </c>
+      <c r="B465" s="140">
+        <v>1</v>
+      </c>
+      <c r="C465" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D465" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="E465" s="141">
+        <v>46335</v>
+      </c>
+      <c r="F465" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G465" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H465" s="143" t="s">
+        <v>234</v>
+      </c>
+      <c r="I465" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J465" s="149" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10">
+      <c r="A466" s="140" t="s">
+        <v>339</v>
+      </c>
+      <c r="B466" s="140">
+        <v>1</v>
+      </c>
+      <c r="C466" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D466" s="140" t="s">
+        <v>115</v>
+      </c>
+      <c r="E466" s="141">
+        <v>46335</v>
+      </c>
+      <c r="F466" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G466" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H466" s="143" t="s">
+        <v>336</v>
+      </c>
+      <c r="I466" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J466" s="148"/>
+    </row>
+    <row r="467" spans="1:10">
+      <c r="A467" s="140" t="s">
+        <v>340</v>
+      </c>
+      <c r="B467" s="140">
+        <v>1</v>
+      </c>
+      <c r="C467" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D467" s="140" t="s">
+        <v>341</v>
+      </c>
+      <c r="E467" s="141">
+        <v>46335</v>
+      </c>
+      <c r="F467" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G467" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H467" s="143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I467" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J467" s="148" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" ht="15">
+      <c r="A468" s="140" t="s">
+        <v>343</v>
+      </c>
+      <c r="B468" s="140">
+        <v>1</v>
+      </c>
+      <c r="C468" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D468" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E468" s="141">
+        <v>46335</v>
+      </c>
+      <c r="F468" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G468" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H468" s="143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I468" s="151" t="s">
+        <v>345</v>
+      </c>
+      <c r="J468" s="148" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" ht="15">
+      <c r="A469" s="140" t="s">
+        <v>343</v>
+      </c>
+      <c r="B469" s="140">
+        <v>1</v>
+      </c>
+      <c r="C469" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D469" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="E469" s="141">
+        <v>46335</v>
+      </c>
+      <c r="F469" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G469" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H469" s="143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I469" s="148" t="s">
+        <v>347</v>
+      </c>
+      <c r="J469" s="148" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10">
+      <c r="A470" s="140" t="s">
+        <v>349</v>
+      </c>
+      <c r="B470" s="140">
+        <v>1</v>
+      </c>
+      <c r="C470" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D470" s="140" t="s">
+        <v>350</v>
+      </c>
+      <c r="E470" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F470" s="142">
+        <v>0.4375</v>
+      </c>
+      <c r="G470" s="142">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H470" s="143" t="s">
+        <v>351</v>
+      </c>
+      <c r="I470" s="148" t="s">
+        <v>352</v>
+      </c>
+      <c r="J470" s="148"/>
+    </row>
+    <row r="471" spans="1:10" ht="15">
+      <c r="A471" s="140" t="s">
+        <v>353</v>
+      </c>
+      <c r="B471" s="140">
+        <v>1</v>
+      </c>
+      <c r="C471" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D471" s="140" t="s">
+        <v>354</v>
+      </c>
+      <c r="E471" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F471" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G471" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H471" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I471" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J471" s="151" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" ht="15">
+      <c r="A472" s="140" t="s">
+        <v>353</v>
+      </c>
+      <c r="B472" s="140">
+        <v>1</v>
+      </c>
+      <c r="C472" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D472" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="E472" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F472" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G472" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H472" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I472" s="151" t="s">
+        <v>355</v>
+      </c>
+      <c r="J472" s="148" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" ht="15">
+      <c r="A473" s="140" t="s">
+        <v>356</v>
+      </c>
+      <c r="B473" s="140">
+        <v>1</v>
+      </c>
+      <c r="C473" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D473" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E473" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F473" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G473" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H473" s="143" t="s">
+        <v>357</v>
+      </c>
+      <c r="I473" s="151" t="s">
+        <v>358</v>
+      </c>
+      <c r="J473" s="148"/>
+    </row>
+    <row r="474" spans="1:10">
+      <c r="A474" s="140" t="s">
+        <v>359</v>
+      </c>
+      <c r="B474" s="140">
+        <v>1</v>
+      </c>
+      <c r="C474" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D474" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="E474" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F474" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G474" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H474" s="143" t="s">
+        <v>357</v>
+      </c>
+      <c r="I474" s="148" t="s">
+        <v>352</v>
+      </c>
+      <c r="J474" s="148"/>
+    </row>
+    <row r="475" spans="1:10" ht="15">
+      <c r="A475" s="140" t="s">
+        <v>360</v>
+      </c>
+      <c r="B475" s="140">
+        <v>1</v>
+      </c>
+      <c r="C475" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D475" s="140" t="s">
+        <v>25</v>
+      </c>
+      <c r="E475" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F475" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G475" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H475" s="143" t="s">
+        <v>355</v>
+      </c>
+      <c r="I475" s="151" t="s">
+        <v>351</v>
+      </c>
+      <c r="J475" s="148" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10">
+      <c r="A476" s="140" t="s">
+        <v>360</v>
+      </c>
+      <c r="B476" s="140">
+        <v>1</v>
+      </c>
+      <c r="C476" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D476" s="140" t="s">
+        <v>29</v>
+      </c>
+      <c r="E476" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F476" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G476" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H476" s="143" t="s">
+        <v>355</v>
+      </c>
+      <c r="I476" s="148" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="463" spans="1:10">
-      <c r="A463" s="142" t="s">
-        <v>335</v>
-      </c>
-      <c r="B463" s="142">
-        <v>1</v>
-      </c>
-      <c r="C463" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D463" s="142" t="s">
-        <v>115</v>
-      </c>
-      <c r="E463" s="143">
-        <v>46335</v>
-      </c>
-      <c r="F463" s="144">
+      <c r="J476" s="148" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" ht="15">
+      <c r="A477" s="140" t="s">
+        <v>362</v>
+      </c>
+      <c r="B477" s="140">
+        <v>1</v>
+      </c>
+      <c r="C477" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D477" s="140" t="s">
+        <v>354</v>
+      </c>
+      <c r="E477" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F477" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G477" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H477" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I477" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J477" s="151" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" ht="15">
+      <c r="A478" s="140" t="s">
+        <v>362</v>
+      </c>
+      <c r="B478" s="140">
+        <v>1</v>
+      </c>
+      <c r="C478" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D478" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="E478" s="141">
+        <v>46336</v>
+      </c>
+      <c r="F478" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G478" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H478" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I478" s="151" t="s">
+        <v>363</v>
+      </c>
+      <c r="J478" s="148" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10">
+      <c r="A479" s="140" t="s">
+        <v>365</v>
+      </c>
+      <c r="B479" s="140">
+        <v>1</v>
+      </c>
+      <c r="C479" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D479" s="140" t="s">
+        <v>366</v>
+      </c>
+      <c r="E479" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F479" s="142">
         <v>0.375</v>
       </c>
-      <c r="G463" s="144">
+      <c r="G479" s="142">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H463" s="145" t="s">
+      <c r="H479" s="143" t="s">
+        <v>357</v>
+      </c>
+      <c r="I479" s="148" t="s">
+        <v>363</v>
+      </c>
+      <c r="J479" s="148"/>
+    </row>
+    <row r="480" spans="1:10">
+      <c r="A480" s="140" t="s">
+        <v>367</v>
+      </c>
+      <c r="B480" s="140">
+        <v>1</v>
+      </c>
+      <c r="C480" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D480" s="140" t="s">
+        <v>368</v>
+      </c>
+      <c r="E480" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F480" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G480" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H480" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="I480" s="148" t="s">
+        <v>276</v>
+      </c>
+      <c r="J480" s="148" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10">
+      <c r="A481" s="140" t="s">
+        <v>367</v>
+      </c>
+      <c r="B481" s="140">
+        <v>1</v>
+      </c>
+      <c r="C481" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D481" s="140" t="s">
+        <v>369</v>
+      </c>
+      <c r="E481" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F481" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G481" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H481" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="I481" s="148" t="s">
+        <v>348</v>
+      </c>
+      <c r="J481" s="148" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" ht="15">
+      <c r="A482" s="140" t="s">
+        <v>367</v>
+      </c>
+      <c r="B482" s="140">
+        <v>1</v>
+      </c>
+      <c r="C482" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D482" s="140" t="s">
+        <v>371</v>
+      </c>
+      <c r="E482" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F482" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G482" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H482" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="I482" s="154" t="s">
+        <v>372</v>
+      </c>
+      <c r="J482" s="152" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10">
+      <c r="A483" s="140" t="s">
+        <v>373</v>
+      </c>
+      <c r="B483" s="140">
+        <v>1</v>
+      </c>
+      <c r="C483" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D483" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E483" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F483" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G483" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H483" s="143" t="s">
+        <v>374</v>
+      </c>
+      <c r="I483" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J483" s="148"/>
+    </row>
+    <row r="484" spans="1:10" ht="15">
+      <c r="A484" s="140" t="s">
+        <v>375</v>
+      </c>
+      <c r="B484" s="140">
+        <v>1</v>
+      </c>
+      <c r="C484" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D484" s="140" t="s">
+        <v>376</v>
+      </c>
+      <c r="E484" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F484" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G484" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H484" s="143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I484" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J484" s="148"/>
+    </row>
+    <row r="485" spans="1:10" ht="15">
+      <c r="A485" s="140" t="s">
+        <v>377</v>
+      </c>
+      <c r="B485" s="140">
+        <v>1</v>
+      </c>
+      <c r="C485" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D485" s="140" t="s">
+        <v>376</v>
+      </c>
+      <c r="E485" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F485" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G485" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H485" s="143" t="s">
+        <v>372</v>
+      </c>
+      <c r="I485" s="151" t="s">
+        <v>357</v>
+      </c>
+      <c r="J485" s="151" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" ht="15">
+      <c r="A486" s="140" t="s">
+        <v>377</v>
+      </c>
+      <c r="B486" s="140">
+        <v>1</v>
+      </c>
+      <c r="C486" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D486" s="140" t="s">
+        <v>378</v>
+      </c>
+      <c r="E486" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F486" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G486" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H486" s="143" t="s">
+        <v>372</v>
+      </c>
+      <c r="I486" s="151" t="s">
+        <v>345</v>
+      </c>
+      <c r="J486" s="148" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10">
+      <c r="A487" s="140" t="s">
+        <v>379</v>
+      </c>
+      <c r="B487" s="140">
+        <v>1</v>
+      </c>
+      <c r="C487" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D487" s="140" t="s">
+        <v>341</v>
+      </c>
+      <c r="E487" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F487" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G487" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H487" s="143" t="s">
+        <v>357</v>
+      </c>
+      <c r="I487" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J487" s="148"/>
+    </row>
+    <row r="488" spans="1:10" ht="15">
+      <c r="A488" s="140" t="s">
+        <v>380</v>
+      </c>
+      <c r="B488" s="140">
+        <v>1</v>
+      </c>
+      <c r="C488" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D488" s="140" t="s">
+        <v>381</v>
+      </c>
+      <c r="E488" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F488" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G488" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H488" s="143" t="s">
+        <v>382</v>
+      </c>
+      <c r="I488" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J488" s="151" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" ht="15">
+      <c r="A489" s="140" t="s">
+        <v>380</v>
+      </c>
+      <c r="B489" s="140">
+        <v>1</v>
+      </c>
+      <c r="C489" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D489" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E489" s="141">
+        <v>46337</v>
+      </c>
+      <c r="F489" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G489" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H489" s="143" t="s">
+        <v>382</v>
+      </c>
+      <c r="I489" s="151" t="s">
+        <v>383</v>
+      </c>
+      <c r="J489" s="151" t="s">
         <v>336</v>
       </c>
-      <c r="I463" s="150" t="s">
+    </row>
+    <row r="490" spans="1:10" ht="15">
+      <c r="A490" s="140" t="s">
+        <v>384</v>
+      </c>
+      <c r="B490" s="140">
+        <v>1</v>
+      </c>
+      <c r="C490" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D490" s="140" t="s">
+        <v>381</v>
+      </c>
+      <c r="E490" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F490" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G490" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H490" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I490" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J490" s="151" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" ht="15">
+      <c r="A491" s="140" t="s">
+        <v>384</v>
+      </c>
+      <c r="B491" s="140">
+        <v>1</v>
+      </c>
+      <c r="C491" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D491" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E491" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F491" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G491" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H491" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I491" s="148" t="s">
         <v>337</v>
       </c>
-      <c r="J463" s="150"/>
-    </row>
-    <row r="464" spans="1:10">
-      <c r="A464" s="142" t="s">
-        <v>335</v>
-      </c>
-      <c r="B464" s="142">
-        <v>1</v>
-      </c>
-      <c r="C464" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D464" s="142" t="s">
-        <v>115</v>
-      </c>
-      <c r="E464" s="143">
-        <v>46335</v>
-      </c>
-      <c r="F464" s="144">
+      <c r="J491" s="151" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10">
+      <c r="A492" s="140" t="s">
+        <v>386</v>
+      </c>
+      <c r="B492" s="140">
+        <v>1</v>
+      </c>
+      <c r="C492" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D492" s="140" t="s">
+        <v>378</v>
+      </c>
+      <c r="E492" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F492" s="142">
         <v>0.4375</v>
       </c>
-      <c r="G464" s="144">
+      <c r="G492" s="142">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H464" s="145" t="s">
+      <c r="H492" s="143" t="s">
+        <v>387</v>
+      </c>
+      <c r="I492" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J492" s="148"/>
+    </row>
+    <row r="493" spans="1:10" ht="15">
+      <c r="A493" s="140" t="s">
+        <v>388</v>
+      </c>
+      <c r="B493" s="140">
+        <v>1</v>
+      </c>
+      <c r="C493" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D493" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E493" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F493" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G493" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H493" s="143" t="s">
+        <v>351</v>
+      </c>
+      <c r="I493" s="150" t="s">
+        <v>345</v>
+      </c>
+      <c r="J493" s="151" t="s">
         <v>336</v>
       </c>
-      <c r="I464" s="150" t="s">
+    </row>
+    <row r="494" spans="1:10" ht="15">
+      <c r="A494" s="140" t="s">
+        <v>388</v>
+      </c>
+      <c r="B494" s="140">
+        <v>1</v>
+      </c>
+      <c r="C494" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D494" s="140" t="s">
+        <v>376</v>
+      </c>
+      <c r="E494" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F494" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G494" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H494" s="143" t="s">
+        <v>351</v>
+      </c>
+      <c r="I494" s="154" t="s">
+        <v>243</v>
+      </c>
+      <c r="J494" s="148" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" ht="15">
+      <c r="A495" s="140" t="s">
+        <v>389</v>
+      </c>
+      <c r="B495" s="140">
+        <v>1</v>
+      </c>
+      <c r="C495" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D495" s="140" t="s">
+        <v>354</v>
+      </c>
+      <c r="E495" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F495" s="142">
+        <v>0.5</v>
+      </c>
+      <c r="G495" s="142">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H495" s="143" t="s">
+        <v>351</v>
+      </c>
+      <c r="I495" s="160" t="s">
+        <v>364</v>
+      </c>
+      <c r="J495" s="148" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" ht="15">
+      <c r="A496" s="140" t="s">
+        <v>390</v>
+      </c>
+      <c r="B496" s="140">
+        <v>1</v>
+      </c>
+      <c r="C496" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D496" s="140" t="s">
+        <v>354</v>
+      </c>
+      <c r="E496" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F496" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G496" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H496" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I496" s="151" t="s">
+        <v>351</v>
+      </c>
+      <c r="J496" s="148" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" ht="15">
+      <c r="A497" s="140" t="s">
+        <v>390</v>
+      </c>
+      <c r="B497" s="140">
+        <v>1</v>
+      </c>
+      <c r="C497" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D497" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="E497" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F497" s="142">
+        <v>0.5625</v>
+      </c>
+      <c r="G497" s="142">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="H497" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="I497" s="151" t="s">
+        <v>336</v>
+      </c>
+      <c r="J497" s="148" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" ht="15">
+      <c r="A498" s="140" t="s">
+        <v>391</v>
+      </c>
+      <c r="B498" s="140">
+        <v>1</v>
+      </c>
+      <c r="C498" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D498" s="140" t="s">
+        <v>392</v>
+      </c>
+      <c r="E498" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F498" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G498" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H498" s="143" t="s">
+        <v>393</v>
+      </c>
+      <c r="I498" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J498" s="150" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" ht="15">
+      <c r="A499" s="140" t="s">
+        <v>391</v>
+      </c>
+      <c r="B499" s="140">
+        <v>1</v>
+      </c>
+      <c r="C499" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D499" s="140" t="s">
+        <v>394</v>
+      </c>
+      <c r="E499" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F499" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G499" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H499" s="143" t="s">
+        <v>393</v>
+      </c>
+      <c r="I499" s="151" t="s">
+        <v>345</v>
+      </c>
+      <c r="J499" s="148" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" ht="15">
+      <c r="A500" s="140" t="s">
+        <v>395</v>
+      </c>
+      <c r="B500" s="140">
+        <v>1</v>
+      </c>
+      <c r="C500" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D500" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="E500" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F500" s="142">
+        <v>0.625</v>
+      </c>
+      <c r="G500" s="142">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H500" s="143" t="s">
+        <v>387</v>
+      </c>
+      <c r="I500" s="151" t="s">
+        <v>243</v>
+      </c>
+      <c r="J500" s="148"/>
+    </row>
+    <row r="501" spans="1:10" ht="15">
+      <c r="A501" s="140" t="s">
+        <v>396</v>
+      </c>
+      <c r="B501" s="140">
+        <v>1</v>
+      </c>
+      <c r="C501" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D501" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E501" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F501" s="142">
+        <v>0.6875</v>
+      </c>
+      <c r="G501" s="142">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H501" s="143" t="s">
+        <v>397</v>
+      </c>
+      <c r="I501" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J501" s="151" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10">
+      <c r="A502" s="140" t="s">
+        <v>396</v>
+      </c>
+      <c r="B502" s="140">
+        <v>1</v>
+      </c>
+      <c r="C502" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D502" s="140" t="s">
+        <v>376</v>
+      </c>
+      <c r="E502" s="141">
+        <v>46338</v>
+      </c>
+      <c r="F502" s="142">
+        <v>0.6875</v>
+      </c>
+      <c r="G502" s="142">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="H502" s="143" t="s">
+        <v>397</v>
+      </c>
+      <c r="I502" s="148" t="s">
         <v>337</v>
       </c>
-      <c r="J464" s="150"/>
-    </row>
-    <row r="465" spans="1:10">
-      <c r="A465" s="142" t="s">
-        <v>338</v>
-      </c>
-      <c r="B465" s="142">
-        <v>1</v>
-      </c>
-      <c r="C465" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D465" s="142" t="s">
-        <v>41</v>
-      </c>
-      <c r="E465" s="143">
-        <v>46335</v>
-      </c>
-      <c r="F465" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G465" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H465" s="145" t="s">
-        <v>339</v>
-      </c>
-      <c r="I465" s="150" t="s">
+      <c r="J502" s="148" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" ht="30.75">
+      <c r="A503" s="140" t="s">
+        <v>398</v>
+      </c>
+      <c r="B503" s="140">
+        <v>1</v>
+      </c>
+      <c r="C503" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D503" s="140" t="s">
+        <v>399</v>
+      </c>
+      <c r="E503" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F503" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G503" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H503" s="143" t="s">
+        <v>217</v>
+      </c>
+      <c r="I503" s="157" t="s">
+        <v>400</v>
+      </c>
+      <c r="J503" s="154" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" ht="15">
+      <c r="A504" s="140" t="s">
+        <v>401</v>
+      </c>
+      <c r="B504" s="140">
+        <v>1</v>
+      </c>
+      <c r="C504" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D504" s="140" t="s">
+        <v>378</v>
+      </c>
+      <c r="E504" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F504" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G504" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H504" s="143" t="s">
+        <v>217</v>
+      </c>
+      <c r="I504" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J504" s="151" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" ht="15">
+      <c r="A505" s="140" t="s">
+        <v>402</v>
+      </c>
+      <c r="B505" s="140">
+        <v>1</v>
+      </c>
+      <c r="C505" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D505" s="140" t="s">
+        <v>368</v>
+      </c>
+      <c r="E505" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F505" s="142">
+        <v>0.375</v>
+      </c>
+      <c r="G505" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H505" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="I505" s="151" t="s">
+        <v>351</v>
+      </c>
+      <c r="J505" s="148"/>
+    </row>
+    <row r="506" spans="1:10">
+      <c r="A506" s="140" t="s">
+        <v>403</v>
+      </c>
+      <c r="B506" s="140">
+        <v>1</v>
+      </c>
+      <c r="C506" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D506" s="140" t="s">
+        <v>378</v>
+      </c>
+      <c r="E506" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F506" s="142">
+        <v>0.4375</v>
+      </c>
+      <c r="G506" s="142">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H506" s="143" t="s">
+        <v>351</v>
+      </c>
+      <c r="I506" s="148" t="s">
         <v>331</v>
       </c>
-      <c r="J465" s="151" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="466" spans="1:10">
-      <c r="A466" s="142" t="s">
-        <v>340</v>
-      </c>
-      <c r="B466" s="142">
-        <v>1</v>
-      </c>
-      <c r="C466" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D466" s="142" t="s">
-        <v>115</v>
-      </c>
-      <c r="E466" s="143">
-        <v>46335</v>
-      </c>
-      <c r="F466" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G466" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H466" s="145" t="s">
+      <c r="J506" s="152" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" ht="15">
+      <c r="A507" s="140" t="s">
+        <v>403</v>
+      </c>
+      <c r="B507" s="140">
+        <v>1</v>
+      </c>
+      <c r="C507" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D507" s="140" t="s">
+        <v>354</v>
+      </c>
+      <c r="E507" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F507" s="142">
+        <v>0.4375</v>
+      </c>
+      <c r="G507" s="142">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H507" s="143" t="s">
+        <v>351</v>
+      </c>
+      <c r="I507" s="151" t="s">
+        <v>345</v>
+      </c>
+      <c r="J507" s="148" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10">
+      <c r="A508" s="140" t="s">
+        <v>404</v>
+      </c>
+      <c r="B508" s="140">
+        <v>1</v>
+      </c>
+      <c r="C508" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D508" s="140" t="s">
+        <v>341</v>
+      </c>
+      <c r="E508" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F508" s="142">
+        <v>0.4375</v>
+      </c>
+      <c r="G508" s="142">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H508" s="143" t="s">
         <v>336</v>
       </c>
-      <c r="I466" s="150" t="s">
+      <c r="I508" s="148" t="s">
         <v>337</v>
       </c>
-      <c r="J466" s="150"/>
-    </row>
-    <row r="467" spans="1:10">
-      <c r="A467" s="142" t="s">
-        <v>341</v>
-      </c>
-      <c r="B467" s="142">
-        <v>1</v>
-      </c>
-      <c r="C467" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D467" s="142" t="s">
-        <v>342</v>
-      </c>
-      <c r="E467" s="143">
-        <v>46335</v>
-      </c>
-      <c r="F467" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G467" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H467" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="I467" s="150" t="s">
+      <c r="J508" s="152" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" ht="15">
+      <c r="A509" s="140" t="s">
+        <v>405</v>
+      </c>
+      <c r="B509" s="140">
+        <v>1</v>
+      </c>
+      <c r="C509" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D509" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="E509" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F509" s="142">
+        <v>0.4375</v>
+      </c>
+      <c r="G509" s="142">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H509" s="143" t="s">
+        <v>336</v>
+      </c>
+      <c r="I509" s="150" t="s">
+        <v>243</v>
+      </c>
+      <c r="J509" s="150" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10">
+      <c r="A510" s="140" t="s">
+        <v>406</v>
+      </c>
+      <c r="B510" s="140">
+        <v>1</v>
+      </c>
+      <c r="C510" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D510" s="140" t="s">
+        <v>344</v>
+      </c>
+      <c r="E510" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F510" s="142">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G510" s="142">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H510" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="I510" s="148" t="s">
         <v>331</v>
       </c>
-      <c r="J467" s="150" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="468" spans="1:10" ht="15">
-      <c r="A468" s="142" t="s">
-        <v>344</v>
-      </c>
-      <c r="B468" s="142">
-        <v>1</v>
-      </c>
-      <c r="C468" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D468" s="142" t="s">
+      <c r="J510" s="148" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" ht="15">
+      <c r="A511" s="140" t="s">
+        <v>406</v>
+      </c>
+      <c r="B511" s="140">
+        <v>1</v>
+      </c>
+      <c r="C511" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D511" s="140" t="s">
+        <v>376</v>
+      </c>
+      <c r="E511" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F511" s="142">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G511" s="142">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H511" s="143" t="s">
         <v>345</v>
       </c>
-      <c r="E468" s="143">
-        <v>46335</v>
-      </c>
-      <c r="F468" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G468" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H468" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="I468" s="153" t="s">
-        <v>346</v>
-      </c>
-      <c r="J468" s="150" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="469" spans="1:10" ht="15">
-      <c r="A469" s="142" t="s">
-        <v>344</v>
-      </c>
-      <c r="B469" s="142">
-        <v>1</v>
-      </c>
-      <c r="C469" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D469" s="142" t="s">
-        <v>347</v>
-      </c>
-      <c r="E469" s="143">
-        <v>46335</v>
-      </c>
-      <c r="F469" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G469" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H469" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="I469" s="150" t="s">
+      <c r="I511" s="160" t="s">
+        <v>408</v>
+      </c>
+      <c r="J511" s="148" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10">
+      <c r="A512" s="140" t="s">
+        <v>409</v>
+      </c>
+      <c r="B512" s="140">
+        <v>1</v>
+      </c>
+      <c r="C512" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D512" s="140" t="s">
+        <v>378</v>
+      </c>
+      <c r="E512" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F512" s="142">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G512" s="142">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="H512" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="I512" s="148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J512" s="148" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10">
+      <c r="A513" s="140" t="s">
+        <v>410</v>
+      </c>
+      <c r="B513" s="140">
+        <v>1</v>
+      </c>
+      <c r="C513" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D513" s="140" t="s">
+        <v>411</v>
+      </c>
+      <c r="E513" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F513" s="142">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G513" s="142">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H513" s="143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I513" s="148" t="s">
+        <v>331</v>
+      </c>
+      <c r="J513" s="148" t="s">
         <v>348</v>
       </c>
-      <c r="J469" s="150" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="470" spans="1:10">
-      <c r="A470" s="142" t="s">
-        <v>350</v>
-      </c>
-      <c r="B470" s="142">
-        <v>1</v>
-      </c>
-      <c r="C470" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D470" s="142" t="s">
-        <v>351</v>
-      </c>
-      <c r="E470" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F470" s="144">
-        <v>0.4375</v>
-      </c>
-      <c r="G470" s="144">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H470" s="145" t="s">
-        <v>352</v>
-      </c>
-      <c r="I470" s="150" t="s">
-        <v>353</v>
-      </c>
-      <c r="J470" s="150"/>
-    </row>
-    <row r="471" spans="1:10" ht="15">
-      <c r="A471" s="142" t="s">
-        <v>354</v>
-      </c>
-      <c r="B471" s="142">
-        <v>1</v>
-      </c>
-      <c r="C471" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D471" s="142" t="s">
-        <v>355</v>
-      </c>
-      <c r="E471" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F471" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G471" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H471" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I471" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J471" s="153" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="472" spans="1:10" ht="15">
-      <c r="A472" s="142" t="s">
-        <v>354</v>
-      </c>
-      <c r="B472" s="142">
-        <v>1</v>
-      </c>
-      <c r="C472" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D472" s="142" t="s">
-        <v>347</v>
-      </c>
-      <c r="E472" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F472" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G472" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H472" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I472" s="153" t="s">
-        <v>356</v>
-      </c>
-      <c r="J472" s="150" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="473" spans="1:10" ht="15">
-      <c r="A473" s="142" t="s">
-        <v>357</v>
-      </c>
-      <c r="B473" s="142">
-        <v>1</v>
-      </c>
-      <c r="C473" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D473" s="142" t="s">
+    </row>
+    <row r="514" spans="1:10" ht="15">
+      <c r="A514" s="140" t="s">
+        <v>410</v>
+      </c>
+      <c r="B514" s="140">
+        <v>1</v>
+      </c>
+      <c r="C514" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D514" s="140" t="s">
+        <v>412</v>
+      </c>
+      <c r="E514" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F514" s="142">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G514" s="142">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H514" s="143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I514" s="151" t="s">
         <v>345</v>
       </c>
-      <c r="E473" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F473" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G473" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H473" s="145" t="s">
-        <v>358</v>
-      </c>
-      <c r="I473" s="153" t="s">
-        <v>359</v>
-      </c>
-      <c r="J473" s="150"/>
-    </row>
-    <row r="474" spans="1:10">
-      <c r="A474" s="142" t="s">
-        <v>360</v>
-      </c>
-      <c r="B474" s="142">
-        <v>1</v>
-      </c>
-      <c r="C474" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D474" s="142" t="s">
-        <v>347</v>
-      </c>
-      <c r="E474" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F474" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G474" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H474" s="145" t="s">
-        <v>358</v>
-      </c>
-      <c r="I474" s="150" t="s">
-        <v>353</v>
-      </c>
-      <c r="J474" s="150"/>
-    </row>
-    <row r="475" spans="1:10" ht="15">
-      <c r="A475" s="142" t="s">
-        <v>361</v>
-      </c>
-      <c r="B475" s="142">
-        <v>1</v>
-      </c>
-      <c r="C475" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D475" s="142" t="s">
-        <v>25</v>
-      </c>
-      <c r="E475" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F475" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G475" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H475" s="145" t="s">
-        <v>356</v>
-      </c>
-      <c r="I475" s="153" t="s">
-        <v>352</v>
-      </c>
-      <c r="J475" s="150" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="476" spans="1:10">
-      <c r="A476" s="142" t="s">
-        <v>361</v>
-      </c>
-      <c r="B476" s="142">
-        <v>1</v>
-      </c>
-      <c r="C476" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D476" s="142" t="s">
-        <v>29</v>
-      </c>
-      <c r="E476" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F476" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G476" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H476" s="145" t="s">
-        <v>356</v>
-      </c>
-      <c r="I476" s="150" t="s">
-        <v>275</v>
-      </c>
-      <c r="J476" s="150" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="477" spans="1:10" ht="15">
-      <c r="A477" s="142" t="s">
+      <c r="J514" s="148" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10">
+      <c r="A515" s="140" t="s">
+        <v>413</v>
+      </c>
+      <c r="B515" s="140">
+        <v>1</v>
+      </c>
+      <c r="C515" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D515" s="140" t="s">
+        <v>414</v>
+      </c>
+      <c r="E515" s="141">
+        <v>46339</v>
+      </c>
+      <c r="F515" s="142">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G515" s="142">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="H515" s="143" t="s">
+        <v>243</v>
+      </c>
+      <c r="I515" s="148" t="s">
         <v>363</v>
       </c>
-      <c r="B477" s="142">
-        <v>1</v>
-      </c>
-      <c r="C477" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D477" s="142" t="s">
-        <v>355</v>
-      </c>
-      <c r="E477" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F477" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G477" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H477" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I477" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J477" s="153" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="478" spans="1:10" ht="15">
-      <c r="A478" s="142" t="s">
-        <v>363</v>
-      </c>
-      <c r="B478" s="142">
-        <v>1</v>
-      </c>
-      <c r="C478" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D478" s="142" t="s">
-        <v>347</v>
-      </c>
-      <c r="E478" s="143">
-        <v>46336</v>
-      </c>
-      <c r="F478" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G478" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H478" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I478" s="153" t="s">
-        <v>364</v>
-      </c>
-      <c r="J478" s="150" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="479" spans="1:10">
-      <c r="A479" s="142" t="s">
-        <v>366</v>
-      </c>
-      <c r="B479" s="142">
-        <v>1</v>
-      </c>
-      <c r="C479" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D479" s="142" t="s">
-        <v>367</v>
-      </c>
-      <c r="E479" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F479" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G479" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H479" s="145" t="s">
-        <v>358</v>
-      </c>
-      <c r="I479" s="150" t="s">
-        <v>364</v>
-      </c>
-      <c r="J479" s="150"/>
-    </row>
-    <row r="480" spans="1:10">
-      <c r="A480" s="142" t="s">
-        <v>368</v>
-      </c>
-      <c r="B480" s="142">
-        <v>1</v>
-      </c>
-      <c r="C480" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D480" s="142" t="s">
-        <v>369</v>
-      </c>
-      <c r="E480" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F480" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G480" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H480" s="145" t="s">
-        <v>346</v>
-      </c>
-      <c r="I480" s="150" t="s">
-        <v>275</v>
-      </c>
-      <c r="J480" s="150" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="481" spans="1:10">
-      <c r="A481" s="142" t="s">
-        <v>368</v>
-      </c>
-      <c r="B481" s="142">
-        <v>1</v>
-      </c>
-      <c r="C481" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D481" s="142" t="s">
-        <v>370</v>
-      </c>
-      <c r="E481" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F481" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G481" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H481" s="145" t="s">
-        <v>346</v>
-      </c>
-      <c r="I481" s="150" t="s">
-        <v>349</v>
-      </c>
-      <c r="J481" s="150" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="482" spans="1:10" ht="15">
-      <c r="A482" s="142" t="s">
-        <v>368</v>
-      </c>
-      <c r="B482" s="142">
-        <v>1</v>
-      </c>
-      <c r="C482" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D482" s="142" t="s">
-        <v>372</v>
-      </c>
-      <c r="E482" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F482" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G482" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H482" s="145" t="s">
-        <v>346</v>
-      </c>
-      <c r="I482" s="156" t="s">
-        <v>242</v>
-      </c>
-      <c r="J482" s="156" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="483" spans="1:10">
-      <c r="A483" s="142" t="s">
-        <v>374</v>
-      </c>
-      <c r="B483" s="142">
-        <v>1</v>
-      </c>
-      <c r="C483" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D483" s="142" t="s">
-        <v>345</v>
-      </c>
-      <c r="E483" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F483" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G483" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H483" s="145" t="s">
-        <v>375</v>
-      </c>
-      <c r="I483" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J483" s="150"/>
-    </row>
-    <row r="484" spans="1:10" ht="15">
-      <c r="A484" s="142" t="s">
-        <v>376</v>
-      </c>
-      <c r="B484" s="142">
-        <v>1</v>
-      </c>
-      <c r="C484" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D484" s="142" t="s">
-        <v>377</v>
-      </c>
-      <c r="E484" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F484" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G484" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H484" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="I484" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J484" s="150"/>
-    </row>
-    <row r="485" spans="1:10" ht="15">
-      <c r="A485" s="142" t="s">
-        <v>378</v>
-      </c>
-      <c r="B485" s="142">
-        <v>1</v>
-      </c>
-      <c r="C485" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D485" s="142" t="s">
-        <v>377</v>
-      </c>
-      <c r="E485" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F485" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G485" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H485" s="145" t="s">
-        <v>373</v>
-      </c>
-      <c r="I485" s="153" t="s">
-        <v>358</v>
-      </c>
-      <c r="J485" s="153" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="486" spans="1:10" ht="15">
-      <c r="A486" s="142" t="s">
-        <v>378</v>
-      </c>
-      <c r="B486" s="142">
-        <v>1</v>
-      </c>
-      <c r="C486" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D486" s="142" t="s">
-        <v>379</v>
-      </c>
-      <c r="E486" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F486" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G486" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H486" s="145" t="s">
-        <v>373</v>
-      </c>
-      <c r="I486" s="153" t="s">
-        <v>346</v>
-      </c>
-      <c r="J486" s="150" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="487" spans="1:10">
-      <c r="A487" s="142" t="s">
-        <v>380</v>
-      </c>
-      <c r="B487" s="142">
-        <v>1</v>
-      </c>
-      <c r="C487" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D487" s="142" t="s">
-        <v>342</v>
-      </c>
-      <c r="E487" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F487" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G487" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H487" s="145" t="s">
-        <v>358</v>
-      </c>
-      <c r="I487" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J487" s="150"/>
-    </row>
-    <row r="488" spans="1:10" ht="15">
-      <c r="A488" s="142" t="s">
-        <v>381</v>
-      </c>
-      <c r="B488" s="142">
-        <v>1</v>
-      </c>
-      <c r="C488" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D488" s="142" t="s">
-        <v>382</v>
-      </c>
-      <c r="E488" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F488" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G488" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H488" s="145" t="s">
-        <v>383</v>
-      </c>
-      <c r="I488" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J488" s="153" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="489" spans="1:10" ht="15">
-      <c r="A489" s="142" t="s">
-        <v>381</v>
-      </c>
-      <c r="B489" s="142">
-        <v>1</v>
-      </c>
-      <c r="C489" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D489" s="142" t="s">
-        <v>345</v>
-      </c>
-      <c r="E489" s="143">
-        <v>46337</v>
-      </c>
-      <c r="F489" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G489" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H489" s="145" t="s">
-        <v>383</v>
-      </c>
-      <c r="I489" s="153" t="s">
-        <v>384</v>
-      </c>
-      <c r="J489" s="153" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="490" spans="1:10" ht="15">
-      <c r="A490" s="142" t="s">
-        <v>385</v>
-      </c>
-      <c r="B490" s="142">
-        <v>1</v>
-      </c>
-      <c r="C490" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D490" s="142" t="s">
-        <v>382</v>
-      </c>
-      <c r="E490" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F490" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G490" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H490" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I490" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J490" s="153" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="491" spans="1:10" ht="15">
-      <c r="A491" s="142" t="s">
-        <v>385</v>
-      </c>
-      <c r="B491" s="142">
-        <v>1</v>
-      </c>
-      <c r="C491" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D491" s="142" t="s">
-        <v>345</v>
-      </c>
-      <c r="E491" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F491" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G491" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H491" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I491" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J491" s="153" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="492" spans="1:10">
-      <c r="A492" s="142" t="s">
-        <v>387</v>
-      </c>
-      <c r="B492" s="142">
-        <v>1</v>
-      </c>
-      <c r="C492" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D492" s="142" t="s">
-        <v>379</v>
-      </c>
-      <c r="E492" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F492" s="144">
-        <v>0.4375</v>
-      </c>
-      <c r="G492" s="144">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H492" s="145" t="s">
-        <v>388</v>
-      </c>
-      <c r="I492" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J492" s="150"/>
-    </row>
-    <row r="493" spans="1:10" ht="15">
-      <c r="A493" s="142" t="s">
-        <v>389</v>
-      </c>
-      <c r="B493" s="142">
-        <v>1</v>
-      </c>
-      <c r="C493" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D493" s="142" t="s">
-        <v>345</v>
-      </c>
-      <c r="E493" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F493" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G493" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H493" s="145" t="s">
-        <v>352</v>
-      </c>
-      <c r="I493" s="152" t="s">
-        <v>353</v>
-      </c>
-      <c r="J493" s="153" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="494" spans="1:10" ht="15">
-      <c r="A494" s="142" t="s">
-        <v>389</v>
-      </c>
-      <c r="B494" s="142">
-        <v>1</v>
-      </c>
-      <c r="C494" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D494" s="142" t="s">
-        <v>377</v>
-      </c>
-      <c r="E494" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F494" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G494" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H494" s="145" t="s">
-        <v>352</v>
-      </c>
-      <c r="I494" s="156" t="s">
-        <v>242</v>
-      </c>
-      <c r="J494" s="150" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="495" spans="1:10" ht="15">
-      <c r="A495" s="142" t="s">
-        <v>390</v>
-      </c>
-      <c r="B495" s="142">
-        <v>1</v>
-      </c>
-      <c r="C495" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D495" s="142" t="s">
-        <v>355</v>
-      </c>
-      <c r="E495" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F495" s="144">
-        <v>0.5</v>
-      </c>
-      <c r="G495" s="144">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H495" s="145" t="s">
-        <v>352</v>
-      </c>
-      <c r="I495" s="163" t="s">
-        <v>365</v>
-      </c>
-      <c r="J495" s="150" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="496" spans="1:10" ht="15">
-      <c r="A496" s="142" t="s">
-        <v>391</v>
-      </c>
-      <c r="B496" s="142">
-        <v>1</v>
-      </c>
-      <c r="C496" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D496" s="142" t="s">
-        <v>355</v>
-      </c>
-      <c r="E496" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F496" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G496" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H496" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I496" s="153" t="s">
-        <v>352</v>
-      </c>
-      <c r="J496" s="150" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="497" spans="1:10" ht="15">
-      <c r="A497" s="142" t="s">
-        <v>391</v>
-      </c>
-      <c r="B497" s="142">
-        <v>1</v>
-      </c>
-      <c r="C497" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D497" s="142" t="s">
-        <v>347</v>
-      </c>
-      <c r="E497" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F497" s="144">
-        <v>0.5625</v>
-      </c>
-      <c r="G497" s="144">
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="H497" s="145" t="s">
-        <v>353</v>
-      </c>
-      <c r="I497" s="153" t="s">
-        <v>336</v>
-      </c>
-      <c r="J497" s="150" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="498" spans="1:10" ht="15">
-      <c r="A498" s="142" t="s">
-        <v>392</v>
-      </c>
-      <c r="B498" s="142">
-        <v>1</v>
-      </c>
-      <c r="C498" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D498" s="142" t="s">
-        <v>393</v>
-      </c>
-      <c r="E498" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F498" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G498" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H498" s="145" t="s">
-        <v>394</v>
-      </c>
-      <c r="I498" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J498" s="152" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="499" spans="1:10" ht="15">
-      <c r="A499" s="142" t="s">
-        <v>392</v>
-      </c>
-      <c r="B499" s="142">
-        <v>1</v>
-      </c>
-      <c r="C499" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D499" s="142" t="s">
-        <v>395</v>
-      </c>
-      <c r="E499" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F499" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G499" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H499" s="145" t="s">
-        <v>394</v>
-      </c>
-      <c r="I499" s="153" t="s">
-        <v>346</v>
-      </c>
-      <c r="J499" s="150" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="500" spans="1:10" ht="15">
-      <c r="A500" s="142" t="s">
-        <v>396</v>
-      </c>
-      <c r="B500" s="142">
-        <v>1</v>
-      </c>
-      <c r="C500" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D500" s="142" t="s">
-        <v>347</v>
-      </c>
-      <c r="E500" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F500" s="144">
-        <v>0.625</v>
-      </c>
-      <c r="G500" s="144">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="H500" s="145" t="s">
-        <v>388</v>
-      </c>
-      <c r="I500" s="153" t="s">
-        <v>242</v>
-      </c>
-      <c r="J500" s="150"/>
-    </row>
-    <row r="501" spans="1:10" ht="15">
-      <c r="A501" s="142" t="s">
-        <v>397</v>
-      </c>
-      <c r="B501" s="142">
-        <v>1</v>
-      </c>
-      <c r="C501" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D501" s="142" t="s">
-        <v>345</v>
-      </c>
-      <c r="E501" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F501" s="144">
-        <v>0.6875</v>
-      </c>
-      <c r="G501" s="144">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="H501" s="145" t="s">
-        <v>398</v>
-      </c>
-      <c r="I501" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J501" s="153" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="502" spans="1:10">
-      <c r="A502" s="142" t="s">
-        <v>397</v>
-      </c>
-      <c r="B502" s="142">
-        <v>1</v>
-      </c>
-      <c r="C502" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D502" s="142" t="s">
-        <v>377</v>
-      </c>
-      <c r="E502" s="143">
-        <v>46338</v>
-      </c>
-      <c r="F502" s="144">
-        <v>0.6875</v>
-      </c>
-      <c r="G502" s="144">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="H502" s="145" t="s">
-        <v>398</v>
-      </c>
-      <c r="I502" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J502" s="150" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="503" spans="1:10" ht="30.75">
-      <c r="A503" s="142" t="s">
-        <v>399</v>
-      </c>
-      <c r="B503" s="142">
-        <v>1</v>
-      </c>
-      <c r="C503" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D503" s="142" t="s">
-        <v>400</v>
-      </c>
-      <c r="E503" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F503" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G503" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H503" s="145" t="s">
-        <v>217</v>
-      </c>
-      <c r="I503" s="159" t="s">
-        <v>401</v>
-      </c>
-      <c r="J503" s="156" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="504" spans="1:10" ht="15">
-      <c r="A504" s="142" t="s">
-        <v>402</v>
-      </c>
-      <c r="B504" s="142">
-        <v>1</v>
-      </c>
-      <c r="C504" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D504" s="142" t="s">
-        <v>379</v>
-      </c>
-      <c r="E504" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F504" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G504" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H504" s="145" t="s">
-        <v>217</v>
-      </c>
-      <c r="I504" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J504" s="153" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="505" spans="1:10" ht="15">
-      <c r="A505" s="142" t="s">
-        <v>403</v>
-      </c>
-      <c r="B505" s="142">
-        <v>1</v>
-      </c>
-      <c r="C505" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D505" s="142" t="s">
-        <v>369</v>
-      </c>
-      <c r="E505" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F505" s="144">
-        <v>0.375</v>
-      </c>
-      <c r="G505" s="144">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H505" s="145" t="s">
-        <v>346</v>
-      </c>
-      <c r="I505" s="153" t="s">
-        <v>352</v>
-      </c>
-      <c r="J505" s="150"/>
-    </row>
-    <row r="506" spans="1:10">
-      <c r="A506" s="142" t="s">
-        <v>404</v>
-      </c>
-      <c r="B506" s="142">
-        <v>1</v>
-      </c>
-      <c r="C506" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D506" s="142" t="s">
-        <v>379</v>
-      </c>
-      <c r="E506" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F506" s="144">
-        <v>0.4375</v>
-      </c>
-      <c r="G506" s="144">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H506" s="145" t="s">
-        <v>352</v>
-      </c>
-      <c r="I506" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J506" s="150" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="507" spans="1:10" ht="15">
-      <c r="A507" s="142" t="s">
-        <v>404</v>
-      </c>
-      <c r="B507" s="142">
-        <v>1</v>
-      </c>
-      <c r="C507" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D507" s="142" t="s">
-        <v>355</v>
-      </c>
-      <c r="E507" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F507" s="144">
-        <v>0.4375</v>
-      </c>
-      <c r="G507" s="144">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H507" s="145" t="s">
-        <v>352</v>
-      </c>
-      <c r="I507" s="153" t="s">
-        <v>346</v>
-      </c>
-      <c r="J507" s="150" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="508" spans="1:10">
-      <c r="A508" s="142" t="s">
-        <v>405</v>
-      </c>
-      <c r="B508" s="142">
-        <v>1</v>
-      </c>
-      <c r="C508" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D508" s="142" t="s">
-        <v>342</v>
-      </c>
-      <c r="E508" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F508" s="144">
-        <v>0.4375</v>
-      </c>
-      <c r="G508" s="144">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H508" s="145" t="s">
-        <v>336</v>
-      </c>
-      <c r="I508" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J508" s="150" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="509" spans="1:10" ht="15">
-      <c r="A509" s="142" t="s">
-        <v>406</v>
-      </c>
-      <c r="B509" s="142">
-        <v>1</v>
-      </c>
-      <c r="C509" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D509" s="142" t="s">
-        <v>347</v>
-      </c>
-      <c r="E509" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F509" s="144">
-        <v>0.4375</v>
-      </c>
-      <c r="G509" s="144">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H509" s="145" t="s">
-        <v>336</v>
-      </c>
-      <c r="I509" s="152" t="s">
-        <v>242</v>
-      </c>
-      <c r="J509" s="152" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="510" spans="1:10">
-      <c r="A510" s="142" t="s">
+      <c r="J515" s="148" t="s">
         <v>407</v>
-      </c>
-      <c r="B510" s="142">
-        <v>1</v>
-      </c>
-      <c r="C510" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D510" s="142" t="s">
-        <v>345</v>
-      </c>
-      <c r="E510" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F510" s="144">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G510" s="144">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="H510" s="145" t="s">
-        <v>346</v>
-      </c>
-      <c r="I510" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J510" s="150" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="511" spans="1:10" ht="15">
-      <c r="A511" s="142" t="s">
-        <v>407</v>
-      </c>
-      <c r="B511" s="142">
-        <v>1</v>
-      </c>
-      <c r="C511" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D511" s="142" t="s">
-        <v>377</v>
-      </c>
-      <c r="E511" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F511" s="144">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G511" s="144">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="H511" s="145" t="s">
-        <v>346</v>
-      </c>
-      <c r="I511" s="163" t="s">
-        <v>409</v>
-      </c>
-      <c r="J511" s="150" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="512" spans="1:10">
-      <c r="A512" s="142" t="s">
-        <v>410</v>
-      </c>
-      <c r="B512" s="142">
-        <v>1</v>
-      </c>
-      <c r="C512" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D512" s="142" t="s">
-        <v>379</v>
-      </c>
-      <c r="E512" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F512" s="144">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G512" s="144">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="H512" s="145" t="s">
-        <v>346</v>
-      </c>
-      <c r="I512" s="150" t="s">
-        <v>337</v>
-      </c>
-      <c r="J512" s="150" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="513" spans="1:10">
-      <c r="A513" s="142" t="s">
-        <v>411</v>
-      </c>
-      <c r="B513" s="142">
-        <v>1</v>
-      </c>
-      <c r="C513" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D513" s="142" t="s">
-        <v>412</v>
-      </c>
-      <c r="E513" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F513" s="144">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="G513" s="144">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="H513" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="I513" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="J513" s="150" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="514" spans="1:10" ht="15">
-      <c r="A514" s="142" t="s">
-        <v>411</v>
-      </c>
-      <c r="B514" s="142">
-        <v>1</v>
-      </c>
-      <c r="C514" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D514" s="142" t="s">
-        <v>413</v>
-      </c>
-      <c r="E514" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F514" s="144">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="G514" s="144">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="H514" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="I514" s="153" t="s">
-        <v>346</v>
-      </c>
-      <c r="J514" s="150" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="515" spans="1:10">
-      <c r="A515" s="142" t="s">
-        <v>414</v>
-      </c>
-      <c r="B515" s="142">
-        <v>1</v>
-      </c>
-      <c r="C515" s="142" t="s">
-        <v>12</v>
-      </c>
-      <c r="D515" s="142" t="s">
-        <v>415</v>
-      </c>
-      <c r="E515" s="143">
-        <v>46339</v>
-      </c>
-      <c r="F515" s="144">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="G515" s="144">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="H515" s="145" t="s">
-        <v>242</v>
-      </c>
-      <c r="I515" s="150" t="s">
-        <v>364</v>
-      </c>
-      <c r="J515" s="150" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="516" spans="1:10">
       <c r="A516" s="115" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B516" s="115">
         <v>1</v>
@@ -20605,7 +20604,7 @@
         <v>12</v>
       </c>
       <c r="D516" s="115" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E516" s="116">
         <v>46335</v>
@@ -20617,18 +20616,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H516" s="115" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I516" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J516" s="115" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="517" spans="1:10">
       <c r="A517" s="115" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B517" s="115">
         <v>1</v>
@@ -20637,7 +20636,7 @@
         <v>12</v>
       </c>
       <c r="D517" s="115" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E517" s="116">
         <v>46335</v>
@@ -20649,18 +20648,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H517" s="115" t="s">
+        <v>416</v>
+      </c>
+      <c r="I517" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="J517" s="115" t="s">
         <v>417</v>
-      </c>
-      <c r="I517" s="115" t="s">
-        <v>239</v>
-      </c>
-      <c r="J517" s="115" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="518" spans="1:10">
       <c r="A518" s="115" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B518" s="115">
         <v>2</v>
@@ -20669,7 +20668,7 @@
         <v>12</v>
       </c>
       <c r="D518" s="115" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E518" s="116">
         <v>46335</v>
@@ -20681,18 +20680,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H518" s="115" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I518" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J518" s="115" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="519" spans="1:10">
       <c r="A519" s="115" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B519" s="115">
         <v>2</v>
@@ -20701,7 +20700,7 @@
         <v>12</v>
       </c>
       <c r="D519" s="115" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E519" s="116">
         <v>46335</v>
@@ -20713,18 +20712,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H519" s="115" t="s">
+        <v>416</v>
+      </c>
+      <c r="I519" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="J519" s="115" t="s">
         <v>417</v>
-      </c>
-      <c r="I519" s="115" t="s">
-        <v>239</v>
-      </c>
-      <c r="J519" s="115" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="520" spans="1:10">
       <c r="A520" s="115" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B520" s="115">
         <v>1</v>
@@ -20733,7 +20732,7 @@
         <v>12</v>
       </c>
       <c r="D520" s="115" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E520" s="116">
         <v>46335</v>
@@ -20745,18 +20744,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H520" s="115" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I520" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J520" s="115" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="521" spans="1:10">
       <c r="A521" s="115" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B521" s="115">
         <v>1</v>
@@ -20765,7 +20764,7 @@
         <v>12</v>
       </c>
       <c r="D521" s="115" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E521" s="116">
         <v>46335</v>
@@ -20777,18 +20776,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H521" s="115" t="s">
+        <v>416</v>
+      </c>
+      <c r="I521" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="J521" s="115" t="s">
         <v>417</v>
-      </c>
-      <c r="I521" s="115" t="s">
-        <v>239</v>
-      </c>
-      <c r="J521" s="115" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="522" spans="1:10">
       <c r="A522" s="115" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B522" s="115">
         <v>1</v>
@@ -20809,18 +20808,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H522" s="115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I522" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J522" s="115" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="523" spans="1:10">
       <c r="A523" s="115" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B523" s="115">
         <v>1</v>
@@ -20829,7 +20828,7 @@
         <v>12</v>
       </c>
       <c r="D523" s="115" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E523" s="116">
         <v>46335</v>
@@ -20841,10 +20840,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H523" s="115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I523" s="115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J523" s="115" t="s">
         <v>205</v>
@@ -20852,7 +20851,7 @@
     </row>
     <row r="524" spans="1:10">
       <c r="A524" s="115" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B524" s="115">
         <v>1</v>
@@ -20861,7 +20860,7 @@
         <v>12</v>
       </c>
       <c r="D524" s="115" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E524" s="116">
         <v>46335</v>
@@ -20873,18 +20872,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H524" s="115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I524" s="115" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J524" s="115" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="525" spans="1:10">
       <c r="A525" s="115" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B525" s="115">
         <v>3</v>
@@ -20893,7 +20892,7 @@
         <v>12</v>
       </c>
       <c r="D525" s="115" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E525" s="116">
         <v>46335</v>
@@ -20905,10 +20904,10 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H525" s="115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I525" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J525" s="115" t="s">
         <v>210</v>
@@ -20916,7 +20915,7 @@
     </row>
     <row r="526" spans="1:10">
       <c r="A526" s="115" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B526" s="115">
         <v>3</v>
@@ -20925,7 +20924,7 @@
         <v>12</v>
       </c>
       <c r="D526" s="115" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E526" s="116">
         <v>46335</v>
@@ -20937,27 +20936,27 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H526" s="115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I526" s="115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J526" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="527" spans="1:10">
       <c r="A527" s="115" t="s">
+        <v>425</v>
+      </c>
+      <c r="B527" s="115">
+        <v>1</v>
+      </c>
+      <c r="C527" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D527" s="115" t="s">
         <v>426</v>
-      </c>
-      <c r="B527" s="115">
-        <v>1</v>
-      </c>
-      <c r="C527" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D527" s="115" t="s">
-        <v>427</v>
       </c>
       <c r="E527" s="116">
         <v>46335</v>
@@ -20969,7 +20968,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H527" s="115" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I527" s="115" t="s">
         <v>217</v>
@@ -20980,7 +20979,7 @@
     </row>
     <row r="528" spans="1:10">
       <c r="A528" s="115" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B528" s="115">
         <v>1</v>
@@ -20989,7 +20988,7 @@
         <v>12</v>
       </c>
       <c r="D528" s="115" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E528" s="116">
         <v>46335</v>
@@ -21001,10 +21000,10 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H528" s="115" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I528" s="115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J528" s="115" t="s">
         <v>304</v>
@@ -21012,16 +21011,16 @@
     </row>
     <row r="529" spans="1:10">
       <c r="A529" s="115" t="s">
+        <v>429</v>
+      </c>
+      <c r="B529" s="115">
+        <v>1</v>
+      </c>
+      <c r="C529" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D529" s="115" t="s">
         <v>430</v>
-      </c>
-      <c r="B529" s="115">
-        <v>1</v>
-      </c>
-      <c r="C529" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D529" s="115" t="s">
-        <v>431</v>
       </c>
       <c r="E529" s="116">
         <v>46336</v>
@@ -21033,18 +21032,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H529" s="115" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I529" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J529" s="115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="530" spans="1:10">
       <c r="A530" s="115" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B530" s="115">
         <v>2</v>
@@ -21053,7 +21052,7 @@
         <v>12</v>
       </c>
       <c r="D530" s="115" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E530" s="116">
         <v>46336</v>
@@ -21065,27 +21064,27 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H530" s="115" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I530" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J530" s="115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="531" spans="1:10">
       <c r="A531" s="115" t="s">
+        <v>432</v>
+      </c>
+      <c r="B531" s="115">
+        <v>1</v>
+      </c>
+      <c r="C531" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D531" s="115" t="s">
         <v>433</v>
-      </c>
-      <c r="B531" s="115">
-        <v>1</v>
-      </c>
-      <c r="C531" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D531" s="115" t="s">
-        <v>434</v>
       </c>
       <c r="E531" s="116">
         <v>46336</v>
@@ -21097,10 +21096,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H531" s="115" t="s">
+        <v>434</v>
+      </c>
+      <c r="I531" s="115" t="s">
         <v>435</v>
-      </c>
-      <c r="I531" s="115" t="s">
-        <v>436</v>
       </c>
       <c r="J531" s="115" t="s">
         <v>296</v>
@@ -21108,7 +21107,7 @@
     </row>
     <row r="532" spans="1:10">
       <c r="A532" s="115" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B532" s="115">
         <v>1</v>
@@ -21117,7 +21116,7 @@
         <v>12</v>
       </c>
       <c r="D532" s="115" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E532" s="116">
         <v>46336</v>
@@ -21129,10 +21128,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H532" s="115" t="s">
+        <v>434</v>
+      </c>
+      <c r="I532" s="115" t="s">
         <v>435</v>
-      </c>
-      <c r="I532" s="115" t="s">
-        <v>436</v>
       </c>
       <c r="J532" s="115" t="s">
         <v>296</v>
@@ -21140,16 +21139,16 @@
     </row>
     <row r="533" spans="1:10">
       <c r="A533" s="115" t="s">
+        <v>437</v>
+      </c>
+      <c r="B533" s="115">
+        <v>1</v>
+      </c>
+      <c r="C533" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D533" s="115" t="s">
         <v>438</v>
-      </c>
-      <c r="B533" s="115">
-        <v>1</v>
-      </c>
-      <c r="C533" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D533" s="115" t="s">
-        <v>439</v>
       </c>
       <c r="E533" s="116">
         <v>46336</v>
@@ -21161,18 +21160,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H533" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I533" s="115" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J533" s="115" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="534" spans="1:10">
       <c r="A534" s="115" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B534" s="115">
         <v>1</v>
@@ -21181,7 +21180,7 @@
         <v>12</v>
       </c>
       <c r="D534" s="115" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E534" s="116">
         <v>46336</v>
@@ -21193,27 +21192,27 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H534" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I534" s="115" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J534" s="115" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="535" spans="1:10">
       <c r="A535" s="115" t="s">
+        <v>441</v>
+      </c>
+      <c r="B535" s="115">
+        <v>1</v>
+      </c>
+      <c r="C535" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D535" s="115" t="s">
         <v>442</v>
-      </c>
-      <c r="B535" s="115">
-        <v>1</v>
-      </c>
-      <c r="C535" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D535" s="115" t="s">
-        <v>443</v>
       </c>
       <c r="E535" s="116">
         <v>46336</v>
@@ -21225,18 +21224,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H535" s="115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I535" s="115" t="s">
         <v>210</v>
       </c>
       <c r="J535" s="115" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="536" spans="1:10">
       <c r="A536" s="115" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B536" s="115">
         <v>1</v>
@@ -21245,7 +21244,7 @@
         <v>12</v>
       </c>
       <c r="D536" s="115" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E536" s="116">
         <v>46336</v>
@@ -21257,27 +21256,27 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H536" s="115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I536" s="115" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J536" s="115" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="537" spans="1:10">
       <c r="A537" s="115" t="s">
+        <v>446</v>
+      </c>
+      <c r="B537" s="115">
+        <v>1</v>
+      </c>
+      <c r="C537" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D537" s="115" t="s">
         <v>447</v>
-      </c>
-      <c r="B537" s="115">
-        <v>1</v>
-      </c>
-      <c r="C537" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D537" s="115" t="s">
-        <v>448</v>
       </c>
       <c r="E537" s="116">
         <v>46336</v>
@@ -21289,18 +21288,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H537" s="115" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I537" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J537" s="115" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="538" spans="1:10">
       <c r="A538" s="115" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B538" s="115">
         <v>1</v>
@@ -21309,7 +21308,7 @@
         <v>12</v>
       </c>
       <c r="D538" s="115" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E538" s="116">
         <v>46336</v>
@@ -21321,27 +21320,27 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H538" s="115" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I538" s="115" t="s">
+        <v>227</v>
+      </c>
+      <c r="J538" s="115" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" ht="15">
+      <c r="A539" s="115" t="s">
+        <v>449</v>
+      </c>
+      <c r="B539" s="115">
+        <v>1</v>
+      </c>
+      <c r="C539" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D539" s="115" t="s">
         <v>450</v>
-      </c>
-      <c r="J538" s="115" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="539" spans="1:10">
-      <c r="A539" s="115" t="s">
-        <v>451</v>
-      </c>
-      <c r="B539" s="115">
-        <v>1</v>
-      </c>
-      <c r="C539" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D539" s="115" t="s">
-        <v>452</v>
       </c>
       <c r="E539" s="116">
         <v>46337</v>
@@ -21353,16 +21352,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H539" s="115" t="s">
-        <v>432</v>
-      </c>
-      <c r="I539" s="154" t="s">
-        <v>291</v>
+        <v>431</v>
+      </c>
+      <c r="I539" s="169" t="s">
+        <v>243</v>
       </c>
       <c r="J539" s="115"/>
     </row>
     <row r="540" spans="1:10">
       <c r="A540" s="115" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B540" s="115">
         <v>1</v>
@@ -21371,7 +21370,7 @@
         <v>12</v>
       </c>
       <c r="D540" s="115" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E540" s="116">
         <v>46337</v>
@@ -21383,18 +21382,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H540" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I540" s="115" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J540" s="115" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="541" spans="1:10">
       <c r="A541" s="115" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B541" s="115">
         <v>1</v>
@@ -21403,7 +21402,7 @@
         <v>12</v>
       </c>
       <c r="D541" s="115" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E541" s="116">
         <v>46337</v>
@@ -21415,18 +21414,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H541" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I541" s="115" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J541" s="115" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="542" spans="1:10">
       <c r="A542" s="115" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B542" s="115">
         <v>1</v>
@@ -21435,7 +21434,7 @@
         <v>12</v>
       </c>
       <c r="D542" s="115" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E542" s="116">
         <v>46337</v>
@@ -21447,10 +21446,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H542" s="115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I542" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J542" s="115" t="s">
         <v>214</v>
@@ -21458,7 +21457,7 @@
     </row>
     <row r="543" spans="1:10">
       <c r="A543" s="115" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B543" s="115">
         <v>1</v>
@@ -21467,7 +21466,7 @@
         <v>12</v>
       </c>
       <c r="D543" s="115" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E543" s="116">
         <v>46337</v>
@@ -21479,18 +21478,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H543" s="115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I543" s="115" t="s">
         <v>287</v>
       </c>
       <c r="J543" s="115" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="544" spans="1:10">
       <c r="A544" s="115" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B544" s="115">
         <v>1</v>
@@ -21499,7 +21498,7 @@
         <v>12</v>
       </c>
       <c r="D544" s="115" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E544" s="116">
         <v>46337</v>
@@ -21514,15 +21513,15 @@
         <v>296</v>
       </c>
       <c r="I544" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J544" s="115" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="545" spans="1:10">
       <c r="A545" s="115" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B545" s="115">
         <v>1</v>
@@ -21531,7 +21530,7 @@
         <v>12</v>
       </c>
       <c r="D545" s="115" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E545" s="116">
         <v>46337</v>
@@ -21546,7 +21545,7 @@
         <v>296</v>
       </c>
       <c r="I545" s="115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J545" s="115" t="s">
         <v>206</v>
@@ -21554,7 +21553,7 @@
     </row>
     <row r="546" spans="1:10">
       <c r="A546" s="115" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B546" s="115">
         <v>1</v>
@@ -21563,7 +21562,7 @@
         <v>12</v>
       </c>
       <c r="D546" s="115" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E546" s="116">
         <v>46337</v>
@@ -21581,12 +21580,12 @@
         <v>214</v>
       </c>
       <c r="J546" s="115" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="547" spans="1:10">
       <c r="A547" s="115" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B547" s="115">
         <v>1</v>
@@ -21607,16 +21606,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H547" s="115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I547" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J547" s="115"/>
     </row>
     <row r="548" spans="1:10">
       <c r="A548" s="115" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B548" s="115">
         <v>1</v>
@@ -21625,7 +21624,7 @@
         <v>12</v>
       </c>
       <c r="D548" s="115" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E548" s="116">
         <v>46338</v>
@@ -21637,18 +21636,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H548" s="115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I548" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J548" s="115" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="549" spans="1:10">
       <c r="A549" s="115" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B549" s="115">
         <v>1</v>
@@ -21669,18 +21668,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H549" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I549" s="115" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="J549" s="115" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="550" spans="1:10">
       <c r="A550" s="115" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B550" s="115">
         <v>1</v>
@@ -21689,7 +21688,7 @@
         <v>12</v>
       </c>
       <c r="D550" s="115" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E550" s="116">
         <v>46338</v>
@@ -21701,18 +21700,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H550" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I550" s="115" t="s">
         <v>296</v>
       </c>
       <c r="J550" s="115" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="551" spans="1:10">
       <c r="A551" s="115" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B551" s="115">
         <v>1</v>
@@ -21721,7 +21720,7 @@
         <v>12</v>
       </c>
       <c r="D551" s="115" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E551" s="116">
         <v>46338</v>
@@ -21733,10 +21732,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H551" s="115" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I551" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J551" s="115" t="s">
         <v>287</v>
@@ -21744,7 +21743,7 @@
     </row>
     <row r="552" spans="1:10">
       <c r="A552" s="115" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B552" s="115">
         <v>2</v>
@@ -21753,7 +21752,7 @@
         <v>12</v>
       </c>
       <c r="D552" s="115" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E552" s="116">
         <v>46338</v>
@@ -21765,10 +21764,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H552" s="115" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I552" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J552" s="115" t="s">
         <v>296</v>
@@ -21776,7 +21775,7 @@
     </row>
     <row r="553" spans="1:10">
       <c r="A553" s="115" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B553" s="115">
         <v>1</v>
@@ -21785,7 +21784,7 @@
         <v>12</v>
       </c>
       <c r="D553" s="115" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E553" s="116">
         <v>46338</v>
@@ -21797,10 +21796,10 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H553" s="115" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I553" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J553" s="115" t="s">
         <v>322</v>
@@ -21808,16 +21807,16 @@
     </row>
     <row r="554" spans="1:10">
       <c r="A554" s="115" t="s">
+        <v>464</v>
+      </c>
+      <c r="B554" s="115">
+        <v>1</v>
+      </c>
+      <c r="C554" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D554" s="115" t="s">
         <v>466</v>
-      </c>
-      <c r="B554" s="115">
-        <v>1</v>
-      </c>
-      <c r="C554" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="D554" s="115" t="s">
-        <v>468</v>
       </c>
       <c r="E554" s="116">
         <v>46338</v>
@@ -21829,18 +21828,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H554" s="115" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I554" s="115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J554" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="555" spans="1:10">
       <c r="A555" s="115" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B555" s="115">
         <v>1</v>
@@ -21849,7 +21848,7 @@
         <v>12</v>
       </c>
       <c r="D555" s="115" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E555" s="116">
         <v>46339</v>
@@ -21861,18 +21860,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H555" s="115" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I555" s="115" t="s">
-        <v>291</v>
-      </c>
-      <c r="J555" s="115" t="s">
-        <v>291</v>
+        <v>361</v>
+      </c>
+      <c r="J555" s="168" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="556" spans="1:10">
       <c r="A556" s="115" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B556" s="115">
         <v>1</v>
@@ -21881,7 +21880,7 @@
         <v>12</v>
       </c>
       <c r="D556" s="115" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E556" s="116">
         <v>46339</v>
@@ -21893,18 +21892,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H556" s="115" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I556" s="115" t="s">
-        <v>239</v>
-      </c>
-      <c r="J556" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="J556" s="152" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="557" spans="1:10">
       <c r="A557" s="115" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B557" s="115">
         <v>1</v>
@@ -21925,18 +21924,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H557" s="131" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I557" s="115" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J557" s="115" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="558" spans="1:10">
       <c r="A558" s="115" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B558" s="115">
         <v>1</v>
@@ -21945,7 +21944,7 @@
         <v>12</v>
       </c>
       <c r="D558" s="115" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E558" s="116">
         <v>46336</v>
@@ -21957,10 +21956,10 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H558" s="131" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I558" s="115" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J558" s="115" t="s">
         <v>210</v>
@@ -21968,7 +21967,7 @@
     </row>
     <row r="559" spans="1:10">
       <c r="A559" s="115" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B559" s="115">
         <v>1</v>
@@ -21989,10 +21988,10 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H559" s="115" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I559" s="115" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J559" s="115" t="s">
         <v>223</v>
@@ -22000,7 +21999,7 @@
     </row>
     <row r="560" spans="1:10">
       <c r="A560" s="115" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B560" s="115">
         <v>1</v>
@@ -22021,7 +22020,7 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H560" s="115" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I560" s="115" t="s">
         <v>285</v>
@@ -22030,7 +22029,7 @@
     </row>
     <row r="561" spans="1:10" ht="15">
       <c r="A561" s="115" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B561" s="115">
         <v>1</v>
@@ -22039,7 +22038,7 @@
         <v>12</v>
       </c>
       <c r="D561" s="115" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E561" s="116">
         <v>46336</v>
@@ -22054,7 +22053,7 @@
         <v>296</v>
       </c>
       <c r="I561" s="115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J561" s="130" t="s">
         <v>211</v>
@@ -22062,7 +22061,7 @@
     </row>
     <row r="562" spans="1:10">
       <c r="A562" s="115" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B562" s="115">
         <v>1</v>
@@ -22086,15 +22085,15 @@
         <v>296</v>
       </c>
       <c r="I562" s="115" t="s">
-        <v>239</v>
-      </c>
-      <c r="J562" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="J562" s="152" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="563" spans="1:10">
       <c r="A563" s="115" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B563" s="115">
         <v>1</v>
@@ -22103,7 +22102,7 @@
         <v>12</v>
       </c>
       <c r="D563" s="115" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E563" s="116">
         <v>46336</v>
@@ -22115,16 +22114,16 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H563" s="115" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I563" s="115" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="J563" s="115"/>
     </row>
     <row r="564" spans="1:10">
       <c r="A564" s="115" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B564" s="115">
         <v>1</v>
@@ -22145,7 +22144,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H564" s="115" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I564" s="115" t="s">
         <v>217</v>
@@ -22154,7 +22153,7 @@
     </row>
     <row r="565" spans="1:10">
       <c r="A565" s="115" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B565" s="115">
         <v>1</v>
@@ -22163,7 +22162,7 @@
         <v>12</v>
       </c>
       <c r="D565" s="115" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E565" s="116">
         <v>46337</v>
@@ -22184,7 +22183,7 @@
     </row>
     <row r="566" spans="1:10">
       <c r="A566" s="115" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B566" s="115">
         <v>1</v>
@@ -22207,16 +22206,16 @@
       <c r="H566" s="115" t="s">
         <v>210</v>
       </c>
-      <c r="I566" s="115" t="s">
-        <v>483</v>
+      <c r="I566" s="152" t="s">
+        <v>473</v>
       </c>
       <c r="J566" s="115" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="567" spans="1:10">
       <c r="A567" s="115" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B567" s="115">
         <v>1</v>
@@ -22239,16 +22238,16 @@
       <c r="H567" s="115" t="s">
         <v>210</v>
       </c>
-      <c r="I567" s="115" t="s">
-        <v>483</v>
+      <c r="I567" s="152" t="s">
+        <v>473</v>
       </c>
       <c r="J567" s="115" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="568" spans="1:10">
       <c r="A568" s="115" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B568" s="115">
         <v>1</v>
@@ -22274,13 +22273,13 @@
       <c r="I568" s="115" t="s">
         <v>331</v>
       </c>
-      <c r="J568" s="154" t="s">
+      <c r="J568" s="152" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="569" spans="1:10" ht="15">
       <c r="A569" s="115" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B569" s="115">
         <v>1</v>
@@ -22304,7 +22303,7 @@
         <v>217</v>
       </c>
       <c r="I569" s="130" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J569" s="115" t="s">
         <v>296</v>
@@ -22312,7 +22311,7 @@
     </row>
     <row r="570" spans="1:10">
       <c r="A570" s="115" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B570" s="115">
         <v>1</v>
@@ -22321,7 +22320,7 @@
         <v>12</v>
       </c>
       <c r="D570" s="115" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E570" s="116">
         <v>46339</v>
@@ -22341,192 +22340,192 @@
       <c r="J570" s="115"/>
     </row>
     <row r="571" spans="1:10">
-      <c r="A571" s="146" t="s">
+      <c r="A571" s="144" t="s">
+        <v>484</v>
+      </c>
+      <c r="B571" s="144">
+        <v>1</v>
+      </c>
+      <c r="C571" s="145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D571" s="144" t="s">
+        <v>430</v>
+      </c>
+      <c r="E571" s="146">
+        <v>46337</v>
+      </c>
+      <c r="F571" s="147">
+        <v>0.375</v>
+      </c>
+      <c r="G571" s="147">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="H571" s="144" t="s">
+        <v>424</v>
+      </c>
+      <c r="I571" s="144" t="s">
+        <v>452</v>
+      </c>
+      <c r="J571" s="144" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="572" spans="1:10">
+      <c r="A572" s="144" t="s">
+        <v>485</v>
+      </c>
+      <c r="B572" s="144">
+        <v>1</v>
+      </c>
+      <c r="C572" s="145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D572" s="144" t="s">
+        <v>486</v>
+      </c>
+      <c r="E572" s="146">
+        <v>46335</v>
+      </c>
+      <c r="F572" s="147">
+        <v>0.5</v>
+      </c>
+      <c r="G572" s="147">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="H572" s="144" t="s">
+        <v>424</v>
+      </c>
+      <c r="I572" s="144" t="s">
+        <v>285</v>
+      </c>
+      <c r="J572" s="144" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="573" spans="1:10">
+      <c r="A573" s="144" t="s">
         <v>487</v>
       </c>
-      <c r="B571" s="146">
-        <v>1</v>
-      </c>
-      <c r="C571" s="147" t="s">
-        <v>12</v>
-      </c>
-      <c r="D571" s="146" t="s">
-        <v>431</v>
-      </c>
-      <c r="E571" s="148">
-        <v>46337</v>
-      </c>
-      <c r="F571" s="149">
+      <c r="B573" s="144">
+        <v>1</v>
+      </c>
+      <c r="C573" s="145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D573" s="144" t="s">
+        <v>486</v>
+      </c>
+      <c r="E573" s="146">
+        <v>46335</v>
+      </c>
+      <c r="F573" s="147">
+        <v>0.4375</v>
+      </c>
+      <c r="G573" s="147">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H573" s="144" t="s">
+        <v>488</v>
+      </c>
+      <c r="I573" s="144" t="s">
+        <v>213</v>
+      </c>
+      <c r="J573" s="144"/>
+    </row>
+    <row r="574" spans="1:10">
+      <c r="A574" s="144" t="s">
+        <v>489</v>
+      </c>
+      <c r="B574" s="144">
+        <v>1</v>
+      </c>
+      <c r="C574" s="145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D574" s="144" t="s">
+        <v>75</v>
+      </c>
+      <c r="E574" s="146">
+        <v>46339</v>
+      </c>
+      <c r="F574" s="147">
+        <v>0.4375</v>
+      </c>
+      <c r="G574" s="147">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H574" s="144" t="s">
+        <v>440</v>
+      </c>
+      <c r="I574" s="144" t="s">
+        <v>347</v>
+      </c>
+      <c r="J574" s="144" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="575" spans="1:10" ht="15">
+      <c r="A575" s="144" t="s">
+        <v>489</v>
+      </c>
+      <c r="B575" s="144">
+        <v>1</v>
+      </c>
+      <c r="C575" s="145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D575" s="144" t="s">
+        <v>491</v>
+      </c>
+      <c r="E575" s="146">
+        <v>46339</v>
+      </c>
+      <c r="F575" s="147">
+        <v>0.4375</v>
+      </c>
+      <c r="G575" s="147">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="H575" s="144" t="s">
+        <v>440</v>
+      </c>
+      <c r="I575" s="144" t="s">
+        <v>492</v>
+      </c>
+      <c r="J575" s="161" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="576" spans="1:10">
+      <c r="A576" s="144" t="s">
+        <v>494</v>
+      </c>
+      <c r="B576" s="144">
+        <v>1</v>
+      </c>
+      <c r="C576" s="144" t="s">
+        <v>12</v>
+      </c>
+      <c r="D576" s="144" t="s">
+        <v>204</v>
+      </c>
+      <c r="E576" s="146">
+        <v>46338</v>
+      </c>
+      <c r="F576" s="147">
         <v>0.375</v>
       </c>
-      <c r="G571" s="149">
+      <c r="G576" s="147">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H571" s="146" t="s">
-        <v>425</v>
-      </c>
-      <c r="I571" s="146" t="s">
-        <v>454</v>
-      </c>
-      <c r="J571" s="146" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="572" spans="1:10">
-      <c r="A572" s="146" t="s">
-        <v>488</v>
-      </c>
-      <c r="B572" s="146">
-        <v>1</v>
-      </c>
-      <c r="C572" s="147" t="s">
-        <v>12</v>
-      </c>
-      <c r="D572" s="146" t="s">
-        <v>489</v>
-      </c>
-      <c r="E572" s="148">
-        <v>46335</v>
-      </c>
-      <c r="F572" s="149">
-        <v>0.5</v>
-      </c>
-      <c r="G572" s="149">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="H572" s="146" t="s">
-        <v>425</v>
-      </c>
-      <c r="I572" s="146" t="s">
-        <v>54</v>
-      </c>
-      <c r="J572" s="146" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="573" spans="1:10">
-      <c r="A573" s="146" t="s">
-        <v>490</v>
-      </c>
-      <c r="B573" s="146">
-        <v>1</v>
-      </c>
-      <c r="C573" s="147" t="s">
-        <v>12</v>
-      </c>
-      <c r="D573" s="146" t="s">
-        <v>489</v>
-      </c>
-      <c r="E573" s="148">
-        <v>46335</v>
-      </c>
-      <c r="F573" s="149">
-        <v>0.4375</v>
-      </c>
-      <c r="G573" s="149">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H573" s="146" t="s">
-        <v>491</v>
-      </c>
-      <c r="I573" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="J573" s="146"/>
-    </row>
-    <row r="574" spans="1:10">
-      <c r="A574" s="146" t="s">
-        <v>492</v>
-      </c>
-      <c r="B574" s="146">
-        <v>1</v>
-      </c>
-      <c r="C574" s="147" t="s">
-        <v>12</v>
-      </c>
-      <c r="D574" s="146" t="s">
-        <v>75</v>
-      </c>
-      <c r="E574" s="148">
-        <v>46339</v>
-      </c>
-      <c r="F574" s="149">
-        <v>0.4375</v>
-      </c>
-      <c r="G574" s="149">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H574" s="146" t="s">
-        <v>441</v>
-      </c>
-      <c r="I574" s="146" t="s">
-        <v>348</v>
-      </c>
-      <c r="J574" s="146" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="575" spans="1:10" ht="15">
-      <c r="A575" s="146" t="s">
-        <v>492</v>
-      </c>
-      <c r="B575" s="146">
-        <v>1</v>
-      </c>
-      <c r="C575" s="147" t="s">
-        <v>12</v>
-      </c>
-      <c r="D575" s="146" t="s">
-        <v>494</v>
-      </c>
-      <c r="E575" s="148">
-        <v>46339</v>
-      </c>
-      <c r="F575" s="149">
-        <v>0.4375</v>
-      </c>
-      <c r="G575" s="149">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="H575" s="146" t="s">
-        <v>441</v>
-      </c>
-      <c r="I575" s="146" t="s">
-        <v>495</v>
-      </c>
-      <c r="J575" s="164" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="576" spans="1:10">
-      <c r="A576" s="146" t="s">
-        <v>497</v>
-      </c>
-      <c r="B576" s="146">
-        <v>1</v>
-      </c>
-      <c r="C576" s="146" t="s">
-        <v>12</v>
-      </c>
-      <c r="D576" s="146" t="s">
-        <v>204</v>
-      </c>
-      <c r="E576" s="148">
-        <v>46338</v>
-      </c>
-      <c r="F576" s="149">
-        <v>0.375</v>
-      </c>
-      <c r="G576" s="149">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="H576" s="146" t="s">
+      <c r="H576" s="144" t="s">
         <v>283</v>
       </c>
-      <c r="I576" s="146" t="s">
+      <c r="I576" s="144" t="s">
         <v>213</v>
       </c>
-      <c r="J576" s="147"/>
+      <c r="J576" s="145"/>
     </row>
     <row r="577" spans="1:10">
       <c r="E577" s="113"/>
@@ -22536,7 +22535,7 @@
     </row>
     <row r="578" spans="1:10">
       <c r="A578" s="119" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B578" s="119"/>
       <c r="C578" s="119"/>
@@ -22549,16 +22548,16 @@
     </row>
     <row r="579" spans="1:10">
       <c r="A579" s="119" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B579" s="119">
         <v>1</v>
       </c>
       <c r="C579" s="119" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D579" s="119" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E579" s="120">
         <v>46335</v>
@@ -22570,7 +22569,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H579" s="119" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I579" s="119" t="s">
         <v>206</v>
@@ -22578,16 +22577,16 @@
     </row>
     <row r="580" spans="1:10">
       <c r="A580" s="119" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B580" s="119">
         <v>1</v>
       </c>
       <c r="C580" s="119" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D580" s="119" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E580" s="120">
         <v>46336</v>
@@ -22607,16 +22606,16 @@
     </row>
     <row r="581" spans="1:10">
       <c r="A581" s="119" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B581" s="119">
         <v>1</v>
       </c>
       <c r="C581" s="119" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D581" s="119" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E581" s="120">
         <v>46337</v>
@@ -22636,16 +22635,16 @@
     </row>
     <row r="582" spans="1:10">
       <c r="A582" s="119" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B582" s="119">
         <v>1</v>
       </c>
       <c r="C582" s="119" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D582" s="119" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E582" s="120">
         <v>46338</v>
@@ -22657,7 +22656,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H582" s="119" t="s">
-        <v>339</v>
+        <v>234</v>
       </c>
       <c r="I582" s="119" t="s">
         <v>206</v>
@@ -22665,16 +22664,16 @@
     </row>
     <row r="583" spans="1:10" ht="15">
       <c r="A583" s="122" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B583" s="122">
         <v>1</v>
       </c>
       <c r="C583" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D583" s="122" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E583" s="123">
         <v>46335</v>
@@ -22686,21 +22685,21 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H583" s="122" t="s">
-        <v>491</v>
-      </c>
-      <c r="I583" s="160" t="s">
+        <v>488</v>
+      </c>
+      <c r="I583" s="158" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="584" spans="1:10" ht="15">
       <c r="A584" s="122" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B584" s="122">
         <v>1</v>
       </c>
       <c r="C584" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D584" s="122" t="s">
         <v>219</v>
@@ -22715,22 +22714,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H584" s="122" t="s">
-        <v>506</v>
-      </c>
-      <c r="I584" s="161"/>
+        <v>503</v>
+      </c>
+      <c r="I584" s="159" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="585" spans="1:10" ht="15">
       <c r="A585" s="122" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B585" s="122">
         <v>1</v>
       </c>
       <c r="C585" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D585" s="122" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E585" s="123">
         <v>46336</v>
@@ -22742,19 +22743,21 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H585" s="122" t="s">
-        <v>508</v>
-      </c>
-      <c r="I585" s="161"/>
+        <v>506</v>
+      </c>
+      <c r="I585" s="159" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="586" spans="1:10" ht="15">
       <c r="A586" s="122" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B586" s="122">
         <v>1</v>
       </c>
       <c r="C586" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D586" s="122" t="s">
         <v>13</v>
@@ -22769,22 +22772,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H586" s="122" t="s">
-        <v>510</v>
-      </c>
-      <c r="I586" s="161"/>
+        <v>508</v>
+      </c>
+      <c r="I586" s="159" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="587" spans="1:10" ht="15">
       <c r="A587" s="125" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B587" s="125">
         <v>1</v>
       </c>
       <c r="C587" s="125" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D587" s="125" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E587" s="126">
         <v>46338</v>
@@ -22798,22 +22803,22 @@
       <c r="H587" s="125" t="s">
         <v>296</v>
       </c>
-      <c r="I587" s="160" t="s">
+      <c r="I587" s="158" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="588" spans="1:10" ht="15">
       <c r="A588" s="122" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B588" s="122">
         <v>1</v>
       </c>
       <c r="C588" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D588" s="122" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E588" s="123">
         <v>46339</v>
@@ -22825,24 +22830,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H588" s="122" t="s">
-        <v>514</v>
-      </c>
-      <c r="I588" s="161" t="s">
-        <v>515</v>
+        <v>512</v>
+      </c>
+      <c r="I588" s="159" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="589" spans="1:10" ht="15">
       <c r="A589" s="122" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B589" s="122">
         <v>1</v>
       </c>
       <c r="C589" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D589" s="122" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E589" s="123">
         <v>46339</v>
@@ -22854,24 +22859,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H589" s="122" t="s">
-        <v>514</v>
-      </c>
-      <c r="I589" s="161" t="s">
-        <v>515</v>
+        <v>512</v>
+      </c>
+      <c r="I589" s="159" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="590" spans="1:10" ht="15">
       <c r="A590" s="122" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B590" s="122">
         <v>1</v>
       </c>
       <c r="C590" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D590" s="122" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E590" s="123">
         <v>46339</v>
@@ -22883,24 +22888,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H590" s="122" t="s">
-        <v>514</v>
-      </c>
-      <c r="I590" s="161" t="s">
-        <v>515</v>
+        <v>512</v>
+      </c>
+      <c r="I590" s="159" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="591" spans="1:10" ht="15">
       <c r="A591" s="122" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B591" s="122">
         <v>1</v>
       </c>
       <c r="C591" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D591" s="122" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E591" s="123">
         <v>46335</v>
@@ -22912,24 +22917,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H591" s="122" t="s">
-        <v>428</v>
-      </c>
-      <c r="I591" s="161" t="s">
-        <v>519</v>
+        <v>427</v>
+      </c>
+      <c r="I591" s="159" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="592" spans="1:10" ht="15">
       <c r="A592" s="122" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B592" s="122">
         <v>1</v>
       </c>
       <c r="C592" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D592" s="122" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E592" s="123">
         <v>46336</v>
@@ -22941,24 +22946,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H592" s="122" t="s">
-        <v>491</v>
-      </c>
-      <c r="I592" s="160" t="s">
+        <v>488</v>
+      </c>
+      <c r="I592" s="158" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="593" spans="1:9" ht="15">
       <c r="A593" s="122" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B593" s="122">
         <v>1</v>
       </c>
       <c r="C593" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D593" s="122" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E593" s="123">
         <v>46337</v>
@@ -22970,24 +22975,24 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H593" s="122" t="s">
-        <v>522</v>
-      </c>
-      <c r="I593" s="160" t="s">
+        <v>520</v>
+      </c>
+      <c r="I593" s="158" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="594" spans="1:9" ht="15">
       <c r="A594" s="122" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B594" s="122">
         <v>1</v>
       </c>
       <c r="C594" s="122" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D594" s="122" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E594" s="123">
         <v>46338</v>
@@ -22999,15 +23004,15 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H594" s="122" t="s">
-        <v>508</v>
-      </c>
-      <c r="I594" s="161" t="s">
-        <v>519</v>
+        <v>506</v>
+      </c>
+      <c r="I594" s="159" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="595" spans="1:9" ht="15">
       <c r="A595" s="122" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B595" s="122">
         <v>1</v>
@@ -23016,7 +23021,7 @@
         <v>12</v>
       </c>
       <c r="D595" s="122" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E595" s="123">
         <v>46339</v>
@@ -23028,15 +23033,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H595" s="122" t="s">
-        <v>435</v>
-      </c>
-      <c r="I595" s="160" t="s">
+        <v>434</v>
+      </c>
+      <c r="I595" s="158" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="596" spans="1:9" ht="15">
       <c r="A596" s="122" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B596" s="122">
         <v>1</v>
@@ -23045,7 +23050,7 @@
         <v>12</v>
       </c>
       <c r="D596" s="122" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E596" s="123">
         <v>46339</v>
@@ -23057,13 +23062,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H596" s="122" t="s">
-        <v>435</v>
-      </c>
-      <c r="I596" s="161"/>
+        <v>434</v>
+      </c>
+      <c r="I596" s="159" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="597" spans="1:9" ht="15">
       <c r="A597" s="122" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B597" s="122">
         <v>1</v>
@@ -23072,7 +23079,7 @@
         <v>12</v>
       </c>
       <c r="D597" s="122" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E597" s="123">
         <v>46339</v>
@@ -23084,15 +23091,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H597" s="122" t="s">
-        <v>435</v>
-      </c>
-      <c r="I597" s="160" t="s">
+        <v>434</v>
+      </c>
+      <c r="I597" s="158" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="598" spans="1:9" ht="15">
       <c r="A598" s="125" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B598" s="125">
         <v>1</v>
@@ -23101,7 +23108,7 @@
         <v>12</v>
       </c>
       <c r="D598" s="125" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E598" s="126">
         <v>46339</v>
@@ -23113,13 +23120,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H598" s="125" t="s">
-        <v>435</v>
-      </c>
-      <c r="I598" s="162"/>
+        <v>434</v>
+      </c>
+      <c r="I598" s="159" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="599" spans="1:9" ht="15">
       <c r="A599" s="122" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B599" s="125">
         <v>1</v>
@@ -23140,13 +23149,15 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="H599" s="122" t="s">
-        <v>375</v>
-      </c>
-      <c r="I599" s="161"/>
+        <v>374</v>
+      </c>
+      <c r="I599" s="159" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="600" spans="1:9" ht="15">
       <c r="A600" s="122" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B600" s="125">
         <v>1</v>
@@ -23167,13 +23178,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H600" s="122" t="s">
-        <v>356</v>
-      </c>
-      <c r="I600" s="161"/>
+        <v>355</v>
+      </c>
+      <c r="I600" s="159" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="601" spans="1:9" ht="15">
       <c r="A601" s="122" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B601" s="125">
         <v>1</v>
@@ -23182,7 +23195,7 @@
         <v>12</v>
       </c>
       <c r="D601" s="122" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E601" s="123">
         <v>46336</v>
@@ -23194,9 +23207,11 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="H601" s="122" t="s">
-        <v>530</v>
-      </c>
-      <c r="I601" s="161"/>
+        <v>528</v>
+      </c>
+      <c r="I601" s="159" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="602" spans="1:9">
       <c r="A602" s="122"/>
@@ -23242,175 +23257,175 @@
     <row r="1" spans="1:38" ht="20.100000000000001">
       <c r="A1" s="28"/>
       <c r="B1" s="29"/>
-      <c r="C1" s="157" t="s">
+      <c r="C1" s="155" t="s">
+        <v>529</v>
+      </c>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="155" t="s">
+        <v>530</v>
+      </c>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="155" t="s">
         <v>531</v>
       </c>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="157" t="s">
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="155" t="s">
         <v>532</v>
       </c>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="157" t="s">
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="156"/>
+      <c r="AF1" s="155" t="s">
         <v>533</v>
       </c>
-      <c r="R1" s="158"/>
-      <c r="S1" s="158"/>
-      <c r="T1" s="158"/>
-      <c r="U1" s="158"/>
-      <c r="V1" s="158"/>
-      <c r="W1" s="158"/>
-      <c r="X1" s="157" t="s">
-        <v>534</v>
-      </c>
-      <c r="Y1" s="158"/>
-      <c r="Z1" s="158"/>
-      <c r="AA1" s="158"/>
-      <c r="AB1" s="158"/>
-      <c r="AC1" s="158"/>
-      <c r="AD1" s="158"/>
-      <c r="AE1" s="158"/>
-      <c r="AF1" s="157" t="s">
-        <v>535</v>
-      </c>
-      <c r="AG1" s="158"/>
-      <c r="AH1" s="158"/>
-      <c r="AI1" s="158"/>
-      <c r="AJ1" s="158"/>
+      <c r="AG1" s="156"/>
+      <c r="AH1" s="156"/>
+      <c r="AI1" s="156"/>
+      <c r="AJ1" s="156"/>
       <c r="AK1" s="30"/>
       <c r="AL1" s="30"/>
     </row>
     <row r="2" spans="1:38" ht="20.100000000000001">
       <c r="A2" s="31" t="s">
+        <v>534</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>536</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="D2" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="E2" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="F2" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="G2" s="34" t="s">
         <v>540</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="H2" s="35" t="s">
         <v>541</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="I2" s="33" t="s">
         <v>542</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="J2" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="K2" s="33" t="s">
         <v>544</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="L2" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="M2" s="34" t="s">
         <v>546</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="N2" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="O2" s="34" t="s">
         <v>548</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="P2" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="Q2" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="R2" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="U2" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="V2" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="W2" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="X2" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="Y2" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="Z2" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="AA2" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="AB2" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="AC2" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="AD2" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="AE2" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="AF2" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="AG2" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="AH2" s="36" t="s">
+        <v>538</v>
+      </c>
+      <c r="AI2" s="34" t="s">
         <v>550</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="AJ2" s="35" t="s">
         <v>551</v>
       </c>
-      <c r="Q2" s="33" t="s">
-        <v>544</v>
-      </c>
-      <c r="R2" s="33" t="s">
-        <v>545</v>
-      </c>
-      <c r="S2" s="33" t="s">
-        <v>546</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="U2" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="V2" s="34" t="s">
-        <v>549</v>
-      </c>
-      <c r="W2" s="34" t="s">
-        <v>550</v>
-      </c>
-      <c r="X2" s="33" t="s">
-        <v>544</v>
-      </c>
-      <c r="Y2" s="33" t="s">
-        <v>545</v>
-      </c>
-      <c r="Z2" s="33" t="s">
-        <v>546</v>
-      </c>
-      <c r="AA2" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="AB2" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="AC2" s="34" t="s">
-        <v>549</v>
-      </c>
-      <c r="AD2" s="34" t="s">
-        <v>550</v>
-      </c>
-      <c r="AE2" s="35" t="s">
-        <v>551</v>
-      </c>
-      <c r="AF2" s="33" t="s">
-        <v>538</v>
-      </c>
-      <c r="AG2" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="AH2" s="36" t="s">
-        <v>540</v>
-      </c>
-      <c r="AI2" s="34" t="s">
+      <c r="AK2" s="37" t="s">
         <v>552</v>
       </c>
-      <c r="AJ2" s="35" t="s">
+      <c r="AL2" s="35" t="s">
         <v>553</v>
-      </c>
-      <c r="AK2" s="37" t="s">
-        <v>554</v>
-      </c>
-      <c r="AL2" s="35" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:38" ht="109.5" customHeight="1">
       <c r="A3" s="38" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="41"/>
@@ -23420,58 +23435,58 @@
       <c r="H3" s="43"/>
       <c r="I3" s="40"/>
       <c r="J3" s="44" t="s">
+        <v>556</v>
+      </c>
+      <c r="K3" s="45" t="s">
+        <v>557</v>
+      </c>
+      <c r="L3" s="45" t="s">
         <v>558</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="M3" s="45" t="s">
         <v>559</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="N3" s="45" t="s">
         <v>560</v>
       </c>
-      <c r="M3" s="45" t="s">
+      <c r="O3" s="45" t="s">
         <v>561</v>
       </c>
-      <c r="N3" s="45" t="s">
+      <c r="P3" s="46" t="s">
         <v>562</v>
       </c>
-      <c r="O3" s="45" t="s">
+      <c r="Q3" s="47" t="s">
         <v>563</v>
       </c>
-      <c r="P3" s="46" t="s">
+      <c r="R3" s="48" t="s">
         <v>564</v>
       </c>
-      <c r="Q3" s="47" t="s">
+      <c r="S3" s="48" t="s">
         <v>565</v>
       </c>
-      <c r="R3" s="48" t="s">
+      <c r="T3" s="48" t="s">
         <v>566</v>
-      </c>
-      <c r="S3" s="48" t="s">
-        <v>567</v>
-      </c>
-      <c r="T3" s="48" t="s">
-        <v>568</v>
       </c>
       <c r="U3" s="42"/>
       <c r="V3" s="42"/>
       <c r="W3" s="49"/>
       <c r="X3" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="Y3" s="51" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z3" s="51" t="s">
         <v>569</v>
       </c>
-      <c r="Y3" s="51" t="s">
+      <c r="AA3" s="51" t="s">
         <v>570</v>
       </c>
-      <c r="Z3" s="51" t="s">
+      <c r="AB3" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="AA3" s="51" t="s">
+      <c r="AC3" s="51" t="s">
         <v>572</v>
-      </c>
-      <c r="AB3" s="51" t="s">
-        <v>573</v>
-      </c>
-      <c r="AC3" s="51" t="s">
-        <v>574</v>
       </c>
       <c r="AD3" s="49"/>
       <c r="AE3" s="52"/>
@@ -23485,7 +23500,7 @@
     </row>
     <row r="4" spans="1:38" ht="109.5" customHeight="1">
       <c r="A4" s="38" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B4" s="55">
         <v>30</v>
@@ -23498,58 +23513,58 @@
       <c r="H4" s="60"/>
       <c r="I4" s="56"/>
       <c r="J4" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="K4" s="62" t="s">
+        <v>557</v>
+      </c>
+      <c r="L4" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="K4" s="62" t="s">
+      <c r="M4" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="N4" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="M4" s="63" t="s">
+      <c r="O4" s="63" t="s">
         <v>561</v>
       </c>
-      <c r="N4" s="63" t="s">
+      <c r="P4" s="64" t="s">
         <v>562</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="Q4" s="65" t="s">
         <v>563</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="R4" s="66" t="s">
         <v>564</v>
       </c>
-      <c r="Q4" s="65" t="s">
+      <c r="S4" s="66" t="s">
         <v>565</v>
       </c>
-      <c r="R4" s="66" t="s">
+      <c r="T4" s="66" t="s">
         <v>566</v>
-      </c>
-      <c r="S4" s="66" t="s">
-        <v>567</v>
-      </c>
-      <c r="T4" s="66" t="s">
-        <v>568</v>
       </c>
       <c r="U4" s="58"/>
       <c r="V4" s="58"/>
       <c r="W4" s="67"/>
       <c r="X4" s="68" t="s">
+        <v>567</v>
+      </c>
+      <c r="Y4" s="69" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z4" s="69" t="s">
         <v>569</v>
       </c>
-      <c r="Y4" s="69" t="s">
+      <c r="AA4" s="69" t="s">
         <v>570</v>
       </c>
-      <c r="Z4" s="69" t="s">
+      <c r="AB4" s="69" t="s">
         <v>571</v>
       </c>
-      <c r="AA4" s="69" t="s">
+      <c r="AC4" s="69" t="s">
         <v>572</v>
-      </c>
-      <c r="AB4" s="69" t="s">
-        <v>573</v>
-      </c>
-      <c r="AC4" s="69" t="s">
-        <v>574</v>
       </c>
       <c r="AD4" s="67"/>
       <c r="AE4" s="70"/>
@@ -23563,7 +23578,7 @@
     </row>
     <row r="5" spans="1:38" ht="109.5" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B5" s="55">
         <v>50</v>
@@ -23576,58 +23591,58 @@
       <c r="H5" s="60"/>
       <c r="I5" s="56"/>
       <c r="J5" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="K5" s="62" t="s">
+        <v>557</v>
+      </c>
+      <c r="L5" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="K5" s="62" t="s">
+      <c r="M5" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="N5" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="O5" s="63" t="s">
         <v>561</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="P5" s="64" t="s">
         <v>562</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="Q5" s="65" t="s">
         <v>563</v>
       </c>
-      <c r="P5" s="64" t="s">
+      <c r="R5" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="Q5" s="65" t="s">
+      <c r="S5" s="76" t="s">
         <v>565</v>
       </c>
-      <c r="R5" s="76" t="s">
+      <c r="T5" s="76" t="s">
         <v>566</v>
-      </c>
-      <c r="S5" s="76" t="s">
-        <v>567</v>
-      </c>
-      <c r="T5" s="76" t="s">
-        <v>568</v>
       </c>
       <c r="U5" s="75"/>
       <c r="V5" s="75"/>
       <c r="W5" s="67"/>
       <c r="X5" s="68" t="s">
+        <v>567</v>
+      </c>
+      <c r="Y5" s="77" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z5" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="Y5" s="77" t="s">
+      <c r="AA5" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="Z5" s="77" t="s">
+      <c r="AB5" s="77" t="s">
         <v>571</v>
       </c>
-      <c r="AA5" s="77" t="s">
+      <c r="AC5" s="77" t="s">
         <v>572</v>
-      </c>
-      <c r="AB5" s="77" t="s">
-        <v>573</v>
-      </c>
-      <c r="AC5" s="77" t="s">
-        <v>574</v>
       </c>
       <c r="AD5" s="67"/>
       <c r="AE5" s="70"/>
@@ -23641,7 +23656,7 @@
     </row>
     <row r="6" spans="1:38" ht="109.5" customHeight="1">
       <c r="A6" s="79" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B6" s="55">
         <v>50</v>
@@ -23654,58 +23669,58 @@
       <c r="H6" s="82"/>
       <c r="I6" s="80"/>
       <c r="J6" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="K6" s="62" t="s">
+        <v>557</v>
+      </c>
+      <c r="L6" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="M6" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="N6" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="M6" s="63" t="s">
+      <c r="O6" s="63" t="s">
         <v>561</v>
       </c>
-      <c r="N6" s="63" t="s">
+      <c r="P6" s="64" t="s">
         <v>562</v>
       </c>
-      <c r="O6" s="63" t="s">
+      <c r="Q6" s="83" t="s">
         <v>563</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="R6" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="Q6" s="83" t="s">
+      <c r="S6" s="76" t="s">
         <v>565</v>
       </c>
-      <c r="R6" s="76" t="s">
+      <c r="T6" s="76" t="s">
         <v>566</v>
-      </c>
-      <c r="S6" s="76" t="s">
-        <v>567</v>
-      </c>
-      <c r="T6" s="76" t="s">
-        <v>568</v>
       </c>
       <c r="U6" s="75"/>
       <c r="V6" s="75"/>
       <c r="W6" s="84"/>
       <c r="X6" s="85" t="s">
+        <v>567</v>
+      </c>
+      <c r="Y6" s="77" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z6" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="Y6" s="77" t="s">
+      <c r="AA6" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="Z6" s="77" t="s">
+      <c r="AB6" s="77" t="s">
         <v>571</v>
       </c>
-      <c r="AA6" s="77" t="s">
+      <c r="AC6" s="77" t="s">
         <v>572</v>
-      </c>
-      <c r="AB6" s="77" t="s">
-        <v>573</v>
-      </c>
-      <c r="AC6" s="77" t="s">
-        <v>574</v>
       </c>
       <c r="AD6" s="84"/>
       <c r="AE6" s="70"/>
@@ -23719,7 +23734,7 @@
     </row>
     <row r="7" spans="1:38" ht="109.5" customHeight="1">
       <c r="A7" s="79" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B7" s="55">
         <v>50</v>
@@ -23732,58 +23747,58 @@
       <c r="H7" s="82"/>
       <c r="I7" s="80"/>
       <c r="J7" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="K7" s="62" t="s">
+        <v>557</v>
+      </c>
+      <c r="L7" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="K7" s="62" t="s">
+      <c r="M7" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="L7" s="63" t="s">
+      <c r="N7" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="M7" s="63" t="s">
+      <c r="O7" s="63" t="s">
         <v>561</v>
       </c>
-      <c r="N7" s="63" t="s">
+      <c r="P7" s="64" t="s">
         <v>562</v>
       </c>
-      <c r="O7" s="63" t="s">
+      <c r="Q7" s="83" t="s">
         <v>563</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="R7" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="Q7" s="83" t="s">
+      <c r="S7" s="76" t="s">
         <v>565</v>
       </c>
-      <c r="R7" s="76" t="s">
+      <c r="T7" s="76" t="s">
         <v>566</v>
-      </c>
-      <c r="S7" s="76" t="s">
-        <v>567</v>
-      </c>
-      <c r="T7" s="76" t="s">
-        <v>568</v>
       </c>
       <c r="U7" s="75"/>
       <c r="V7" s="75"/>
       <c r="W7" s="84"/>
       <c r="X7" s="85" t="s">
+        <v>567</v>
+      </c>
+      <c r="Y7" s="77" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z7" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="Y7" s="77" t="s">
+      <c r="AA7" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="Z7" s="77" t="s">
+      <c r="AB7" s="77" t="s">
         <v>571</v>
       </c>
-      <c r="AA7" s="77" t="s">
+      <c r="AC7" s="77" t="s">
         <v>572</v>
-      </c>
-      <c r="AB7" s="77" t="s">
-        <v>573</v>
-      </c>
-      <c r="AC7" s="77" t="s">
-        <v>574</v>
       </c>
       <c r="AD7" s="84"/>
       <c r="AE7" s="70"/>
@@ -23797,7 +23812,7 @@
     </row>
     <row r="8" spans="1:38" ht="109.5" customHeight="1">
       <c r="A8" s="79" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B8" s="55">
         <v>48</v>
@@ -23810,58 +23825,58 @@
       <c r="H8" s="82"/>
       <c r="I8" s="80"/>
       <c r="J8" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="K8" s="62" t="s">
+        <v>557</v>
+      </c>
+      <c r="L8" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="K8" s="62" t="s">
+      <c r="M8" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="N8" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="M8" s="63" t="s">
+      <c r="O8" s="63" t="s">
         <v>561</v>
       </c>
-      <c r="N8" s="63" t="s">
+      <c r="P8" s="64" t="s">
         <v>562</v>
       </c>
-      <c r="O8" s="63" t="s">
+      <c r="Q8" s="83" t="s">
         <v>563</v>
       </c>
-      <c r="P8" s="64" t="s">
+      <c r="R8" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="Q8" s="83" t="s">
+      <c r="S8" s="76" t="s">
         <v>565</v>
       </c>
-      <c r="R8" s="76" t="s">
+      <c r="T8" s="76" t="s">
         <v>566</v>
-      </c>
-      <c r="S8" s="76" t="s">
-        <v>567</v>
-      </c>
-      <c r="T8" s="76" t="s">
-        <v>568</v>
       </c>
       <c r="U8" s="75"/>
       <c r="V8" s="75"/>
       <c r="W8" s="84"/>
       <c r="X8" s="85" t="s">
+        <v>567</v>
+      </c>
+      <c r="Y8" s="77" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z8" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="Y8" s="77" t="s">
+      <c r="AA8" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="Z8" s="77" t="s">
+      <c r="AB8" s="77" t="s">
         <v>571</v>
       </c>
-      <c r="AA8" s="77" t="s">
+      <c r="AC8" s="77" t="s">
         <v>572</v>
-      </c>
-      <c r="AB8" s="77" t="s">
-        <v>573</v>
-      </c>
-      <c r="AC8" s="77" t="s">
-        <v>574</v>
       </c>
       <c r="AD8" s="84"/>
       <c r="AE8" s="70"/>
@@ -23875,7 +23890,7 @@
     </row>
     <row r="9" spans="1:38" ht="109.5" customHeight="1">
       <c r="A9" s="90" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B9" s="91">
         <v>40</v>
@@ -23883,65 +23898,65 @@
       <c r="C9" s="92"/>
       <c r="D9" s="93"/>
       <c r="E9" s="94" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F9" s="95"/>
       <c r="G9" s="95"/>
       <c r="H9" s="96"/>
       <c r="I9" s="92"/>
       <c r="J9" s="97" t="s">
+        <v>556</v>
+      </c>
+      <c r="K9" s="98" t="s">
+        <v>557</v>
+      </c>
+      <c r="L9" s="99" t="s">
         <v>558</v>
       </c>
-      <c r="K9" s="98" t="s">
+      <c r="M9" s="99" t="s">
         <v>559</v>
       </c>
-      <c r="L9" s="99" t="s">
+      <c r="N9" s="99" t="s">
         <v>560</v>
       </c>
-      <c r="M9" s="99" t="s">
+      <c r="O9" s="99" t="s">
         <v>561</v>
       </c>
-      <c r="N9" s="99" t="s">
+      <c r="P9" s="100" t="s">
         <v>562</v>
       </c>
-      <c r="O9" s="99" t="s">
+      <c r="Q9" s="101" t="s">
         <v>563</v>
       </c>
-      <c r="P9" s="100" t="s">
+      <c r="R9" s="102" t="s">
         <v>564</v>
       </c>
-      <c r="Q9" s="101" t="s">
+      <c r="S9" s="102" t="s">
         <v>565</v>
       </c>
-      <c r="R9" s="102" t="s">
+      <c r="T9" s="102" t="s">
         <v>566</v>
-      </c>
-      <c r="S9" s="102" t="s">
-        <v>567</v>
-      </c>
-      <c r="T9" s="102" t="s">
-        <v>568</v>
       </c>
       <c r="U9" s="103"/>
       <c r="V9" s="103"/>
       <c r="W9" s="104"/>
       <c r="X9" s="105" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Y9" s="106" t="s">
+        <v>568</v>
+      </c>
+      <c r="Z9" s="106" t="s">
+        <v>580</v>
+      </c>
+      <c r="AA9" s="106" t="s">
         <v>570</v>
       </c>
-      <c r="Z9" s="106" t="s">
-        <v>582</v>
-      </c>
-      <c r="AA9" s="106" t="s">
+      <c r="AB9" s="106" t="s">
+        <v>571</v>
+      </c>
+      <c r="AC9" s="106" t="s">
         <v>572</v>
-      </c>
-      <c r="AB9" s="106" t="s">
-        <v>573</v>
-      </c>
-      <c r="AC9" s="106" t="s">
-        <v>574</v>
       </c>
       <c r="AD9" s="104"/>
       <c r="AE9" s="107"/>

--- a/2026-2027-guz-vize.xlsx
+++ b/2026-2027-guz-vize.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30619"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C493007A-BD1B-4BD6-B5C0-027BD5AFD758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBE5897D-9225-433D-99AC-53F443FA5E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="580">
   <si>
     <t>Ders Kodu</t>
   </si>
@@ -1161,6 +1161,9 @@
     <t>Dr. Öğr. Üyesi Gökçe Özkılıççı</t>
   </si>
   <si>
+    <t>Prof. Dr. Seda BAĞDATLI KALKAN</t>
+  </si>
+  <si>
     <t>PSİ355</t>
   </si>
   <si>
@@ -1470,6 +1473,9 @@
     <t>YBS107</t>
   </si>
   <si>
+    <t>Dr. Öğr. Üyesi Gökçe ÖZKILIÇCI</t>
+  </si>
+  <si>
     <t>YBS201</t>
   </si>
   <si>
@@ -1512,15 +1518,9 @@
     <t>BA301</t>
   </si>
   <si>
-    <t>Dr. Öğr. Üyesi Gökçe ÖZKILIÇCI</t>
-  </si>
-  <si>
     <t>F-104</t>
   </si>
   <si>
-    <t>Prof. Dr. Seda BAĞDATLI KALKAN</t>
-  </si>
-  <si>
     <t>Dr. Öğr. Üyesi Onur YAMANER</t>
   </si>
   <si>
@@ -1552,9 +1552,6 @@
   </si>
   <si>
     <t>Dr. Öğr. Üyesi Engincan Yıldız</t>
-  </si>
-  <si>
-    <t>Büşra Bur Doğan</t>
   </si>
   <si>
     <t>İŞL576</t>
@@ -1963,7 +1960,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2087,6 +2084,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2475,7 +2478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2781,27 +2784,23 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17012,13 +17011,13 @@
       <c r="G400" s="135">
         <v>0.67708333333333337</v>
       </c>
-      <c r="H400" s="162" t="s">
+      <c r="H400" s="136" t="s">
         <v>229</v>
       </c>
-      <c r="I400" s="162" t="s">
+      <c r="I400" s="136" t="s">
         <v>234</v>
       </c>
-      <c r="J400" s="163"/>
+      <c r="J400" s="133"/>
     </row>
     <row r="401" spans="1:10">
       <c r="A401" s="133" t="s">
@@ -17042,13 +17041,13 @@
       <c r="G401" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H401" s="163" t="s">
+      <c r="H401" s="133" t="s">
         <v>217</v>
       </c>
-      <c r="I401" s="162" t="s">
+      <c r="I401" s="136" t="s">
         <v>206</v>
       </c>
-      <c r="J401" s="163" t="s">
+      <c r="J401" s="133" t="s">
         <v>236</v>
       </c>
     </row>
@@ -17074,13 +17073,13 @@
       <c r="G402" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H402" s="163" t="s">
+      <c r="H402" s="133" t="s">
         <v>217</v>
       </c>
-      <c r="I402" s="162" t="s">
+      <c r="I402" s="136" t="s">
         <v>238</v>
       </c>
-      <c r="J402" s="163" t="s">
+      <c r="J402" s="133" t="s">
         <v>223</v>
       </c>
     </row>
@@ -17106,13 +17105,13 @@
       <c r="G403" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H403" s="163" t="s">
+      <c r="H403" s="133" t="s">
         <v>217</v>
       </c>
-      <c r="I403" s="162" t="s">
+      <c r="I403" s="136" t="s">
         <v>240</v>
       </c>
-      <c r="J403" s="163" t="s">
+      <c r="J403" s="133" t="s">
         <v>241</v>
       </c>
     </row>
@@ -17138,13 +17137,13 @@
       <c r="G404" s="135">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H404" s="163" t="s">
+      <c r="H404" s="133" t="s">
         <v>217</v>
       </c>
-      <c r="I404" s="162" t="s">
+      <c r="I404" s="136" t="s">
         <v>243</v>
       </c>
-      <c r="J404" s="163" t="s">
+      <c r="J404" s="133" t="s">
         <v>244</v>
       </c>
     </row>
@@ -17170,13 +17169,13 @@
       <c r="G405" s="135">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H405" s="163" t="s">
+      <c r="H405" s="133" t="s">
         <v>205</v>
       </c>
-      <c r="I405" s="162" t="s">
+      <c r="I405" s="136" t="s">
         <v>206</v>
       </c>
-      <c r="J405" s="163"/>
+      <c r="J405" s="133"/>
     </row>
     <row r="406" spans="1:10">
       <c r="A406" s="133" t="s">
@@ -17200,13 +17199,13 @@
       <c r="G406" s="135">
         <v>0.63541666666666663</v>
       </c>
-      <c r="H406" s="163" t="s">
+      <c r="H406" s="133" t="s">
         <v>247</v>
       </c>
-      <c r="I406" s="162" t="s">
+      <c r="I406" s="136" t="s">
         <v>206</v>
       </c>
-      <c r="J406" s="163"/>
+      <c r="J406" s="133"/>
     </row>
     <row r="407" spans="1:10">
       <c r="A407" s="133" t="s">
@@ -17230,13 +17229,13 @@
       <c r="G407" s="135">
         <v>0.69791666666666663</v>
       </c>
-      <c r="H407" s="163" t="s">
+      <c r="H407" s="133" t="s">
         <v>247</v>
       </c>
-      <c r="I407" s="162" t="s">
+      <c r="I407" s="136" t="s">
         <v>206</v>
       </c>
-      <c r="J407" s="163"/>
+      <c r="J407" s="133"/>
     </row>
     <row r="408" spans="1:10">
       <c r="A408" s="137" t="s">
@@ -17260,13 +17259,13 @@
       <c r="G408" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H408" s="164" t="s">
+      <c r="H408" s="137" t="s">
         <v>251</v>
       </c>
-      <c r="I408" s="164" t="s">
+      <c r="I408" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J408" s="164" t="s">
+      <c r="J408" s="137" t="s">
         <v>252</v>
       </c>
     </row>
@@ -17292,13 +17291,13 @@
       <c r="G409" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H409" s="164" t="s">
+      <c r="H409" s="137" t="s">
         <v>251</v>
       </c>
-      <c r="I409" s="165" t="s">
+      <c r="I409" s="160" t="s">
         <v>253</v>
       </c>
-      <c r="J409" s="165" t="s">
+      <c r="J409" s="160" t="s">
         <v>240</v>
       </c>
     </row>
@@ -17324,13 +17323,13 @@
       <c r="G410" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H410" s="164" t="s">
+      <c r="H410" s="137" t="s">
         <v>251</v>
       </c>
-      <c r="I410" s="164" t="s">
+      <c r="I410" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J410" s="164"/>
+      <c r="J410" s="137"/>
     </row>
     <row r="411" spans="1:10">
       <c r="A411" s="137" t="s">
@@ -17354,13 +17353,13 @@
       <c r="G411" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H411" s="164" t="s">
+      <c r="H411" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="I411" s="164" t="s">
+      <c r="I411" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J411" s="165"/>
+      <c r="J411" s="160"/>
     </row>
     <row r="412" spans="1:10">
       <c r="A412" s="137" t="s">
@@ -17384,13 +17383,13 @@
       <c r="G412" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H412" s="164" t="s">
+      <c r="H412" s="137" t="s">
         <v>258</v>
       </c>
-      <c r="I412" s="164" t="s">
+      <c r="I412" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J412" s="165"/>
+      <c r="J412" s="160"/>
     </row>
     <row r="413" spans="1:10" ht="15">
       <c r="A413" s="137" t="s">
@@ -17414,13 +17413,13 @@
       <c r="G413" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H413" s="164" t="s">
+      <c r="H413" s="137" t="s">
         <v>258</v>
       </c>
-      <c r="I413" s="164" t="s">
+      <c r="I413" s="137" t="s">
         <v>241</v>
       </c>
-      <c r="J413" s="164"/>
+      <c r="J413" s="137"/>
     </row>
     <row r="414" spans="1:10" ht="15">
       <c r="A414" s="137" t="s">
@@ -17444,13 +17443,13 @@
       <c r="G414" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H414" s="164" t="s">
+      <c r="H414" s="137" t="s">
         <v>258</v>
       </c>
-      <c r="I414" s="164" t="s">
+      <c r="I414" s="137" t="s">
         <v>241</v>
       </c>
-      <c r="J414" s="165"/>
+      <c r="J414" s="160"/>
     </row>
     <row r="415" spans="1:10">
       <c r="A415" s="137" t="s">
@@ -17474,13 +17473,13 @@
       <c r="G415" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H415" s="164" t="s">
+      <c r="H415" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="I415" s="166" t="s">
+      <c r="I415" s="161" t="s">
         <v>240</v>
       </c>
-      <c r="J415" s="165"/>
+      <c r="J415" s="160"/>
     </row>
     <row r="416" spans="1:10" ht="15">
       <c r="A416" s="137" t="s">
@@ -17504,13 +17503,13 @@
       <c r="G416" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H416" s="164" t="s">
+      <c r="H416" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="I416" s="166" t="s">
+      <c r="I416" s="161" t="s">
         <v>240</v>
       </c>
-      <c r="J416" s="165"/>
+      <c r="J416" s="160"/>
     </row>
     <row r="417" spans="1:10" ht="15">
       <c r="A417" s="137" t="s">
@@ -17534,13 +17533,13 @@
       <c r="G417" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H417" s="164" t="s">
+      <c r="H417" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="I417" s="166" t="s">
+      <c r="I417" s="161" t="s">
         <v>240</v>
       </c>
-      <c r="J417" s="165"/>
+      <c r="J417" s="160"/>
     </row>
     <row r="418" spans="1:10">
       <c r="A418" s="137" t="s">
@@ -17564,13 +17563,13 @@
       <c r="G418" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H418" s="164" t="s">
+      <c r="H418" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="I418" s="164" t="s">
+      <c r="I418" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="J418" s="164" t="s">
+      <c r="J418" s="137" t="s">
         <v>213</v>
       </c>
     </row>
@@ -17596,13 +17595,13 @@
       <c r="G419" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H419" s="164" t="s">
+      <c r="H419" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="I419" s="164" t="s">
+      <c r="I419" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="J419" s="164" t="s">
+      <c r="J419" s="137" t="s">
         <v>213</v>
       </c>
     </row>
@@ -17628,13 +17627,13 @@
       <c r="G420" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H420" s="164" t="s">
+      <c r="H420" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="I420" s="164" t="s">
+      <c r="I420" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="J420" s="164" t="s">
+      <c r="J420" s="137" t="s">
         <v>213</v>
       </c>
     </row>
@@ -17660,13 +17659,13 @@
       <c r="G421" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H421" s="166" t="s">
+      <c r="H421" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="I421" s="164" t="s">
+      <c r="I421" s="137" t="s">
         <v>272</v>
       </c>
-      <c r="J421" s="165"/>
+      <c r="J421" s="160"/>
     </row>
     <row r="422" spans="1:10">
       <c r="A422" s="137" t="s">
@@ -17690,13 +17689,13 @@
       <c r="G422" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H422" s="166" t="s">
+      <c r="H422" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="I422" s="164" t="s">
+      <c r="I422" s="137" t="s">
         <v>272</v>
       </c>
-      <c r="J422" s="165"/>
+      <c r="J422" s="160"/>
     </row>
     <row r="423" spans="1:10">
       <c r="A423" s="137" t="s">
@@ -17720,13 +17719,13 @@
       <c r="G423" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H423" s="166" t="s">
+      <c r="H423" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="I423" s="164" t="s">
+      <c r="I423" s="137" t="s">
         <v>272</v>
       </c>
-      <c r="J423" s="165"/>
+      <c r="J423" s="160"/>
     </row>
     <row r="424" spans="1:10">
       <c r="A424" s="137" t="s">
@@ -17750,13 +17749,13 @@
       <c r="G424" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H424" s="164" t="s">
+      <c r="H424" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="I424" s="165" t="s">
+      <c r="I424" s="160" t="s">
         <v>276</v>
       </c>
-      <c r="J424" s="165" t="s">
+      <c r="J424" s="160" t="s">
         <v>277</v>
       </c>
     </row>
@@ -17782,13 +17781,13 @@
       <c r="G425" s="139">
         <v>0.55208333333333337</v>
       </c>
-      <c r="H425" s="164" t="s">
+      <c r="H425" s="137" t="s">
         <v>266</v>
       </c>
-      <c r="I425" s="165" t="s">
+      <c r="I425" s="160" t="s">
         <v>276</v>
       </c>
-      <c r="J425" s="165" t="s">
+      <c r="J425" s="160" t="s">
         <v>277</v>
       </c>
     </row>
@@ -17814,13 +17813,13 @@
       <c r="G426" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H426" s="164" t="s">
+      <c r="H426" s="137" t="s">
         <v>271</v>
       </c>
-      <c r="I426" s="165" t="s">
+      <c r="I426" s="160" t="s">
         <v>231</v>
       </c>
-      <c r="J426" s="165" t="s">
+      <c r="J426" s="160" t="s">
         <v>280</v>
       </c>
     </row>
@@ -17846,13 +17845,13 @@
       <c r="G427" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H427" s="164" t="s">
+      <c r="H427" s="137" t="s">
         <v>271</v>
       </c>
-      <c r="I427" s="166" t="s">
+      <c r="I427" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="J427" s="165" t="s">
+      <c r="J427" s="160" t="s">
         <v>277</v>
       </c>
     </row>
@@ -17878,13 +17877,13 @@
       <c r="G428" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H428" s="164" t="s">
+      <c r="H428" s="137" t="s">
         <v>271</v>
       </c>
-      <c r="I428" s="164" t="s">
+      <c r="I428" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J428" s="165" t="s">
+      <c r="J428" s="160" t="s">
         <v>272</v>
       </c>
     </row>
@@ -17910,13 +17909,13 @@
       <c r="G429" s="139">
         <v>0.61458333333333337</v>
       </c>
-      <c r="H429" s="164" t="s">
+      <c r="H429" s="137" t="s">
         <v>272</v>
       </c>
-      <c r="I429" s="164" t="s">
+      <c r="I429" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J429" s="165"/>
+      <c r="J429" s="160"/>
     </row>
     <row r="430" spans="1:10">
       <c r="A430" s="137" t="s">
@@ -17940,13 +17939,13 @@
       <c r="G430" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H430" s="164" t="s">
+      <c r="H430" s="137" t="s">
         <v>283</v>
       </c>
-      <c r="I430" s="164" t="s">
+      <c r="I430" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="J430" s="164" t="s">
+      <c r="J430" s="137" t="s">
         <v>271</v>
       </c>
     </row>
@@ -17972,13 +17971,13 @@
       <c r="G431" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H431" s="164" t="s">
+      <c r="H431" s="137" t="s">
         <v>283</v>
       </c>
-      <c r="I431" s="164" t="s">
+      <c r="I431" s="137" t="s">
         <v>206</v>
       </c>
-      <c r="J431" s="164" t="s">
+      <c r="J431" s="137" t="s">
         <v>284</v>
       </c>
     </row>
@@ -18004,13 +18003,13 @@
       <c r="G432" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H432" s="164" t="s">
+      <c r="H432" s="137" t="s">
         <v>283</v>
       </c>
-      <c r="I432" s="164" t="s">
+      <c r="I432" s="137" t="s">
         <v>285</v>
       </c>
-      <c r="J432" s="164" t="s">
+      <c r="J432" s="137" t="s">
         <v>240</v>
       </c>
     </row>
@@ -18036,13 +18035,13 @@
       <c r="G433" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H433" s="164" t="s">
+      <c r="H433" s="137" t="s">
         <v>287</v>
       </c>
-      <c r="I433" s="164" t="s">
+      <c r="I433" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J433" s="165"/>
+      <c r="J433" s="160"/>
     </row>
     <row r="434" spans="1:10">
       <c r="A434" s="137" t="s">
@@ -18066,13 +18065,13 @@
       <c r="G434" s="139">
         <v>0.67708333333333337</v>
       </c>
-      <c r="H434" s="164" t="s">
+      <c r="H434" s="137" t="s">
         <v>214</v>
       </c>
-      <c r="I434" s="164" t="s">
+      <c r="I434" s="137" t="s">
         <v>251</v>
       </c>
-      <c r="J434" s="164"/>
+      <c r="J434" s="137"/>
     </row>
     <row r="435" spans="1:10">
       <c r="A435" s="137" t="s">
@@ -18096,13 +18095,13 @@
       <c r="G435" s="139">
         <v>0.73958333333333337</v>
       </c>
-      <c r="H435" s="164" t="s">
+      <c r="H435" s="137" t="s">
         <v>272</v>
       </c>
-      <c r="I435" s="164" t="s">
+      <c r="I435" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J435" s="165"/>
+      <c r="J435" s="160"/>
     </row>
     <row r="436" spans="1:10" ht="15">
       <c r="A436" s="137" t="s">
@@ -18126,13 +18125,13 @@
       <c r="G436" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H436" s="164" t="s">
+      <c r="H436" s="137" t="s">
         <v>217</v>
       </c>
-      <c r="I436" s="164" t="s">
+      <c r="I436" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J436" s="167" t="s">
+      <c r="J436" s="152" t="s">
         <v>291</v>
       </c>
     </row>
@@ -18158,13 +18157,13 @@
       <c r="G437" s="139">
         <v>0.42708333333333331</v>
       </c>
-      <c r="H437" s="164" t="s">
+      <c r="H437" s="137" t="s">
         <v>217</v>
       </c>
-      <c r="I437" s="165" t="s">
+      <c r="I437" s="160" t="s">
         <v>292</v>
       </c>
-      <c r="J437" s="165" t="s">
+      <c r="J437" s="160" t="s">
         <v>210</v>
       </c>
     </row>
@@ -18190,13 +18189,13 @@
       <c r="G438" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H438" s="164" t="s">
+      <c r="H438" s="137" t="s">
         <v>295</v>
       </c>
-      <c r="I438" s="164" t="s">
+      <c r="I438" s="137" t="s">
         <v>213</v>
       </c>
-      <c r="J438" s="165" t="s">
+      <c r="J438" s="160" t="s">
         <v>296</v>
       </c>
     </row>
@@ -18222,13 +18221,13 @@
       <c r="G439" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H439" s="164" t="s">
+      <c r="H439" s="137" t="s">
         <v>295</v>
       </c>
-      <c r="I439" s="164" t="s">
+      <c r="I439" s="137" t="s">
         <v>285</v>
       </c>
-      <c r="J439" s="165" t="s">
+      <c r="J439" s="160" t="s">
         <v>210</v>
       </c>
     </row>
@@ -18254,13 +18253,13 @@
       <c r="G440" s="139">
         <v>0.48958333333333331</v>
       </c>
-      <c r="H440" s="164" t="s">
+      <c r="H440" s="137" t="s">
         <v>295</v>
       </c>
-      <c r="I440" s="164" t="s">
+      <c r="I440" s="137" t="s">
         <v>285</v>
       </c>
-      <c r="J440" s="165" t="s">
+      <c r="J440" s="160" t="s">
         <v>210</v>
       </c>
     </row>
@@ -19546,12 +19545,12 @@
         <v>372</v>
       </c>
       <c r="J482" s="152" t="s">
-        <v>291</v>
+        <v>373</v>
       </c>
     </row>
     <row r="483" spans="1:10">
       <c r="A483" s="140" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B483" s="140">
         <v>1</v>
@@ -19572,7 +19571,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H483" s="143" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I483" s="148" t="s">
         <v>331</v>
@@ -19581,7 +19580,7 @@
     </row>
     <row r="484" spans="1:10" ht="15">
       <c r="A484" s="140" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B484" s="140">
         <v>1</v>
@@ -19590,7 +19589,7 @@
         <v>12</v>
       </c>
       <c r="D484" s="140" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E484" s="141">
         <v>46337</v>
@@ -19611,16 +19610,16 @@
     </row>
     <row r="485" spans="1:10" ht="15">
       <c r="A485" s="140" t="s">
+        <v>378</v>
+      </c>
+      <c r="B485" s="140">
+        <v>1</v>
+      </c>
+      <c r="C485" s="140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D485" s="140" t="s">
         <v>377</v>
-      </c>
-      <c r="B485" s="140">
-        <v>1</v>
-      </c>
-      <c r="C485" s="140" t="s">
-        <v>12</v>
-      </c>
-      <c r="D485" s="140" t="s">
-        <v>376</v>
       </c>
       <c r="E485" s="141">
         <v>46337</v>
@@ -19643,7 +19642,7 @@
     </row>
     <row r="486" spans="1:10" ht="15">
       <c r="A486" s="140" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B486" s="140">
         <v>1</v>
@@ -19652,7 +19651,7 @@
         <v>12</v>
       </c>
       <c r="D486" s="140" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E486" s="141">
         <v>46337</v>
@@ -19675,7 +19674,7 @@
     </row>
     <row r="487" spans="1:10">
       <c r="A487" s="140" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B487" s="140">
         <v>1</v>
@@ -19705,7 +19704,7 @@
     </row>
     <row r="488" spans="1:10" ht="15">
       <c r="A488" s="140" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B488" s="140">
         <v>1</v>
@@ -19714,7 +19713,7 @@
         <v>12</v>
       </c>
       <c r="D488" s="140" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E488" s="141">
         <v>46337</v>
@@ -19726,7 +19725,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H488" s="143" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I488" s="148" t="s">
         <v>331</v>
@@ -19737,7 +19736,7 @@
     </row>
     <row r="489" spans="1:10" ht="15">
       <c r="A489" s="140" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B489" s="140">
         <v>1</v>
@@ -19758,10 +19757,10 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H489" s="143" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I489" s="151" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J489" s="151" t="s">
         <v>336</v>
@@ -19769,7 +19768,7 @@
     </row>
     <row r="490" spans="1:10" ht="15">
       <c r="A490" s="140" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B490" s="140">
         <v>1</v>
@@ -19778,7 +19777,7 @@
         <v>12</v>
       </c>
       <c r="D490" s="140" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E490" s="141">
         <v>46338</v>
@@ -19796,12 +19795,12 @@
         <v>331</v>
       </c>
       <c r="J490" s="151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="491" spans="1:10" ht="15">
       <c r="A491" s="140" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B491" s="140">
         <v>1</v>
@@ -19833,7 +19832,7 @@
     </row>
     <row r="492" spans="1:10">
       <c r="A492" s="140" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B492" s="140">
         <v>1</v>
@@ -19842,7 +19841,7 @@
         <v>12</v>
       </c>
       <c r="D492" s="140" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E492" s="141">
         <v>46338</v>
@@ -19854,7 +19853,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H492" s="143" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I492" s="148" t="s">
         <v>337</v>
@@ -19863,7 +19862,7 @@
     </row>
     <row r="493" spans="1:10" ht="15">
       <c r="A493" s="140" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B493" s="140">
         <v>1</v>
@@ -19895,7 +19894,7 @@
     </row>
     <row r="494" spans="1:10" ht="15">
       <c r="A494" s="140" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B494" s="140">
         <v>1</v>
@@ -19904,7 +19903,7 @@
         <v>12</v>
       </c>
       <c r="D494" s="140" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E494" s="141">
         <v>46338</v>
@@ -19927,7 +19926,7 @@
     </row>
     <row r="495" spans="1:10" ht="15">
       <c r="A495" s="140" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B495" s="140">
         <v>1</v>
@@ -19950,7 +19949,7 @@
       <c r="H495" s="143" t="s">
         <v>351</v>
       </c>
-      <c r="I495" s="160" t="s">
+      <c r="I495" s="158" t="s">
         <v>364</v>
       </c>
       <c r="J495" s="148" t="s">
@@ -19959,7 +19958,7 @@
     </row>
     <row r="496" spans="1:10" ht="15">
       <c r="A496" s="140" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B496" s="140">
         <v>1</v>
@@ -19991,7 +19990,7 @@
     </row>
     <row r="497" spans="1:10" ht="15">
       <c r="A497" s="140" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B497" s="140">
         <v>1</v>
@@ -20023,7 +20022,7 @@
     </row>
     <row r="498" spans="1:10" ht="15">
       <c r="A498" s="140" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B498" s="140">
         <v>1</v>
@@ -20032,7 +20031,7 @@
         <v>12</v>
       </c>
       <c r="D498" s="140" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E498" s="141">
         <v>46338</v>
@@ -20044,7 +20043,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H498" s="143" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I498" s="148" t="s">
         <v>331</v>
@@ -20055,7 +20054,7 @@
     </row>
     <row r="499" spans="1:10" ht="15">
       <c r="A499" s="140" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B499" s="140">
         <v>1</v>
@@ -20064,7 +20063,7 @@
         <v>12</v>
       </c>
       <c r="D499" s="140" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E499" s="141">
         <v>46338</v>
@@ -20076,7 +20075,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H499" s="143" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I499" s="151" t="s">
         <v>345</v>
@@ -20087,7 +20086,7 @@
     </row>
     <row r="500" spans="1:10" ht="15">
       <c r="A500" s="140" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B500" s="140">
         <v>1</v>
@@ -20108,7 +20107,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H500" s="143" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I500" s="151" t="s">
         <v>243</v>
@@ -20117,7 +20116,7 @@
     </row>
     <row r="501" spans="1:10" ht="15">
       <c r="A501" s="140" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B501" s="140">
         <v>1</v>
@@ -20138,7 +20137,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H501" s="143" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I501" s="148" t="s">
         <v>331</v>
@@ -20149,7 +20148,7 @@
     </row>
     <row r="502" spans="1:10">
       <c r="A502" s="140" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B502" s="140">
         <v>1</v>
@@ -20158,7 +20157,7 @@
         <v>12</v>
       </c>
       <c r="D502" s="140" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E502" s="141">
         <v>46338</v>
@@ -20170,7 +20169,7 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H502" s="143" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I502" s="148" t="s">
         <v>337</v>
@@ -20181,7 +20180,7 @@
     </row>
     <row r="503" spans="1:10" ht="30.75">
       <c r="A503" s="140" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B503" s="140">
         <v>1</v>
@@ -20190,7 +20189,7 @@
         <v>12</v>
       </c>
       <c r="D503" s="140" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E503" s="141">
         <v>46339</v>
@@ -20204,8 +20203,8 @@
       <c r="H503" s="143" t="s">
         <v>217</v>
       </c>
-      <c r="I503" s="157" t="s">
-        <v>400</v>
+      <c r="I503" s="155" t="s">
+        <v>401</v>
       </c>
       <c r="J503" s="154" t="s">
         <v>347</v>
@@ -20213,7 +20212,7 @@
     </row>
     <row r="504" spans="1:10" ht="15">
       <c r="A504" s="140" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B504" s="140">
         <v>1</v>
@@ -20222,7 +20221,7 @@
         <v>12</v>
       </c>
       <c r="D504" s="140" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E504" s="141">
         <v>46339</v>
@@ -20245,7 +20244,7 @@
     </row>
     <row r="505" spans="1:10" ht="15">
       <c r="A505" s="140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B505" s="140">
         <v>1</v>
@@ -20275,7 +20274,7 @@
     </row>
     <row r="506" spans="1:10">
       <c r="A506" s="140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B506" s="140">
         <v>1</v>
@@ -20284,7 +20283,7 @@
         <v>12</v>
       </c>
       <c r="D506" s="140" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E506" s="141">
         <v>46339</v>
@@ -20307,7 +20306,7 @@
     </row>
     <row r="507" spans="1:10" ht="15">
       <c r="A507" s="140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B507" s="140">
         <v>1</v>
@@ -20339,7 +20338,7 @@
     </row>
     <row r="508" spans="1:10">
       <c r="A508" s="140" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B508" s="140">
         <v>1</v>
@@ -20371,7 +20370,7 @@
     </row>
     <row r="509" spans="1:10" ht="15">
       <c r="A509" s="140" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B509" s="140">
         <v>1</v>
@@ -20403,7 +20402,7 @@
     </row>
     <row r="510" spans="1:10">
       <c r="A510" s="140" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B510" s="140">
         <v>1</v>
@@ -20430,12 +20429,12 @@
         <v>331</v>
       </c>
       <c r="J510" s="148" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="511" spans="1:10" ht="15">
       <c r="A511" s="140" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B511" s="140">
         <v>1</v>
@@ -20444,7 +20443,7 @@
         <v>12</v>
       </c>
       <c r="D511" s="140" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E511" s="141">
         <v>46339</v>
@@ -20458,8 +20457,8 @@
       <c r="H511" s="143" t="s">
         <v>345</v>
       </c>
-      <c r="I511" s="160" t="s">
-        <v>408</v>
+      <c r="I511" s="158" t="s">
+        <v>409</v>
       </c>
       <c r="J511" s="148" t="s">
         <v>334</v>
@@ -20467,7 +20466,7 @@
     </row>
     <row r="512" spans="1:10">
       <c r="A512" s="140" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B512" s="140">
         <v>1</v>
@@ -20476,7 +20475,7 @@
         <v>12</v>
       </c>
       <c r="D512" s="140" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E512" s="141">
         <v>46339</v>
@@ -20499,7 +20498,7 @@
     </row>
     <row r="513" spans="1:10">
       <c r="A513" s="140" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B513" s="140">
         <v>1</v>
@@ -20508,7 +20507,7 @@
         <v>12</v>
       </c>
       <c r="D513" s="140" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E513" s="141">
         <v>46339</v>
@@ -20531,7 +20530,7 @@
     </row>
     <row r="514" spans="1:10" ht="15">
       <c r="A514" s="140" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B514" s="140">
         <v>1</v>
@@ -20540,7 +20539,7 @@
         <v>12</v>
       </c>
       <c r="D514" s="140" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E514" s="141">
         <v>46339</v>
@@ -20563,7 +20562,7 @@
     </row>
     <row r="515" spans="1:10">
       <c r="A515" s="140" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B515" s="140">
         <v>1</v>
@@ -20572,7 +20571,7 @@
         <v>12</v>
       </c>
       <c r="D515" s="140" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E515" s="141">
         <v>46339</v>
@@ -20590,12 +20589,12 @@
         <v>363</v>
       </c>
       <c r="J515" s="148" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="516" spans="1:10">
       <c r="A516" s="115" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B516" s="115">
         <v>1</v>
@@ -20616,7 +20615,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H516" s="115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I516" s="115" t="s">
         <v>253</v>
@@ -20627,7 +20626,7 @@
     </row>
     <row r="517" spans="1:10">
       <c r="A517" s="115" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B517" s="115">
         <v>1</v>
@@ -20648,18 +20647,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H517" s="115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I517" s="115" t="s">
         <v>240</v>
       </c>
       <c r="J517" s="115" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="518" spans="1:10">
       <c r="A518" s="115" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B518" s="115">
         <v>2</v>
@@ -20680,7 +20679,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H518" s="115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I518" s="115" t="s">
         <v>253</v>
@@ -20691,7 +20690,7 @@
     </row>
     <row r="519" spans="1:10">
       <c r="A519" s="115" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B519" s="115">
         <v>2</v>
@@ -20712,18 +20711,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H519" s="115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I519" s="115" t="s">
         <v>240</v>
       </c>
       <c r="J519" s="115" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="520" spans="1:10">
       <c r="A520" s="115" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B520" s="115">
         <v>1</v>
@@ -20744,7 +20743,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H520" s="115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I520" s="115" t="s">
         <v>253</v>
@@ -20755,7 +20754,7 @@
     </row>
     <row r="521" spans="1:10">
       <c r="A521" s="115" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B521" s="115">
         <v>1</v>
@@ -20776,18 +20775,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H521" s="115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I521" s="115" t="s">
         <v>240</v>
       </c>
       <c r="J521" s="115" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="522" spans="1:10">
       <c r="A522" s="115" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B522" s="115">
         <v>1</v>
@@ -20808,7 +20807,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H522" s="115" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I522" s="115" t="s">
         <v>253</v>
@@ -20819,7 +20818,7 @@
     </row>
     <row r="523" spans="1:10">
       <c r="A523" s="115" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B523" s="115">
         <v>1</v>
@@ -20828,7 +20827,7 @@
         <v>12</v>
       </c>
       <c r="D523" s="115" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E523" s="116">
         <v>46335</v>
@@ -20840,7 +20839,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H523" s="115" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I523" s="115" t="s">
         <v>240</v>
@@ -20851,7 +20850,7 @@
     </row>
     <row r="524" spans="1:10">
       <c r="A524" s="115" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B524" s="115">
         <v>1</v>
@@ -20860,7 +20859,7 @@
         <v>12</v>
       </c>
       <c r="D524" s="115" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E524" s="116">
         <v>46335</v>
@@ -20872,7 +20871,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H524" s="115" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I524" s="115" t="s">
         <v>351</v>
@@ -20883,7 +20882,7 @@
     </row>
     <row r="525" spans="1:10">
       <c r="A525" s="115" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B525" s="115">
         <v>3</v>
@@ -20892,7 +20891,7 @@
         <v>12</v>
       </c>
       <c r="D525" s="115" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E525" s="116">
         <v>46335</v>
@@ -20904,7 +20903,7 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H525" s="115" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I525" s="115" t="s">
         <v>253</v>
@@ -20915,7 +20914,7 @@
     </row>
     <row r="526" spans="1:10">
       <c r="A526" s="115" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B526" s="115">
         <v>3</v>
@@ -20924,7 +20923,7 @@
         <v>12</v>
       </c>
       <c r="D526" s="115" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E526" s="116">
         <v>46335</v>
@@ -20936,18 +20935,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H526" s="115" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I526" s="115" t="s">
         <v>240</v>
       </c>
       <c r="J526" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="527" spans="1:10">
       <c r="A527" s="115" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B527" s="115">
         <v>1</v>
@@ -20956,7 +20955,7 @@
         <v>12</v>
       </c>
       <c r="D527" s="115" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E527" s="116">
         <v>46335</v>
@@ -20968,7 +20967,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H527" s="115" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I527" s="115" t="s">
         <v>217</v>
@@ -20979,7 +20978,7 @@
     </row>
     <row r="528" spans="1:10">
       <c r="A528" s="115" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B528" s="115">
         <v>1</v>
@@ -20988,7 +20987,7 @@
         <v>12</v>
       </c>
       <c r="D528" s="115" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E528" s="116">
         <v>46335</v>
@@ -21000,7 +20999,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H528" s="115" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I528" s="115" t="s">
         <v>240</v>
@@ -21011,7 +21010,7 @@
     </row>
     <row r="529" spans="1:10">
       <c r="A529" s="115" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B529" s="115">
         <v>1</v>
@@ -21020,7 +21019,7 @@
         <v>12</v>
       </c>
       <c r="D529" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E529" s="116">
         <v>46336</v>
@@ -21032,7 +21031,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H529" s="115" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I529" s="115" t="s">
         <v>253</v>
@@ -21043,7 +21042,7 @@
     </row>
     <row r="530" spans="1:10">
       <c r="A530" s="115" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B530" s="115">
         <v>2</v>
@@ -21052,7 +21051,7 @@
         <v>12</v>
       </c>
       <c r="D530" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E530" s="116">
         <v>46336</v>
@@ -21064,7 +21063,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H530" s="115" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I530" s="115" t="s">
         <v>253</v>
@@ -21075,7 +21074,7 @@
     </row>
     <row r="531" spans="1:10">
       <c r="A531" s="115" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B531" s="115">
         <v>1</v>
@@ -21084,7 +21083,7 @@
         <v>12</v>
       </c>
       <c r="D531" s="115" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E531" s="116">
         <v>46336</v>
@@ -21096,10 +21095,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H531" s="115" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I531" s="115" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J531" s="115" t="s">
         <v>296</v>
@@ -21107,7 +21106,7 @@
     </row>
     <row r="532" spans="1:10">
       <c r="A532" s="115" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B532" s="115">
         <v>1</v>
@@ -21116,7 +21115,7 @@
         <v>12</v>
       </c>
       <c r="D532" s="115" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E532" s="116">
         <v>46336</v>
@@ -21128,10 +21127,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H532" s="115" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I532" s="115" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J532" s="115" t="s">
         <v>296</v>
@@ -21139,7 +21138,7 @@
     </row>
     <row r="533" spans="1:10">
       <c r="A533" s="115" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B533" s="115">
         <v>1</v>
@@ -21148,7 +21147,7 @@
         <v>12</v>
       </c>
       <c r="D533" s="115" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E533" s="116">
         <v>46336</v>
@@ -21160,10 +21159,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H533" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I533" s="115" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J533" s="115" t="s">
         <v>361</v>
@@ -21171,7 +21170,7 @@
     </row>
     <row r="534" spans="1:10">
       <c r="A534" s="115" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B534" s="115">
         <v>1</v>
@@ -21180,7 +21179,7 @@
         <v>12</v>
       </c>
       <c r="D534" s="115" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E534" s="116">
         <v>46336</v>
@@ -21192,10 +21191,10 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H534" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I534" s="115" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J534" s="115" t="s">
         <v>370</v>
@@ -21203,7 +21202,7 @@
     </row>
     <row r="535" spans="1:10">
       <c r="A535" s="115" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B535" s="115">
         <v>1</v>
@@ -21212,7 +21211,7 @@
         <v>12</v>
       </c>
       <c r="D535" s="115" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E535" s="116">
         <v>46336</v>
@@ -21224,18 +21223,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H535" s="115" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I535" s="115" t="s">
         <v>210</v>
       </c>
       <c r="J535" s="115" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="536" spans="1:10">
       <c r="A536" s="115" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B536" s="115">
         <v>1</v>
@@ -21244,7 +21243,7 @@
         <v>12</v>
       </c>
       <c r="D536" s="115" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E536" s="116">
         <v>46336</v>
@@ -21256,18 +21255,18 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H536" s="115" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I536" s="115" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J536" s="115" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="537" spans="1:10">
       <c r="A537" s="115" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B537" s="115">
         <v>1</v>
@@ -21276,7 +21275,7 @@
         <v>12</v>
       </c>
       <c r="D537" s="115" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E537" s="116">
         <v>46336</v>
@@ -21288,7 +21287,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H537" s="115" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I537" s="115" t="s">
         <v>253</v>
@@ -21299,7 +21298,7 @@
     </row>
     <row r="538" spans="1:10">
       <c r="A538" s="115" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B538" s="115">
         <v>1</v>
@@ -21308,7 +21307,7 @@
         <v>12</v>
       </c>
       <c r="D538" s="115" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E538" s="116">
         <v>46336</v>
@@ -21320,18 +21319,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H538" s="115" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I538" s="115" t="s">
         <v>227</v>
       </c>
       <c r="J538" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="539" spans="1:10" ht="15">
       <c r="A539" s="115" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B539" s="115">
         <v>1</v>
@@ -21340,7 +21339,7 @@
         <v>12</v>
       </c>
       <c r="D539" s="115" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E539" s="116">
         <v>46337</v>
@@ -21352,16 +21351,16 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H539" s="115" t="s">
-        <v>431</v>
-      </c>
-      <c r="I539" s="169" t="s">
+        <v>432</v>
+      </c>
+      <c r="I539" s="162" t="s">
         <v>243</v>
       </c>
       <c r="J539" s="115"/>
     </row>
     <row r="540" spans="1:10">
       <c r="A540" s="115" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B540" s="115">
         <v>1</v>
@@ -21370,7 +21369,7 @@
         <v>12</v>
       </c>
       <c r="D540" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E540" s="116">
         <v>46337</v>
@@ -21382,18 +21381,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H540" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I540" s="115" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J540" s="115" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="541" spans="1:10">
       <c r="A541" s="115" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B541" s="115">
         <v>1</v>
@@ -21402,7 +21401,7 @@
         <v>12</v>
       </c>
       <c r="D541" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E541" s="116">
         <v>46337</v>
@@ -21414,18 +21413,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H541" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I541" s="115" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J541" s="115" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="542" spans="1:10">
       <c r="A542" s="115" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B542" s="115">
         <v>1</v>
@@ -21434,7 +21433,7 @@
         <v>12</v>
       </c>
       <c r="D542" s="115" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E542" s="116">
         <v>46337</v>
@@ -21446,7 +21445,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H542" s="115" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I542" s="115" t="s">
         <v>253</v>
@@ -21457,7 +21456,7 @@
     </row>
     <row r="543" spans="1:10">
       <c r="A543" s="115" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B543" s="115">
         <v>1</v>
@@ -21466,7 +21465,7 @@
         <v>12</v>
       </c>
       <c r="D543" s="115" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E543" s="116">
         <v>46337</v>
@@ -21478,18 +21477,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H543" s="115" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I543" s="115" t="s">
         <v>287</v>
       </c>
       <c r="J543" s="115" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="544" spans="1:10">
       <c r="A544" s="115" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B544" s="115">
         <v>1</v>
@@ -21498,7 +21497,7 @@
         <v>12</v>
       </c>
       <c r="D544" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E544" s="116">
         <v>46337</v>
@@ -21516,12 +21515,12 @@
         <v>253</v>
       </c>
       <c r="J544" s="115" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="545" spans="1:10">
       <c r="A545" s="115" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B545" s="115">
         <v>1</v>
@@ -21530,7 +21529,7 @@
         <v>12</v>
       </c>
       <c r="D545" s="115" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E545" s="116">
         <v>46337</v>
@@ -21553,7 +21552,7 @@
     </row>
     <row r="546" spans="1:10">
       <c r="A546" s="115" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B546" s="115">
         <v>1</v>
@@ -21562,7 +21561,7 @@
         <v>12</v>
       </c>
       <c r="D546" s="115" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E546" s="116">
         <v>46337</v>
@@ -21580,12 +21579,12 @@
         <v>214</v>
       </c>
       <c r="J546" s="115" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="547" spans="1:10">
       <c r="A547" s="115" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B547" s="115">
         <v>1</v>
@@ -21606,7 +21605,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H547" s="115" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I547" s="115" t="s">
         <v>253</v>
@@ -21615,7 +21614,7 @@
     </row>
     <row r="548" spans="1:10">
       <c r="A548" s="115" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B548" s="115">
         <v>1</v>
@@ -21624,7 +21623,7 @@
         <v>12</v>
       </c>
       <c r="D548" s="115" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E548" s="116">
         <v>46338</v>
@@ -21636,7 +21635,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H548" s="115" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I548" s="115" t="s">
         <v>253</v>
@@ -21647,7 +21646,7 @@
     </row>
     <row r="549" spans="1:10">
       <c r="A549" s="115" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B549" s="115">
         <v>1</v>
@@ -21668,7 +21667,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H549" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I549" s="115" t="s">
         <v>352</v>
@@ -21679,7 +21678,7 @@
     </row>
     <row r="550" spans="1:10">
       <c r="A550" s="115" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B550" s="115">
         <v>1</v>
@@ -21688,7 +21687,7 @@
         <v>12</v>
       </c>
       <c r="D550" s="115" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E550" s="116">
         <v>46338</v>
@@ -21700,7 +21699,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H550" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I550" s="115" t="s">
         <v>296</v>
@@ -21711,7 +21710,7 @@
     </row>
     <row r="551" spans="1:10">
       <c r="A551" s="115" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B551" s="115">
         <v>1</v>
@@ -21720,7 +21719,7 @@
         <v>12</v>
       </c>
       <c r="D551" s="115" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E551" s="116">
         <v>46338</v>
@@ -21732,7 +21731,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H551" s="115" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I551" s="115" t="s">
         <v>253</v>
@@ -21743,7 +21742,7 @@
     </row>
     <row r="552" spans="1:10">
       <c r="A552" s="115" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B552" s="115">
         <v>2</v>
@@ -21752,7 +21751,7 @@
         <v>12</v>
       </c>
       <c r="D552" s="115" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E552" s="116">
         <v>46338</v>
@@ -21764,7 +21763,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H552" s="115" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I552" s="115" t="s">
         <v>253</v>
@@ -21775,7 +21774,7 @@
     </row>
     <row r="553" spans="1:10">
       <c r="A553" s="115" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B553" s="115">
         <v>1</v>
@@ -21784,7 +21783,7 @@
         <v>12</v>
       </c>
       <c r="D553" s="115" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E553" s="116">
         <v>46338</v>
@@ -21796,7 +21795,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H553" s="115" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I553" s="115" t="s">
         <v>253</v>
@@ -21807,7 +21806,7 @@
     </row>
     <row r="554" spans="1:10">
       <c r="A554" s="115" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B554" s="115">
         <v>1</v>
@@ -21816,7 +21815,7 @@
         <v>12</v>
       </c>
       <c r="D554" s="115" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E554" s="116">
         <v>46338</v>
@@ -21828,18 +21827,18 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H554" s="115" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I554" s="115" t="s">
         <v>240</v>
       </c>
       <c r="J554" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="555" spans="1:10">
       <c r="A555" s="115" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B555" s="115">
         <v>1</v>
@@ -21848,7 +21847,7 @@
         <v>12</v>
       </c>
       <c r="D555" s="115" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E555" s="116">
         <v>46339</v>
@@ -21860,18 +21859,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H555" s="115" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I555" s="115" t="s">
         <v>361</v>
       </c>
-      <c r="J555" s="168" t="s">
+      <c r="J555" s="115" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="556" spans="1:10">
       <c r="A556" s="115" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B556" s="115">
         <v>1</v>
@@ -21880,7 +21879,7 @@
         <v>12</v>
       </c>
       <c r="D556" s="115" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E556" s="116">
         <v>46339</v>
@@ -21892,7 +21891,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H556" s="115" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I556" s="115" t="s">
         <v>240</v>
@@ -21903,7 +21902,7 @@
     </row>
     <row r="557" spans="1:10">
       <c r="A557" s="115" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B557" s="115">
         <v>1</v>
@@ -21927,15 +21926,15 @@
         <v>266</v>
       </c>
       <c r="I557" s="115" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J557" s="115" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="558" spans="1:10">
       <c r="A558" s="115" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B558" s="115">
         <v>1</v>
@@ -21944,7 +21943,7 @@
         <v>12</v>
       </c>
       <c r="D558" s="115" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E558" s="116">
         <v>46336</v>
@@ -21959,7 +21958,7 @@
         <v>266</v>
       </c>
       <c r="I558" s="115" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J558" s="115" t="s">
         <v>210</v>
@@ -21967,7 +21966,7 @@
     </row>
     <row r="559" spans="1:10">
       <c r="A559" s="115" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B559" s="115">
         <v>1</v>
@@ -21988,10 +21987,10 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H559" s="115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I559" s="115" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J559" s="115" t="s">
         <v>223</v>
@@ -21999,7 +21998,7 @@
     </row>
     <row r="560" spans="1:10">
       <c r="A560" s="115" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B560" s="115">
         <v>1</v>
@@ -22020,7 +22019,7 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H560" s="115" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I560" s="115" t="s">
         <v>285</v>
@@ -22029,7 +22028,7 @@
     </row>
     <row r="561" spans="1:10" ht="15">
       <c r="A561" s="115" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B561" s="115">
         <v>1</v>
@@ -22061,7 +22060,7 @@
     </row>
     <row r="562" spans="1:10">
       <c r="A562" s="115" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B562" s="115">
         <v>1</v>
@@ -22088,12 +22087,12 @@
         <v>240</v>
       </c>
       <c r="J562" s="152" t="s">
-        <v>291</v>
+        <v>477</v>
       </c>
     </row>
     <row r="563" spans="1:10">
       <c r="A563" s="115" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B563" s="115">
         <v>1</v>
@@ -22114,7 +22113,7 @@
         <v>0.61458333333333337</v>
       </c>
       <c r="H563" s="115" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I563" s="115" t="s">
         <v>309</v>
@@ -22123,7 +22122,7 @@
     </row>
     <row r="564" spans="1:10">
       <c r="A564" s="115" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B564" s="115">
         <v>1</v>
@@ -22144,7 +22143,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H564" s="115" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I564" s="115" t="s">
         <v>217</v>
@@ -22153,7 +22152,7 @@
     </row>
     <row r="565" spans="1:10">
       <c r="A565" s="115" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B565" s="115">
         <v>1</v>
@@ -22183,7 +22182,7 @@
     </row>
     <row r="566" spans="1:10">
       <c r="A566" s="115" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B566" s="115">
         <v>1</v>
@@ -22207,7 +22206,7 @@
         <v>210</v>
       </c>
       <c r="I566" s="152" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J566" s="115" t="s">
         <v>266</v>
@@ -22215,7 +22214,7 @@
     </row>
     <row r="567" spans="1:10">
       <c r="A567" s="115" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B567" s="115">
         <v>1</v>
@@ -22239,15 +22238,15 @@
         <v>210</v>
       </c>
       <c r="I567" s="152" t="s">
-        <v>473</v>
-      </c>
-      <c r="J567" s="115" t="s">
-        <v>408</v>
+        <v>474</v>
+      </c>
+      <c r="J567" s="165" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="568" spans="1:10">
       <c r="A568" s="115" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B568" s="115">
         <v>1</v>
@@ -22279,7 +22278,7 @@
     </row>
     <row r="569" spans="1:10" ht="15">
       <c r="A569" s="115" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B569" s="115">
         <v>1</v>
@@ -22303,7 +22302,7 @@
         <v>217</v>
       </c>
       <c r="I569" s="130" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J569" s="115" t="s">
         <v>296</v>
@@ -22311,7 +22310,7 @@
     </row>
     <row r="570" spans="1:10">
       <c r="A570" s="115" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B570" s="115">
         <v>1</v>
@@ -22320,7 +22319,7 @@
         <v>12</v>
       </c>
       <c r="D570" s="115" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E570" s="116">
         <v>46339</v>
@@ -22341,7 +22340,7 @@
     </row>
     <row r="571" spans="1:10">
       <c r="A571" s="144" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B571" s="144">
         <v>1</v>
@@ -22350,7 +22349,7 @@
         <v>12</v>
       </c>
       <c r="D571" s="144" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E571" s="146">
         <v>46337</v>
@@ -22362,18 +22361,18 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="H571" s="144" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I571" s="144" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J571" s="144" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="572" spans="1:10">
       <c r="A572" s="144" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B572" s="144">
         <v>1</v>
@@ -22382,7 +22381,7 @@
         <v>12</v>
       </c>
       <c r="D572" s="144" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E572" s="146">
         <v>46335</v>
@@ -22394,18 +22393,18 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="H572" s="144" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I572" s="144" t="s">
         <v>285</v>
       </c>
       <c r="J572" s="144" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="573" spans="1:10">
       <c r="A573" s="144" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B573" s="144">
         <v>1</v>
@@ -22414,7 +22413,7 @@
         <v>12</v>
       </c>
       <c r="D573" s="144" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E573" s="146">
         <v>46335</v>
@@ -22426,7 +22425,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H573" s="144" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I573" s="144" t="s">
         <v>213</v>
@@ -22435,7 +22434,7 @@
     </row>
     <row r="574" spans="1:10">
       <c r="A574" s="144" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B574" s="144">
         <v>1</v>
@@ -22456,18 +22455,18 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H574" s="144" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I574" s="144" t="s">
         <v>347</v>
       </c>
       <c r="J574" s="144" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
     </row>
     <row r="575" spans="1:10" ht="15">
       <c r="A575" s="144" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B575" s="144">
         <v>1</v>
@@ -22476,7 +22475,7 @@
         <v>12</v>
       </c>
       <c r="D575" s="144" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E575" s="146">
         <v>46339</v>
@@ -22488,12 +22487,12 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="H575" s="144" t="s">
-        <v>440</v>
-      </c>
-      <c r="I575" s="144" t="s">
-        <v>492</v>
-      </c>
-      <c r="J575" s="161" t="s">
+        <v>441</v>
+      </c>
+      <c r="I575" s="152" t="s">
+        <v>291</v>
+      </c>
+      <c r="J575" s="159" t="s">
         <v>493</v>
       </c>
     </row>
@@ -22557,7 +22556,7 @@
         <v>497</v>
       </c>
       <c r="D579" s="119" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E579" s="120">
         <v>46335</v>
@@ -22569,7 +22568,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H579" s="119" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I579" s="119" t="s">
         <v>206</v>
@@ -22586,7 +22585,7 @@
         <v>497</v>
       </c>
       <c r="D580" s="119" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E580" s="120">
         <v>46336</v>
@@ -22615,7 +22614,7 @@
         <v>497</v>
       </c>
       <c r="D581" s="119" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E581" s="120">
         <v>46337</v>
@@ -22644,7 +22643,7 @@
         <v>497</v>
       </c>
       <c r="D582" s="119" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E582" s="120">
         <v>46338</v>
@@ -22673,7 +22672,7 @@
         <v>497</v>
       </c>
       <c r="D583" s="122" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E583" s="123">
         <v>46335</v>
@@ -22685,9 +22684,9 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H583" s="122" t="s">
-        <v>488</v>
-      </c>
-      <c r="I583" s="158" t="s">
+        <v>490</v>
+      </c>
+      <c r="I583" s="156" t="s">
         <v>54</v>
       </c>
     </row>
@@ -22716,13 +22715,13 @@
       <c r="H584" s="122" t="s">
         <v>503</v>
       </c>
-      <c r="I584" s="159" t="s">
-        <v>504</v>
+      <c r="I584" s="157" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="585" spans="1:10" ht="15">
       <c r="A585" s="122" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B585" s="122">
         <v>1</v>
@@ -22731,7 +22730,7 @@
         <v>497</v>
       </c>
       <c r="D585" s="122" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E585" s="123">
         <v>46336</v>
@@ -22743,15 +22742,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H585" s="122" t="s">
-        <v>506</v>
-      </c>
-      <c r="I585" s="159" t="s">
+        <v>505</v>
+      </c>
+      <c r="I585" s="157" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="586" spans="1:10" ht="15">
       <c r="A586" s="122" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B586" s="122">
         <v>1</v>
@@ -22772,15 +22771,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H586" s="122" t="s">
-        <v>508</v>
-      </c>
-      <c r="I586" s="159" t="s">
-        <v>504</v>
+        <v>507</v>
+      </c>
+      <c r="I586" s="157" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="587" spans="1:10" ht="15">
       <c r="A587" s="125" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B587" s="125">
         <v>1</v>
@@ -22789,7 +22788,7 @@
         <v>497</v>
       </c>
       <c r="D587" s="125" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E587" s="126">
         <v>46338</v>
@@ -22803,13 +22802,13 @@
       <c r="H587" s="125" t="s">
         <v>296</v>
       </c>
-      <c r="I587" s="158" t="s">
+      <c r="I587" s="156" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="588" spans="1:10" ht="15">
       <c r="A588" s="122" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B588" s="122">
         <v>1</v>
@@ -22818,7 +22817,7 @@
         <v>497</v>
       </c>
       <c r="D588" s="122" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E588" s="123">
         <v>46339</v>
@@ -22830,15 +22829,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H588" s="122" t="s">
+        <v>511</v>
+      </c>
+      <c r="I588" s="157" t="s">
         <v>512</v>
-      </c>
-      <c r="I588" s="159" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="589" spans="1:10" ht="15">
       <c r="A589" s="122" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B589" s="122">
         <v>1</v>
@@ -22847,7 +22846,7 @@
         <v>497</v>
       </c>
       <c r="D589" s="122" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E589" s="123">
         <v>46339</v>
@@ -22859,15 +22858,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H589" s="122" t="s">
+        <v>511</v>
+      </c>
+      <c r="I589" s="157" t="s">
         <v>512</v>
-      </c>
-      <c r="I589" s="159" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="590" spans="1:10" ht="15">
       <c r="A590" s="122" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B590" s="122">
         <v>1</v>
@@ -22876,7 +22875,7 @@
         <v>497</v>
       </c>
       <c r="D590" s="122" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E590" s="123">
         <v>46339</v>
@@ -22888,15 +22887,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H590" s="122" t="s">
+        <v>511</v>
+      </c>
+      <c r="I590" s="157" t="s">
         <v>512</v>
-      </c>
-      <c r="I590" s="159" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="591" spans="1:10" ht="15">
       <c r="A591" s="122" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B591" s="122">
         <v>1</v>
@@ -22905,7 +22904,7 @@
         <v>497</v>
       </c>
       <c r="D591" s="122" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E591" s="123">
         <v>46335</v>
@@ -22917,15 +22916,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H591" s="122" t="s">
-        <v>427</v>
-      </c>
-      <c r="I591" s="159" t="s">
-        <v>517</v>
+        <v>428</v>
+      </c>
+      <c r="I591" s="157" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="592" spans="1:10" ht="15">
       <c r="A592" s="122" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B592" s="122">
         <v>1</v>
@@ -22934,7 +22933,7 @@
         <v>497</v>
       </c>
       <c r="D592" s="122" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E592" s="123">
         <v>46336</v>
@@ -22946,15 +22945,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H592" s="122" t="s">
-        <v>488</v>
-      </c>
-      <c r="I592" s="158" t="s">
+        <v>490</v>
+      </c>
+      <c r="I592" s="156" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="593" spans="1:9" ht="15">
       <c r="A593" s="122" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B593" s="122">
         <v>1</v>
@@ -22963,7 +22962,7 @@
         <v>497</v>
       </c>
       <c r="D593" s="122" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E593" s="123">
         <v>46337</v>
@@ -22975,15 +22974,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H593" s="122" t="s">
-        <v>520</v>
-      </c>
-      <c r="I593" s="158" t="s">
+        <v>519</v>
+      </c>
+      <c r="I593" s="156" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="594" spans="1:9" ht="15">
       <c r="A594" s="122" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B594" s="122">
         <v>1</v>
@@ -22992,7 +22991,7 @@
         <v>497</v>
       </c>
       <c r="D594" s="122" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E594" s="123">
         <v>46338</v>
@@ -23004,15 +23003,15 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="H594" s="122" t="s">
-        <v>506</v>
-      </c>
-      <c r="I594" s="159" t="s">
-        <v>517</v>
+        <v>505</v>
+      </c>
+      <c r="I594" s="157" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="595" spans="1:9" ht="15">
       <c r="A595" s="122" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B595" s="122">
         <v>1</v>
@@ -23021,7 +23020,7 @@
         <v>12</v>
       </c>
       <c r="D595" s="122" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E595" s="123">
         <v>46339</v>
@@ -23033,15 +23032,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H595" s="122" t="s">
-        <v>434</v>
-      </c>
-      <c r="I595" s="158" t="s">
+        <v>435</v>
+      </c>
+      <c r="I595" s="156" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="596" spans="1:9" ht="15">
       <c r="A596" s="122" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B596" s="122">
         <v>1</v>
@@ -23050,7 +23049,7 @@
         <v>12</v>
       </c>
       <c r="D596" s="122" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E596" s="123">
         <v>46339</v>
@@ -23062,15 +23061,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H596" s="122" t="s">
-        <v>434</v>
-      </c>
-      <c r="I596" s="159" t="s">
+        <v>435</v>
+      </c>
+      <c r="I596" s="157" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="597" spans="1:9" ht="15">
       <c r="A597" s="122" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B597" s="122">
         <v>1</v>
@@ -23079,7 +23078,7 @@
         <v>12</v>
       </c>
       <c r="D597" s="122" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E597" s="123">
         <v>46339</v>
@@ -23091,15 +23090,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H597" s="122" t="s">
-        <v>434</v>
-      </c>
-      <c r="I597" s="158" t="s">
+        <v>435</v>
+      </c>
+      <c r="I597" s="156" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="598" spans="1:9" ht="15">
       <c r="A598" s="125" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B598" s="125">
         <v>1</v>
@@ -23108,7 +23107,7 @@
         <v>12</v>
       </c>
       <c r="D598" s="125" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E598" s="126">
         <v>46339</v>
@@ -23120,15 +23119,15 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="H598" s="125" t="s">
-        <v>434</v>
-      </c>
-      <c r="I598" s="159" t="s">
+        <v>435</v>
+      </c>
+      <c r="I598" s="157" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="599" spans="1:9" ht="15">
       <c r="A599" s="122" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B599" s="125">
         <v>1</v>
@@ -23149,15 +23148,15 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="H599" s="122" t="s">
-        <v>374</v>
-      </c>
-      <c r="I599" s="159" t="s">
+        <v>375</v>
+      </c>
+      <c r="I599" s="157" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="600" spans="1:9" ht="15">
       <c r="A600" s="122" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B600" s="125">
         <v>1</v>
@@ -23180,22 +23179,22 @@
       <c r="H600" s="122" t="s">
         <v>355</v>
       </c>
-      <c r="I600" s="159" t="s">
+      <c r="I600" s="157" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="601" spans="1:9" ht="15">
       <c r="A601" s="122" t="s">
+        <v>525</v>
+      </c>
+      <c r="B601" s="125">
+        <v>1</v>
+      </c>
+      <c r="C601" s="125" t="s">
+        <v>12</v>
+      </c>
+      <c r="D601" s="122" t="s">
         <v>526</v>
-      </c>
-      <c r="B601" s="125">
-        <v>1</v>
-      </c>
-      <c r="C601" s="125" t="s">
-        <v>12</v>
-      </c>
-      <c r="D601" s="122" t="s">
-        <v>527</v>
       </c>
       <c r="E601" s="123">
         <v>46336</v>
@@ -23207,9 +23206,9 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="H601" s="122" t="s">
-        <v>528</v>
-      </c>
-      <c r="I601" s="159" t="s">
+        <v>527</v>
+      </c>
+      <c r="I601" s="157" t="s">
         <v>53</v>
       </c>
     </row>
@@ -23257,175 +23256,175 @@
     <row r="1" spans="1:38" ht="20.100000000000001">
       <c r="A1" s="28"/>
       <c r="B1" s="29"/>
-      <c r="C1" s="155" t="s">
+      <c r="C1" s="163" t="s">
+        <v>528</v>
+      </c>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="163" t="s">
         <v>529</v>
       </c>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="155" t="s">
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
+      <c r="M1" s="164"/>
+      <c r="N1" s="164"/>
+      <c r="O1" s="164"/>
+      <c r="P1" s="164"/>
+      <c r="Q1" s="163" t="s">
         <v>530</v>
       </c>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="155" t="s">
+      <c r="R1" s="164"/>
+      <c r="S1" s="164"/>
+      <c r="T1" s="164"/>
+      <c r="U1" s="164"/>
+      <c r="V1" s="164"/>
+      <c r="W1" s="164"/>
+      <c r="X1" s="163" t="s">
         <v>531</v>
       </c>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="155" t="s">
+      <c r="Y1" s="164"/>
+      <c r="Z1" s="164"/>
+      <c r="AA1" s="164"/>
+      <c r="AB1" s="164"/>
+      <c r="AC1" s="164"/>
+      <c r="AD1" s="164"/>
+      <c r="AE1" s="164"/>
+      <c r="AF1" s="163" t="s">
         <v>532</v>
       </c>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
-      <c r="AE1" s="156"/>
-      <c r="AF1" s="155" t="s">
-        <v>533</v>
-      </c>
-      <c r="AG1" s="156"/>
-      <c r="AH1" s="156"/>
-      <c r="AI1" s="156"/>
-      <c r="AJ1" s="156"/>
+      <c r="AG1" s="164"/>
+      <c r="AH1" s="164"/>
+      <c r="AI1" s="164"/>
+      <c r="AJ1" s="164"/>
       <c r="AK1" s="30"/>
       <c r="AL1" s="30"/>
     </row>
     <row r="2" spans="1:38" ht="20.100000000000001">
       <c r="A2" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="B2" s="32" t="s">
         <v>534</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="C2" s="33" t="s">
         <v>535</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="D2" s="34" t="s">
         <v>536</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="E2" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="F2" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="G2" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="H2" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="I2" s="33" t="s">
         <v>541</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="J2" s="33" t="s">
         <v>542</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="K2" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="L2" s="34" t="s">
         <v>544</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="M2" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="N2" s="34" t="s">
         <v>546</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="O2" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="P2" s="34" t="s">
         <v>548</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="Q2" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="R2" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="U2" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="V2" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="W2" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="X2" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="Y2" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="Z2" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="AA2" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="AB2" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="AC2" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="AD2" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="AE2" s="35" t="s">
+        <v>548</v>
+      </c>
+      <c r="AF2" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="AG2" s="34" t="s">
+        <v>536</v>
+      </c>
+      <c r="AH2" s="36" t="s">
+        <v>537</v>
+      </c>
+      <c r="AI2" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="Q2" s="33" t="s">
-        <v>542</v>
-      </c>
-      <c r="R2" s="33" t="s">
-        <v>543</v>
-      </c>
-      <c r="S2" s="33" t="s">
-        <v>544</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>545</v>
-      </c>
-      <c r="U2" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="V2" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="W2" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="X2" s="33" t="s">
-        <v>542</v>
-      </c>
-      <c r="Y2" s="33" t="s">
-        <v>543</v>
-      </c>
-      <c r="Z2" s="33" t="s">
-        <v>544</v>
-      </c>
-      <c r="AA2" s="34" t="s">
-        <v>545</v>
-      </c>
-      <c r="AB2" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="AC2" s="34" t="s">
-        <v>547</v>
-      </c>
-      <c r="AD2" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="AE2" s="35" t="s">
-        <v>549</v>
-      </c>
-      <c r="AF2" s="33" t="s">
-        <v>536</v>
-      </c>
-      <c r="AG2" s="34" t="s">
-        <v>537</v>
-      </c>
-      <c r="AH2" s="36" t="s">
-        <v>538</v>
-      </c>
-      <c r="AI2" s="34" t="s">
+      <c r="AJ2" s="35" t="s">
         <v>550</v>
       </c>
-      <c r="AJ2" s="35" t="s">
+      <c r="AK2" s="37" t="s">
         <v>551</v>
       </c>
-      <c r="AK2" s="37" t="s">
+      <c r="AL2" s="35" t="s">
         <v>552</v>
-      </c>
-      <c r="AL2" s="35" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="3" spans="1:38" ht="109.5" customHeight="1">
       <c r="A3" s="38" t="s">
+        <v>553</v>
+      </c>
+      <c r="B3" s="39" t="s">
         <v>554</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>555</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="41"/>
@@ -23435,58 +23434,58 @@
       <c r="H3" s="43"/>
       <c r="I3" s="40"/>
       <c r="J3" s="44" t="s">
+        <v>555</v>
+      </c>
+      <c r="K3" s="45" t="s">
         <v>556</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="L3" s="45" t="s">
         <v>557</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="M3" s="45" t="s">
         <v>558</v>
       </c>
-      <c r="M3" s="45" t="s">
+      <c r="N3" s="45" t="s">
         <v>559</v>
       </c>
-      <c r="N3" s="45" t="s">
+      <c r="O3" s="45" t="s">
         <v>560</v>
       </c>
-      <c r="O3" s="45" t="s">
+      <c r="P3" s="46" t="s">
         <v>561</v>
       </c>
-      <c r="P3" s="46" t="s">
+      <c r="Q3" s="47" t="s">
         <v>562</v>
       </c>
-      <c r="Q3" s="47" t="s">
+      <c r="R3" s="48" t="s">
         <v>563</v>
       </c>
-      <c r="R3" s="48" t="s">
+      <c r="S3" s="48" t="s">
         <v>564</v>
       </c>
-      <c r="S3" s="48" t="s">
+      <c r="T3" s="48" t="s">
         <v>565</v>
-      </c>
-      <c r="T3" s="48" t="s">
-        <v>566</v>
       </c>
       <c r="U3" s="42"/>
       <c r="V3" s="42"/>
       <c r="W3" s="49"/>
       <c r="X3" s="50" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y3" s="51" t="s">
         <v>567</v>
       </c>
-      <c r="Y3" s="51" t="s">
+      <c r="Z3" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="Z3" s="51" t="s">
+      <c r="AA3" s="51" t="s">
         <v>569</v>
       </c>
-      <c r="AA3" s="51" t="s">
+      <c r="AB3" s="51" t="s">
         <v>570</v>
       </c>
-      <c r="AB3" s="51" t="s">
+      <c r="AC3" s="51" t="s">
         <v>571</v>
-      </c>
-      <c r="AC3" s="51" t="s">
-        <v>572</v>
       </c>
       <c r="AD3" s="49"/>
       <c r="AE3" s="52"/>
@@ -23500,7 +23499,7 @@
     </row>
     <row r="4" spans="1:38" ht="109.5" customHeight="1">
       <c r="A4" s="38" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B4" s="55">
         <v>30</v>
@@ -23513,58 +23512,58 @@
       <c r="H4" s="60"/>
       <c r="I4" s="56"/>
       <c r="J4" s="61" t="s">
+        <v>555</v>
+      </c>
+      <c r="K4" s="62" t="s">
         <v>556</v>
       </c>
-      <c r="K4" s="62" t="s">
+      <c r="L4" s="63" t="s">
         <v>557</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="M4" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="M4" s="63" t="s">
+      <c r="N4" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="N4" s="63" t="s">
+      <c r="O4" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="O4" s="63" t="s">
+      <c r="P4" s="64" t="s">
         <v>561</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="Q4" s="65" t="s">
         <v>562</v>
       </c>
-      <c r="Q4" s="65" t="s">
+      <c r="R4" s="66" t="s">
         <v>563</v>
       </c>
-      <c r="R4" s="66" t="s">
+      <c r="S4" s="66" t="s">
         <v>564</v>
       </c>
-      <c r="S4" s="66" t="s">
+      <c r="T4" s="66" t="s">
         <v>565</v>
-      </c>
-      <c r="T4" s="66" t="s">
-        <v>566</v>
       </c>
       <c r="U4" s="58"/>
       <c r="V4" s="58"/>
       <c r="W4" s="67"/>
       <c r="X4" s="68" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y4" s="69" t="s">
         <v>567</v>
       </c>
-      <c r="Y4" s="69" t="s">
+      <c r="Z4" s="69" t="s">
         <v>568</v>
       </c>
-      <c r="Z4" s="69" t="s">
+      <c r="AA4" s="69" t="s">
         <v>569</v>
       </c>
-      <c r="AA4" s="69" t="s">
+      <c r="AB4" s="69" t="s">
         <v>570</v>
       </c>
-      <c r="AB4" s="69" t="s">
+      <c r="AC4" s="69" t="s">
         <v>571</v>
-      </c>
-      <c r="AC4" s="69" t="s">
-        <v>572</v>
       </c>
       <c r="AD4" s="67"/>
       <c r="AE4" s="70"/>
@@ -23578,7 +23577,7 @@
     </row>
     <row r="5" spans="1:38" ht="109.5" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B5" s="55">
         <v>50</v>
@@ -23591,58 +23590,58 @@
       <c r="H5" s="60"/>
       <c r="I5" s="56"/>
       <c r="J5" s="61" t="s">
+        <v>555</v>
+      </c>
+      <c r="K5" s="62" t="s">
         <v>556</v>
       </c>
-      <c r="K5" s="62" t="s">
+      <c r="L5" s="63" t="s">
         <v>557</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="M5" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="N5" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="O5" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="P5" s="64" t="s">
         <v>561</v>
       </c>
-      <c r="P5" s="64" t="s">
+      <c r="Q5" s="65" t="s">
         <v>562</v>
       </c>
-      <c r="Q5" s="65" t="s">
+      <c r="R5" s="76" t="s">
         <v>563</v>
       </c>
-      <c r="R5" s="76" t="s">
+      <c r="S5" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="S5" s="76" t="s">
+      <c r="T5" s="76" t="s">
         <v>565</v>
-      </c>
-      <c r="T5" s="76" t="s">
-        <v>566</v>
       </c>
       <c r="U5" s="75"/>
       <c r="V5" s="75"/>
       <c r="W5" s="67"/>
       <c r="X5" s="68" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y5" s="77" t="s">
         <v>567</v>
       </c>
-      <c r="Y5" s="77" t="s">
+      <c r="Z5" s="77" t="s">
         <v>568</v>
       </c>
-      <c r="Z5" s="77" t="s">
+      <c r="AA5" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="AA5" s="77" t="s">
+      <c r="AB5" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="AB5" s="77" t="s">
+      <c r="AC5" s="77" t="s">
         <v>571</v>
-      </c>
-      <c r="AC5" s="77" t="s">
-        <v>572</v>
       </c>
       <c r="AD5" s="67"/>
       <c r="AE5" s="70"/>
@@ -23656,7 +23655,7 @@
     </row>
     <row r="6" spans="1:38" ht="109.5" customHeight="1">
       <c r="A6" s="79" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B6" s="55">
         <v>50</v>
@@ -23669,58 +23668,58 @@
       <c r="H6" s="82"/>
       <c r="I6" s="80"/>
       <c r="J6" s="61" t="s">
+        <v>555</v>
+      </c>
+      <c r="K6" s="62" t="s">
         <v>556</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="L6" s="63" t="s">
         <v>557</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="M6" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="M6" s="63" t="s">
+      <c r="N6" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="N6" s="63" t="s">
+      <c r="O6" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="O6" s="63" t="s">
+      <c r="P6" s="64" t="s">
         <v>561</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="Q6" s="83" t="s">
         <v>562</v>
       </c>
-      <c r="Q6" s="83" t="s">
+      <c r="R6" s="76" t="s">
         <v>563</v>
       </c>
-      <c r="R6" s="76" t="s">
+      <c r="S6" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="S6" s="76" t="s">
+      <c r="T6" s="76" t="s">
         <v>565</v>
-      </c>
-      <c r="T6" s="76" t="s">
-        <v>566</v>
       </c>
       <c r="U6" s="75"/>
       <c r="V6" s="75"/>
       <c r="W6" s="84"/>
       <c r="X6" s="85" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y6" s="77" t="s">
         <v>567</v>
       </c>
-      <c r="Y6" s="77" t="s">
+      <c r="Z6" s="77" t="s">
         <v>568</v>
       </c>
-      <c r="Z6" s="77" t="s">
+      <c r="AA6" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="AA6" s="77" t="s">
+      <c r="AB6" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="AB6" s="77" t="s">
+      <c r="AC6" s="77" t="s">
         <v>571</v>
-      </c>
-      <c r="AC6" s="77" t="s">
-        <v>572</v>
       </c>
       <c r="AD6" s="84"/>
       <c r="AE6" s="70"/>
@@ -23734,7 +23733,7 @@
     </row>
     <row r="7" spans="1:38" ht="109.5" customHeight="1">
       <c r="A7" s="79" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B7" s="55">
         <v>50</v>
@@ -23747,58 +23746,58 @@
       <c r="H7" s="82"/>
       <c r="I7" s="80"/>
       <c r="J7" s="61" t="s">
+        <v>555</v>
+      </c>
+      <c r="K7" s="62" t="s">
         <v>556</v>
       </c>
-      <c r="K7" s="62" t="s">
+      <c r="L7" s="63" t="s">
         <v>557</v>
       </c>
-      <c r="L7" s="63" t="s">
+      <c r="M7" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="M7" s="63" t="s">
+      <c r="N7" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="N7" s="63" t="s">
+      <c r="O7" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="O7" s="63" t="s">
+      <c r="P7" s="64" t="s">
         <v>561</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="Q7" s="83" t="s">
         <v>562</v>
       </c>
-      <c r="Q7" s="83" t="s">
+      <c r="R7" s="76" t="s">
         <v>563</v>
       </c>
-      <c r="R7" s="76" t="s">
+      <c r="S7" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="S7" s="76" t="s">
+      <c r="T7" s="76" t="s">
         <v>565</v>
-      </c>
-      <c r="T7" s="76" t="s">
-        <v>566</v>
       </c>
       <c r="U7" s="75"/>
       <c r="V7" s="75"/>
       <c r="W7" s="84"/>
       <c r="X7" s="85" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y7" s="77" t="s">
         <v>567</v>
       </c>
-      <c r="Y7" s="77" t="s">
+      <c r="Z7" s="77" t="s">
         <v>568</v>
       </c>
-      <c r="Z7" s="77" t="s">
+      <c r="AA7" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="AA7" s="77" t="s">
+      <c r="AB7" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="AB7" s="77" t="s">
+      <c r="AC7" s="77" t="s">
         <v>571</v>
-      </c>
-      <c r="AC7" s="77" t="s">
-        <v>572</v>
       </c>
       <c r="AD7" s="84"/>
       <c r="AE7" s="70"/>
@@ -23812,7 +23811,7 @@
     </row>
     <row r="8" spans="1:38" ht="109.5" customHeight="1">
       <c r="A8" s="79" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B8" s="55">
         <v>48</v>
@@ -23825,58 +23824,58 @@
       <c r="H8" s="82"/>
       <c r="I8" s="80"/>
       <c r="J8" s="61" t="s">
+        <v>555</v>
+      </c>
+      <c r="K8" s="62" t="s">
         <v>556</v>
       </c>
-      <c r="K8" s="62" t="s">
+      <c r="L8" s="63" t="s">
         <v>557</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="M8" s="63" t="s">
         <v>558</v>
       </c>
-      <c r="M8" s="63" t="s">
+      <c r="N8" s="63" t="s">
         <v>559</v>
       </c>
-      <c r="N8" s="63" t="s">
+      <c r="O8" s="63" t="s">
         <v>560</v>
       </c>
-      <c r="O8" s="63" t="s">
+      <c r="P8" s="64" t="s">
         <v>561</v>
       </c>
-      <c r="P8" s="64" t="s">
+      <c r="Q8" s="83" t="s">
         <v>562</v>
       </c>
-      <c r="Q8" s="83" t="s">
+      <c r="R8" s="76" t="s">
         <v>563</v>
       </c>
-      <c r="R8" s="76" t="s">
+      <c r="S8" s="76" t="s">
         <v>564</v>
       </c>
-      <c r="S8" s="76" t="s">
+      <c r="T8" s="76" t="s">
         <v>565</v>
-      </c>
-      <c r="T8" s="76" t="s">
-        <v>566</v>
       </c>
       <c r="U8" s="75"/>
       <c r="V8" s="75"/>
       <c r="W8" s="84"/>
       <c r="X8" s="85" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y8" s="77" t="s">
         <v>567</v>
       </c>
-      <c r="Y8" s="77" t="s">
+      <c r="Z8" s="77" t="s">
         <v>568</v>
       </c>
-      <c r="Z8" s="77" t="s">
+      <c r="AA8" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="AA8" s="77" t="s">
+      <c r="AB8" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="AB8" s="77" t="s">
+      <c r="AC8" s="77" t="s">
         <v>571</v>
-      </c>
-      <c r="AC8" s="77" t="s">
-        <v>572</v>
       </c>
       <c r="AD8" s="84"/>
       <c r="AE8" s="70"/>
@@ -23890,7 +23889,7 @@
     </row>
     <row r="9" spans="1:38" ht="109.5" customHeight="1">
       <c r="A9" s="90" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B9" s="91">
         <v>40</v>
@@ -23898,65 +23897,65 @@
       <c r="C9" s="92"/>
       <c r="D9" s="93"/>
       <c r="E9" s="94" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F9" s="95"/>
       <c r="G9" s="95"/>
       <c r="H9" s="96"/>
       <c r="I9" s="92"/>
       <c r="J9" s="97" t="s">
+        <v>555</v>
+      </c>
+      <c r="K9" s="98" t="s">
         <v>556</v>
       </c>
-      <c r="K9" s="98" t="s">
+      <c r="L9" s="99" t="s">
         <v>557</v>
       </c>
-      <c r="L9" s="99" t="s">
+      <c r="M9" s="99" t="s">
         <v>558</v>
       </c>
-      <c r="M9" s="99" t="s">
+      <c r="N9" s="99" t="s">
         <v>559</v>
       </c>
-      <c r="N9" s="99" t="s">
+      <c r="O9" s="99" t="s">
         <v>560</v>
       </c>
-      <c r="O9" s="99" t="s">
+      <c r="P9" s="100" t="s">
         <v>561</v>
       </c>
-      <c r="P9" s="100" t="s">
+      <c r="Q9" s="101" t="s">
         <v>562</v>
       </c>
-      <c r="Q9" s="101" t="s">
+      <c r="R9" s="102" t="s">
         <v>563</v>
       </c>
-      <c r="R9" s="102" t="s">
+      <c r="S9" s="102" t="s">
         <v>564</v>
       </c>
-      <c r="S9" s="102" t="s">
+      <c r="T9" s="102" t="s">
         <v>565</v>
-      </c>
-      <c r="T9" s="102" t="s">
-        <v>566</v>
       </c>
       <c r="U9" s="103"/>
       <c r="V9" s="103"/>
       <c r="W9" s="104"/>
       <c r="X9" s="105" t="s">
+        <v>566</v>
+      </c>
+      <c r="Y9" s="106" t="s">
         <v>567</v>
       </c>
-      <c r="Y9" s="106" t="s">
-        <v>568</v>
-      </c>
       <c r="Z9" s="106" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AA9" s="106" t="s">
+        <v>569</v>
+      </c>
+      <c r="AB9" s="106" t="s">
         <v>570</v>
       </c>
-      <c r="AB9" s="106" t="s">
+      <c r="AC9" s="106" t="s">
         <v>571</v>
-      </c>
-      <c r="AC9" s="106" t="s">
-        <v>572</v>
       </c>
       <c r="AD9" s="104"/>
       <c r="AE9" s="107"/>
